--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -379,7 +379,7 @@
         <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>2163.0</v>
+        <v>2174.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -431,7 +431,7 @@
         <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -483,7 +483,7 @@
         <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>147.0</v>
+        <v>158.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -509,7 +509,7 @@
         <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>363.0</v>
+        <v>368.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -535,7 +535,7 @@
         <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>827.0</v>
+        <v>834.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -561,7 +561,7 @@
         <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>3262.0</v>
+        <v>3265.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -587,7 +587,7 @@
         <v>47</v>
       </c>
       <c r="F15" t="n">
-        <v>550.0</v>
+        <v>551.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -821,7 +821,7 @@
         <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>10483.0</v>
+        <v>10502.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
@@ -847,7 +847,7 @@
         <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>2948.0</v>
+        <v>2953.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
@@ -873,10 +873,10 @@
         <v>47</v>
       </c>
       <c r="F26" t="n">
-        <v>4918.0</v>
+        <v>4946.0</v>
       </c>
       <c r="G26" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="H26" t="n">
         <v>210.0</v>
@@ -899,7 +899,7 @@
         <v>47</v>
       </c>
       <c r="F27" t="n">
-        <v>513.0</v>
+        <v>514.0</v>
       </c>
       <c r="G27" t="n">
         <v>3.0</v>
@@ -925,7 +925,7 @@
         <v>47</v>
       </c>
       <c r="F28" t="n">
-        <v>5614.0</v>
+        <v>5633.0</v>
       </c>
       <c r="G28" t="n">
         <v>12.0</v>
@@ -951,7 +951,7 @@
         <v>47</v>
       </c>
       <c r="F29" t="n">
-        <v>10827.0</v>
+        <v>10850.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -977,7 +977,7 @@
         <v>47</v>
       </c>
       <c r="F30" t="n">
-        <v>4928.0</v>
+        <v>4941.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1003,7 +1003,7 @@
         <v>47</v>
       </c>
       <c r="F31" t="n">
-        <v>1257.0</v>
+        <v>1258.0</v>
       </c>
       <c r="G31" t="n">
         <v>3.0</v>
@@ -1029,7 +1029,7 @@
         <v>47</v>
       </c>
       <c r="F32" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="G32" t="n">
         <v>4.0</v>
@@ -1367,7 +1367,7 @@
         <v>47</v>
       </c>
       <c r="F45" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1445,7 +1445,7 @@
         <v>47</v>
       </c>
       <c r="F48" t="n">
-        <v>571.0</v>
+        <v>573.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1497,7 +1497,7 @@
         <v>47</v>
       </c>
       <c r="F50" t="n">
-        <v>644.0</v>
+        <v>647.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1549,7 +1549,7 @@
         <v>47</v>
       </c>
       <c r="F52" t="n">
-        <v>1955.0</v>
+        <v>1956.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1575,7 +1575,7 @@
         <v>47</v>
       </c>
       <c r="F53" t="n">
-        <v>1781.0</v>
+        <v>1793.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1627,7 +1627,7 @@
         <v>47</v>
       </c>
       <c r="F55" t="n">
-        <v>1259.0</v>
+        <v>1271.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1835,7 +1835,7 @@
         <v>48</v>
       </c>
       <c r="F63" t="n">
-        <v>4940.0</v>
+        <v>4964.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1861,7 +1861,7 @@
         <v>48</v>
       </c>
       <c r="F64" t="n">
-        <v>758.0</v>
+        <v>763.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1887,7 +1887,7 @@
         <v>48</v>
       </c>
       <c r="F65" t="n">
-        <v>988.0</v>
+        <v>989.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2329,7 +2329,7 @@
         <v>48</v>
       </c>
       <c r="F82" t="n">
-        <v>4859.0</v>
+        <v>4876.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2355,7 +2355,7 @@
         <v>48</v>
       </c>
       <c r="F83" t="n">
-        <v>1271.0</v>
+        <v>1272.0</v>
       </c>
       <c r="G83" t="n">
         <v>2.0</v>
@@ -2641,7 +2641,7 @@
         <v>48</v>
       </c>
       <c r="F94" t="n">
-        <v>3942.0</v>
+        <v>3943.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2797,7 +2797,7 @@
         <v>48</v>
       </c>
       <c r="F100" t="n">
-        <v>11836.0</v>
+        <v>11860.0</v>
       </c>
       <c r="G100" t="n">
         <v>14.0</v>
@@ -2875,7 +2875,7 @@
         <v>48</v>
       </c>
       <c r="F103" t="n">
-        <v>1027.0</v>
+        <v>1029.0</v>
       </c>
       <c r="G103" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -249,7 +249,7 @@
         <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -301,7 +301,7 @@
         <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>727.0</v>
+        <v>730.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -535,7 +535,7 @@
         <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>834.0</v>
+        <v>835.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -717,7 +717,7 @@
         <v>47</v>
       </c>
       <c r="F20" t="n">
-        <v>2755.0</v>
+        <v>2765.0</v>
       </c>
       <c r="G20" t="n">
         <v>57.0</v>
@@ -743,7 +743,7 @@
         <v>47</v>
       </c>
       <c r="F21" t="n">
-        <v>1821.0</v>
+        <v>1823.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
@@ -795,7 +795,7 @@
         <v>47</v>
       </c>
       <c r="F23" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G23" t="n">
         <v>6.0</v>
@@ -847,13 +847,13 @@
         <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>2953.0</v>
+        <v>2954.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
       </c>
       <c r="H25" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="26">
@@ -879,7 +879,7 @@
         <v>36.0</v>
       </c>
       <c r="H26" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="27">
@@ -951,7 +951,7 @@
         <v>47</v>
       </c>
       <c r="F29" t="n">
-        <v>10850.0</v>
+        <v>10856.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -1185,7 +1185,7 @@
         <v>47</v>
       </c>
       <c r="F38" t="n">
-        <v>376.0</v>
+        <v>466.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1211,7 +1211,7 @@
         <v>47</v>
       </c>
       <c r="F39" t="n">
-        <v>388.0</v>
+        <v>392.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1497,7 +1497,7 @@
         <v>47</v>
       </c>
       <c r="F50" t="n">
-        <v>647.0</v>
+        <v>648.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1549,7 +1549,7 @@
         <v>47</v>
       </c>
       <c r="F52" t="n">
-        <v>1956.0</v>
+        <v>1959.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1731,7 +1731,7 @@
         <v>48</v>
       </c>
       <c r="F59" t="n">
-        <v>2414.0</v>
+        <v>2418.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1991,7 +1991,7 @@
         <v>48</v>
       </c>
       <c r="F69" t="n">
-        <v>194.0</v>
+        <v>196.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2147,7 +2147,7 @@
         <v>48</v>
       </c>
       <c r="F75" t="n">
-        <v>2914.0</v>
+        <v>2915.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Torino</t>
+  </si>
+  <si>
+    <t>Pisa</t>
   </si>
   <si>
     <t>Salerno</t>
@@ -246,7 +249,7 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
         <v>25.0</v>
@@ -272,10 +275,10 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>311.0</v>
+        <v>327.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -298,10 +301,10 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>730.0</v>
+        <v>736.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -324,7 +327,7 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
         <v>124.0</v>
@@ -350,7 +353,7 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
         <v>231.0</v>
@@ -376,10 +379,10 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>2174.0</v>
+        <v>2176.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -402,10 +405,10 @@
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>44.0</v>
+        <v>53.0</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
@@ -428,7 +431,7 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
         <v>119.0</v>
@@ -454,7 +457,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
         <v>65.0</v>
@@ -480,10 +483,10 @@
         <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>158.0</v>
+        <v>161.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -506,10 +509,10 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>368.0</v>
+        <v>375.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -532,10 +535,10 @@
         <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>835.0</v>
+        <v>880.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -558,10 +561,10 @@
         <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>3265.0</v>
+        <v>3288.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -584,10 +587,10 @@
         <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>551.0</v>
+        <v>557.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -610,10 +613,10 @@
         <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>140.0</v>
+        <v>143.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -636,10 +639,10 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>277.0</v>
+        <v>308.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -662,7 +665,7 @@
         <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F18" t="n">
         <v>128.0</v>
@@ -688,7 +691,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
         <v>74.0</v>
@@ -714,16 +717,16 @@
         <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2765.0</v>
+        <v>2793.0</v>
       </c>
       <c r="G20" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="H20" t="n">
-        <v>331.0</v>
+        <v>336.0</v>
       </c>
     </row>
     <row r="21">
@@ -740,16 +743,16 @@
         <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1823.0</v>
+        <v>1826.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
       </c>
       <c r="H21" t="n">
-        <v>221.0</v>
+        <v>224.0</v>
       </c>
     </row>
     <row r="22">
@@ -766,7 +769,7 @@
         <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -775,7 +778,7 @@
         <v>0.0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="23">
@@ -792,13 +795,13 @@
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G23" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -818,16 +821,16 @@
         <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10502.0</v>
+        <v>10512.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
       </c>
       <c r="H24" t="n">
-        <v>962.0</v>
+        <v>964.0</v>
       </c>
     </row>
     <row r="25">
@@ -844,16 +847,16 @@
         <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>2954.0</v>
+        <v>3013.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
       </c>
       <c r="H25" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="26">
@@ -870,13 +873,13 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4946.0</v>
+        <v>4951.0</v>
       </c>
       <c r="G26" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="H26" t="n">
         <v>212.0</v>
@@ -896,7 +899,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
         <v>514.0</v>
@@ -922,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>5633.0</v>
+        <v>5666.0</v>
       </c>
       <c r="G28" t="n">
         <v>12.0</v>
@@ -948,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10856.0</v>
+        <v>10927.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -974,10 +977,10 @@
         <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>4941.0</v>
+        <v>4982.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1000,10 +1003,10 @@
         <v>31</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>1258.0</v>
+        <v>1264.0</v>
       </c>
       <c r="G31" t="n">
         <v>3.0</v>
@@ -1026,10 +1029,10 @@
         <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>165.0</v>
+        <v>168.0</v>
       </c>
       <c r="G32" t="n">
         <v>4.0</v>
@@ -1052,7 +1055,7 @@
         <v>33</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
@@ -1078,16 +1081,16 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>610.0</v>
+        <v>634.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>178.0</v>
+        <v>204.0</v>
       </c>
     </row>
     <row r="35">
@@ -1104,7 +1107,7 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F35" t="n">
         <v>0.0</v>
@@ -1113,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>181.0</v>
+        <v>204.0</v>
       </c>
     </row>
     <row r="36">
@@ -1130,10 +1133,10 @@
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3295.0</v>
+        <v>3318.0</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
@@ -1156,7 +1159,7 @@
         <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F37" t="n">
         <v>18.0</v>
@@ -1182,10 +1185,10 @@
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>466.0</v>
+        <v>472.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1208,10 +1211,10 @@
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>392.0</v>
+        <v>464.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1234,7 +1237,7 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F40" t="n">
         <v>18.0</v>
@@ -1260,7 +1263,7 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41" t="n">
         <v>3.0</v>
@@ -1286,10 +1289,10 @@
         <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>749.0</v>
+        <v>759.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1312,10 +1315,10 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>996.0</v>
+        <v>1009.0</v>
       </c>
       <c r="G43" t="n">
         <v>4.0</v>
@@ -1338,7 +1341,7 @@
         <v>41</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
@@ -1364,10 +1367,10 @@
         <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1390,7 +1393,7 @@
         <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F46" t="n">
         <v>8.0</v>
@@ -1416,7 +1419,7 @@
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F47" t="n">
         <v>3.0</v>
@@ -1442,10 +1445,10 @@
         <v>28</v>
       </c>
       <c r="E48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>573.0</v>
+        <v>575.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1468,10 +1471,10 @@
         <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1494,10 +1497,10 @@
         <v>30</v>
       </c>
       <c r="E50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>648.0</v>
+        <v>677.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1520,7 +1523,7 @@
         <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F51" t="n">
         <v>1.0</v>
@@ -1546,10 +1549,10 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1959.0</v>
+        <v>1981.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1572,10 +1575,10 @@
         <v>32</v>
       </c>
       <c r="E53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1793.0</v>
+        <v>1853.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1598,7 +1601,7 @@
         <v>44</v>
       </c>
       <c r="E54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F54" t="n">
         <v>1.0</v>
@@ -1624,10 +1627,10 @@
         <v>33</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1271.0</v>
+        <v>1285.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1650,10 +1653,10 @@
         <v>34</v>
       </c>
       <c r="E56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
-        <v>759.0</v>
+        <v>760.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1673,16 +1676,16 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F57" t="n">
-        <v>1163.0</v>
+        <v>1.0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1693,22 +1696,22 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E58" t="s">
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>33.0</v>
+        <v>1188.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1725,13 +1728,13 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E59" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>2418.0</v>
+        <v>38.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1751,13 +1754,13 @@
         <v>12</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>1032.0</v>
+        <v>2443.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1777,13 +1780,13 @@
         <v>12</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>40.0</v>
+        <v>1043.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1800,16 +1803,16 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>9.0</v>
+        <v>41.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1826,22 +1829,22 @@
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F63" t="n">
-        <v>4964.0</v>
+        <v>9.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1855,19 +1858,19 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>763.0</v>
+        <v>4999.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="65">
@@ -1881,19 +1884,19 @@
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>989.0</v>
+        <v>770.0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1904,22 +1907,22 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>51.0</v>
+        <v>995.0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="67">
@@ -1933,13 +1936,13 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>104.0</v>
+        <v>54.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1959,16 +1962,16 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>306.0</v>
+        <v>104.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1985,19 +1988,19 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>196.0</v>
+        <v>309.0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H69" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -2008,22 +2011,22 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>18.0</v>
+        <v>198.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="71">
@@ -2037,16 +2040,16 @@
         <v>16</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
         <v>18.0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2057,22 +2060,22 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E72" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F72" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2086,16 +2089,16 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="E73" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F73" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2115,16 +2118,16 @@
         <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1645.0</v>
+        <v>4.0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2141,19 +2144,19 @@
         <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>2915.0</v>
+        <v>1667.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H75" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -2167,19 +2170,19 @@
         <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E76" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>1.0</v>
+        <v>2957.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="77">
@@ -2190,16 +2193,16 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E77" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F77" t="n">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2219,16 +2222,16 @@
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E78" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F78" t="n">
-        <v>24.0</v>
+        <v>31.0</v>
       </c>
       <c r="G78" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2245,16 +2248,16 @@
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E79" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F79" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2268,16 +2271,16 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F80" t="n">
-        <v>7.0</v>
+        <v>27.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2297,19 +2300,19 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F81" t="n">
-        <v>328.0</v>
+        <v>7.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
       </c>
       <c r="H81" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -2323,19 +2326,19 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>4876.0</v>
+        <v>328.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
       </c>
       <c r="H82" t="n">
-        <v>12928.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="83">
@@ -2346,22 +2349,22 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E83" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>1272.0</v>
+        <v>4899.0</v>
       </c>
       <c r="G83" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H83" t="n">
-        <v>29.0</v>
+        <v>12928.0</v>
       </c>
     </row>
     <row r="84">
@@ -2375,19 +2378,19 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>15.0</v>
+        <v>1278.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="85">
@@ -2401,19 +2404,19 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>29.0</v>
+        <v>16.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>47.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -2424,22 +2427,22 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F86" t="n">
-        <v>8.0</v>
+        <v>29.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="87">
@@ -2453,13 +2456,13 @@
         <v>16</v>
       </c>
       <c r="D87" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E87" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F87" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2473,19 +2476,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E88" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F88" t="n">
-        <v>239.0</v>
+        <v>17.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2505,13 +2508,13 @@
         <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>517.0</v>
+        <v>241.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2531,13 +2534,13 @@
         <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E90" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>287.0</v>
+        <v>521.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2557,13 +2560,13 @@
         <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>217.0</v>
+        <v>289.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2583,13 +2586,13 @@
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E92" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>310.0</v>
+        <v>220.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2606,16 +2609,16 @@
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E93" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F93" t="n">
-        <v>14.0</v>
+        <v>311.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2632,16 +2635,16 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>3943.0</v>
+        <v>14.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2661,16 +2664,16 @@
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E95" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F95" t="n">
-        <v>2794.0</v>
+        <v>3945.0</v>
       </c>
       <c r="G95" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2687,16 +2690,16 @@
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E96" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>77.0</v>
+        <v>2795.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2713,13 +2716,13 @@
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F97" t="n">
-        <v>71.0</v>
+        <v>77.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2736,16 +2739,16 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2765,13 +2768,13 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F99" t="n">
-        <v>131.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2791,16 +2794,16 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E100" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F100" t="n">
-        <v>11860.0</v>
+        <v>131.0</v>
       </c>
       <c r="G100" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2817,19 +2820,19 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>285.0</v>
+        <v>11941.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H101" t="n">
-        <v>39.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -2843,19 +2846,19 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>287.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="103">
@@ -2869,19 +2872,19 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E103" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F103" t="n">
-        <v>1029.0</v>
+        <v>4.0</v>
       </c>
       <c r="G103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2892,22 +2895,22 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E104" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F104" t="n">
+        <v>1034.0</v>
+      </c>
+      <c r="G104" t="n">
         <v>1.0</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H104" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="105">
@@ -2918,16 +2921,16 @@
         <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E105" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F105" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2947,18 +2950,44 @@
         <v>16</v>
       </c>
       <c r="D106" t="s">
+        <v>34</v>
+      </c>
+      <c r="E106" t="s">
+        <v>49</v>
+      </c>
+      <c r="F106" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" t="s">
         <v>35</v>
       </c>
-      <c r="E106" t="s">
-        <v>48</v>
-      </c>
-      <c r="F106" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H106" t="n">
+      <c r="E107" t="s">
+        <v>49</v>
+      </c>
+      <c r="F107" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H107" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -382,7 +382,7 @@
         <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>2176.0</v>
+        <v>2177.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>880.0</v>
+        <v>891.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -564,7 +564,7 @@
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>3288.0</v>
+        <v>3290.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>557.0</v>
+        <v>562.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -752,7 +752,7 @@
         <v>40.0</v>
       </c>
       <c r="H21" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
     </row>
     <row r="22">
@@ -824,13 +824,13 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10512.0</v>
+        <v>10520.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
       </c>
       <c r="H24" t="n">
-        <v>964.0</v>
+        <v>965.0</v>
       </c>
     </row>
     <row r="25">
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4951.0</v>
+        <v>4956.0</v>
       </c>
       <c r="G26" t="n">
         <v>38.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>4982.0</v>
+        <v>4995.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1136,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3318.0</v>
+        <v>3320.0</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>1009.0</v>
+        <v>1011.0</v>
       </c>
       <c r="G43" t="n">
         <v>4.0</v>
@@ -1500,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>677.0</v>
+        <v>678.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1853.0</v>
+        <v>1899.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1285.0</v>
+        <v>1293.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1188.0</v>
+        <v>1192.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -1968,7 +1968,7 @@
         <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>11941.0</v>
+        <v>11964.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2852,7 +2852,7 @@
         <v>49</v>
       </c>
       <c r="F102" t="n">
-        <v>287.0</v>
+        <v>289.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>891.0</v>
+        <v>892.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>562.0</v>
+        <v>563.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -642,7 +642,7 @@
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>5666.0</v>
+        <v>5703.0</v>
       </c>
       <c r="G28" t="n">
         <v>12.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10927.0</v>
+        <v>10935.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>4995.0</v>
+        <v>4997.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1090,7 +1090,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>204.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="35">
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1500,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>678.0</v>
+        <v>681.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1981.0</v>
+        <v>1987.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1899.0</v>
+        <v>1913.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>11964.0</v>
+        <v>11975.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2904,7 +2904,7 @@
         <v>49</v>
       </c>
       <c r="F104" t="n">
-        <v>1034.0</v>
+        <v>1039.0</v>
       </c>
       <c r="G104" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>736.0</v>
+        <v>737.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -694,7 +694,7 @@
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G19" t="n">
         <v>2.0</v>
@@ -720,13 +720,13 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2793.0</v>
+        <v>2794.0</v>
       </c>
       <c r="G20" t="n">
         <v>58.0</v>
       </c>
       <c r="H20" t="n">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="21">
@@ -1136,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3320.0</v>
+        <v>3321.0</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
@@ -1188,7 +1188,7 @@
         <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>472.0</v>
+        <v>478.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1214,7 +1214,7 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>464.0</v>
+        <v>467.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>759.0</v>
+        <v>765.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>38.0</v>
+        <v>47.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2443.0</v>
+        <v>2457.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1786,7 +1786,7 @@
         <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>1043.0</v>
+        <v>1051.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2150,7 +2150,7 @@
         <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>1667.0</v>
+        <v>1669.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>2957.0</v>
+        <v>2961.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>289.0</v>
+        <v>291.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>737.0</v>
+        <v>739.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -382,7 +382,7 @@
         <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>2177.0</v>
+        <v>2178.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>892.0</v>
+        <v>897.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -616,7 +616,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -720,7 +720,7 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2794.0</v>
+        <v>2799.0</v>
       </c>
       <c r="G20" t="n">
         <v>58.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4956.0</v>
+        <v>4960.0</v>
       </c>
       <c r="G26" t="n">
         <v>38.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10935.0</v>
+        <v>10951.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -1116,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>204.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="36">
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1987.0</v>
+        <v>1993.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1913.0</v>
+        <v>1935.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1293.0</v>
+        <v>1298.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2457.0</v>
+        <v>2461.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1786,7 +1786,7 @@
         <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>1051.0</v>
+        <v>1053.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1968,7 +1968,7 @@
         <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>2961.0</v>
+        <v>2966.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>1278.0</v>
+        <v>1279.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>11975.0</v>
+        <v>12005.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2852,7 +2852,7 @@
         <v>49</v>
       </c>
       <c r="F102" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>
@@ -2904,7 +2904,7 @@
         <v>49</v>
       </c>
       <c r="F104" t="n">
-        <v>1039.0</v>
+        <v>1040.0</v>
       </c>
       <c r="G104" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>897.0</v>
+        <v>898.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -642,7 +642,7 @@
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -850,13 +850,13 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3013.0</v>
+        <v>3023.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
       </c>
       <c r="H25" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="26">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10951.0</v>
+        <v>10954.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -1084,7 +1084,7 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>634.0</v>
+        <v>635.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
@@ -1500,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>681.0</v>
+        <v>687.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1935.0</v>
+        <v>1937.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1298.0</v>
+        <v>1304.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1192.0</v>
+        <v>1193.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -2020,7 +2020,7 @@
         <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>198.0</v>
+        <v>200.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2852,7 +2852,7 @@
         <v>49</v>
       </c>
       <c r="F102" t="n">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>739.0</v>
+        <v>740.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>898.0</v>
+        <v>899.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>563.0</v>
+        <v>565.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -642,7 +642,7 @@
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>310.0</v>
+        <v>313.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -694,13 +694,13 @@
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G19" t="n">
         <v>2.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="20">
@@ -720,7 +720,7 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2799.0</v>
+        <v>2803.0</v>
       </c>
       <c r="G20" t="n">
         <v>58.0</v>
@@ -746,13 +746,13 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1826.0</v>
+        <v>1828.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
       </c>
       <c r="H21" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="22">
@@ -824,13 +824,13 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10520.0</v>
+        <v>10524.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
       </c>
       <c r="H24" t="n">
-        <v>965.0</v>
+        <v>966.0</v>
       </c>
     </row>
     <row r="25">
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3023.0</v>
+        <v>3030.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4960.0</v>
+        <v>4963.0</v>
       </c>
       <c r="G26" t="n">
         <v>38.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>4997.0</v>
+        <v>5004.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1006,7 +1006,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>1264.0</v>
+        <v>1266.0</v>
       </c>
       <c r="G31" t="n">
         <v>3.0</v>
@@ -1084,13 +1084,13 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>635.0</v>
+        <v>643.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>207.0</v>
+        <v>218.0</v>
       </c>
     </row>
     <row r="35">
@@ -1116,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>207.0</v>
+        <v>211.0</v>
       </c>
     </row>
     <row r="36">
@@ -1136,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3321.0</v>
+        <v>3330.0</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
@@ -1500,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>687.0</v>
+        <v>691.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1993.0</v>
+        <v>1995.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1937.0</v>
+        <v>1939.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1193.0</v>
+        <v>1197.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2461.0</v>
+        <v>2472.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1786,7 +1786,7 @@
         <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>1053.0</v>
+        <v>1059.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1812,7 +1812,7 @@
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1994,7 +1994,7 @@
         <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
       <c r="G69" t="n">
         <v>1.0</v>
@@ -2020,7 +2020,7 @@
         <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2150,7 +2150,7 @@
         <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>1669.0</v>
+        <v>1678.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>2966.0</v>
+        <v>2976.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12005.0</v>
+        <v>12028.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2852,7 +2852,7 @@
         <v>49</v>
       </c>
       <c r="F102" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>375.0</v>
+        <v>377.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>899.0</v>
+        <v>903.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -564,7 +564,7 @@
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>3290.0</v>
+        <v>3291.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10954.0</v>
+        <v>10964.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>5004.0</v>
+        <v>5007.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1009,7 +1009,7 @@
         <v>1266.0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1084,13 +1084,13 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>643.0</v>
+        <v>645.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>218.0</v>
+        <v>227.0</v>
       </c>
     </row>
     <row r="35">
@@ -1136,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3330.0</v>
+        <v>3331.0</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>98.0</v>
+        <v>104.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1995.0</v>
+        <v>1997.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1939.0</v>
+        <v>1950.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1197.0</v>
+        <v>1200.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>1279.0</v>
+        <v>1280.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -2800,7 +2800,7 @@
         <v>49</v>
       </c>
       <c r="F100" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12028.0</v>
+        <v>12047.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>740.0</v>
+        <v>741.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -408,7 +408,7 @@
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>53.0</v>
+        <v>64.0</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
@@ -697,7 +697,7 @@
         <v>77.0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H19" t="n">
         <v>2.0</v>
@@ -720,10 +720,10 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2803.0</v>
+        <v>2807.0</v>
       </c>
       <c r="G20" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="H20" t="n">
         <v>337.0</v>
@@ -830,7 +830,7 @@
         <v>146.0</v>
       </c>
       <c r="H24" t="n">
-        <v>966.0</v>
+        <v>967.0</v>
       </c>
     </row>
     <row r="25">
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3030.0</v>
+        <v>3033.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
@@ -882,7 +882,7 @@
         <v>38.0</v>
       </c>
       <c r="H26" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="27">
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>5703.0</v>
+        <v>5739.0</v>
       </c>
       <c r="G28" t="n">
         <v>12.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10964.0</v>
+        <v>10985.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -1006,7 +1006,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>1266.0</v>
+        <v>1268.0</v>
       </c>
       <c r="G31" t="n">
         <v>4.0</v>
@@ -1116,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>211.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="36">
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1997.0</v>
+        <v>2004.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1950.0</v>
+        <v>1982.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1304.0</v>
+        <v>1305.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>47.0</v>
+        <v>51.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2472.0</v>
+        <v>2477.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1786,7 +1786,7 @@
         <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>1059.0</v>
+        <v>1064.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1864,7 +1864,7 @@
         <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>4999.0</v>
+        <v>5043.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1890,7 +1890,7 @@
         <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>770.0</v>
+        <v>784.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>995.0</v>
+        <v>1001.0</v>
       </c>
       <c r="G66" t="n">
         <v>1.0</v>
@@ -2150,7 +2150,7 @@
         <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>1678.0</v>
+        <v>1684.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>2976.0</v>
+        <v>2981.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2332,7 +2332,7 @@
         <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>328.0</v>
+        <v>336.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2358,7 +2358,7 @@
         <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>4899.0</v>
+        <v>4931.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2514,7 +2514,7 @@
         <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2540,7 +2540,7 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>521.0</v>
+        <v>523.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2618,7 +2618,7 @@
         <v>49</v>
       </c>
       <c r="F93" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2670,7 +2670,7 @@
         <v>49</v>
       </c>
       <c r="F95" t="n">
-        <v>3945.0</v>
+        <v>3950.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2696,7 +2696,7 @@
         <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>2795.0</v>
+        <v>2796.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2748,7 +2748,7 @@
         <v>49</v>
       </c>
       <c r="F98" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2800,7 +2800,7 @@
         <v>49</v>
       </c>
       <c r="F100" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12047.0</v>
+        <v>12063.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2904,7 +2904,7 @@
         <v>49</v>
       </c>
       <c r="F104" t="n">
-        <v>1040.0</v>
+        <v>1041.0</v>
       </c>
       <c r="G104" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -252,7 +252,7 @@
         <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -278,7 +278,7 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>741.0</v>
+        <v>757.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -330,7 +330,7 @@
         <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>124.0</v>
+        <v>129.0</v>
       </c>
       <c r="G5" t="n">
         <v>3.0</v>
@@ -356,7 +356,7 @@
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>231.0</v>
+        <v>235.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -720,13 +720,13 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2807.0</v>
+        <v>2852.0</v>
       </c>
       <c r="G20" t="n">
         <v>59.0</v>
       </c>
       <c r="H20" t="n">
-        <v>337.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1828.0</v>
+        <v>1832.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
@@ -1188,7 +1188,7 @@
         <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>478.0</v>
+        <v>503.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1214,7 +1214,7 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>467.0</v>
+        <v>491.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>765.0</v>
+        <v>769.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1200.0</v>
+        <v>1201.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>903.0</v>
+        <v>908.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>565.0</v>
+        <v>566.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10985.0</v>
+        <v>10992.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>2004.0</v>
+        <v>2005.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1982.0</v>
+        <v>1988.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>1280.0</v>
+        <v>1281.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12063.0</v>
+        <v>12083.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -382,7 +382,7 @@
         <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>2178.0</v>
+        <v>2179.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -726,7 +726,7 @@
         <v>59.0</v>
       </c>
       <c r="H20" t="n">
-        <v>340.0</v>
+        <v>342.0</v>
       </c>
     </row>
     <row r="21">
@@ -752,7 +752,7 @@
         <v>40.0</v>
       </c>
       <c r="H21" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
     </row>
     <row r="22">
@@ -824,13 +824,13 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10524.0</v>
+        <v>10528.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
       </c>
       <c r="H24" t="n">
-        <v>967.0</v>
+        <v>969.0</v>
       </c>
     </row>
     <row r="25">
@@ -850,13 +850,13 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3033.0</v>
+        <v>3038.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
       </c>
       <c r="H25" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4963.0</v>
+        <v>4967.0</v>
       </c>
       <c r="G26" t="n">
         <v>38.0</v>
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>5739.0</v>
+        <v>5745.0</v>
       </c>
       <c r="G28" t="n">
         <v>12.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>104.0</v>
+        <v>107.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1500,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>691.0</v>
+        <v>692.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1988.0</v>
+        <v>1994.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1305.0</v>
+        <v>1310.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1864,7 +1864,7 @@
         <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>5043.0</v>
+        <v>5054.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1890,7 +1890,7 @@
         <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>784.0</v>
+        <v>788.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>1001.0</v>
+        <v>1007.0</v>
       </c>
       <c r="G66" t="n">
         <v>1.0</v>
@@ -2020,7 +2020,7 @@
         <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>201.0</v>
+        <v>203.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2332,7 +2332,7 @@
         <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>336.0</v>
+        <v>338.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2358,7 +2358,7 @@
         <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>4931.0</v>
+        <v>4939.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2670,7 +2670,7 @@
         <v>49</v>
       </c>
       <c r="F95" t="n">
-        <v>3950.0</v>
+        <v>3952.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2748,7 +2748,7 @@
         <v>49</v>
       </c>
       <c r="F98" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>757.0</v>
+        <v>753.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>908.0</v>
+        <v>911.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -564,7 +564,7 @@
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>3291.0</v>
+        <v>3297.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -697,7 +697,7 @@
         <v>77.0</v>
       </c>
       <c r="G19" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H19" t="n">
         <v>2.0</v>
@@ -720,13 +720,13 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2852.0</v>
+        <v>2865.0</v>
       </c>
       <c r="G20" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="H20" t="n">
-        <v>342.0</v>
+        <v>344.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1832.0</v>
+        <v>1833.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3038.0</v>
+        <v>3040.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10992.0</v>
+        <v>10994.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>5007.0</v>
+        <v>5009.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1084,13 +1084,13 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>645.0</v>
+        <v>654.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>227.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="35">
@@ -1116,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
     </row>
     <row r="36">
@@ -1136,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3331.0</v>
+        <v>3338.0</v>
       </c>
       <c r="G36" t="n">
         <v>3.0</v>
@@ -1240,7 +1240,7 @@
         <v>48</v>
       </c>
       <c r="F40" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>575.0</v>
+        <v>576.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>2005.0</v>
+        <v>2009.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1656,7 +1656,7 @@
         <v>48</v>
       </c>
       <c r="F56" t="n">
-        <v>760.0</v>
+        <v>761.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1201.0</v>
+        <v>1202.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2477.0</v>
+        <v>2485.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1786,7 +1786,7 @@
         <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>1064.0</v>
+        <v>1070.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2150,7 +2150,7 @@
         <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>1684.0</v>
+        <v>1693.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>2981.0</v>
+        <v>2997.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>1281.0</v>
+        <v>1282.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>223.0</v>
+        <v>225.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2748,7 +2748,7 @@
         <v>49</v>
       </c>
       <c r="F98" t="n">
-        <v>74.0</v>
+        <v>73.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12083.0</v>
+        <v>12102.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>911.0</v>
+        <v>940.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>566.0</v>
+        <v>571.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -824,13 +824,13 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10528.0</v>
+        <v>10534.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
       </c>
       <c r="H24" t="n">
-        <v>969.0</v>
+        <v>970.0</v>
       </c>
     </row>
     <row r="25">
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3040.0</v>
+        <v>3047.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>514.0</v>
+        <v>515.0</v>
       </c>
       <c r="G27" t="n">
         <v>3.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>10994.0</v>
+        <v>11014.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>5009.0</v>
+        <v>5014.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1032,7 +1032,7 @@
         <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G32" t="n">
         <v>4.0</v>
@@ -1090,7 +1090,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" t="n">
-        <v>240.0</v>
+        <v>249.0</v>
       </c>
     </row>
     <row r="35">
@@ -1116,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="36">
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1500,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>692.0</v>
+        <v>696.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="F53" t="n">
-        <v>1994.0</v>
+        <v>2026.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1310.0</v>
+        <v>1311.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1202.0</v>
+        <v>1204.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -2020,7 +2020,7 @@
         <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12102.0</v>
+        <v>12122.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2904,7 +2904,7 @@
         <v>49</v>
       </c>
       <c r="F104" t="n">
-        <v>1041.0</v>
+        <v>1047.0</v>
       </c>
       <c r="G104" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -252,7 +252,7 @@
         <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>753.0</v>
+        <v>757.0</v>
       </c>
       <c r="G4" t="n">
         <v>5.0</v>
@@ -330,7 +330,7 @@
         <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>129.0</v>
+        <v>141.0</v>
       </c>
       <c r="G5" t="n">
         <v>3.0</v>
@@ -356,7 +356,7 @@
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>235.0</v>
+        <v>240.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -564,7 +564,7 @@
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>3297.0</v>
+        <v>3298.0</v>
       </c>
       <c r="G14" t="n">
         <v>4.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>571.0</v>
+        <v>572.0</v>
       </c>
       <c r="G15" t="n">
         <v>2.0</v>
@@ -720,7 +720,7 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2865.0</v>
+        <v>2898.0</v>
       </c>
       <c r="G20" t="n">
         <v>61.0</v>
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1833.0</v>
+        <v>1835.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
@@ -798,7 +798,7 @@
         <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>318.0</v>
+        <v>321.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10534.0</v>
+        <v>10543.0</v>
       </c>
       <c r="G24" t="n">
         <v>146.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3047.0</v>
+        <v>3049.0</v>
       </c>
       <c r="G25" t="n">
         <v>20.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4967.0</v>
+        <v>4968.0</v>
       </c>
       <c r="G26" t="n">
         <v>38.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>11014.0</v>
+        <v>11026.0</v>
       </c>
       <c r="G29" t="n">
         <v>24.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>5014.0</v>
+        <v>5015.0</v>
       </c>
       <c r="G30" t="n">
         <v>6.0</v>
@@ -1084,7 +1084,7 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>654.0</v>
+        <v>655.0</v>
       </c>
       <c r="G34" t="n">
         <v>1.0</v>
@@ -1188,7 +1188,7 @@
         <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>503.0</v>
+        <v>554.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1214,7 +1214,7 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>491.0</v>
+        <v>513.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>769.0</v>
+        <v>774.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>2009.0</v>
+        <v>2010.0</v>
       </c>
       <c r="G52" t="n">
         <v>10.0</v>
@@ -1630,7 +1630,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>1311.0</v>
+        <v>1312.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2485.0</v>
+        <v>2499.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1994,7 +1994,7 @@
         <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="G69" t="n">
         <v>1.0</v>
@@ -2150,7 +2150,7 @@
         <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>1693.0</v>
+        <v>1703.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>2997.0</v>
+        <v>3006.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2514,7 +2514,7 @@
         <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>242.0</v>
+        <v>245.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2540,7 +2540,7 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>523.0</v>
+        <v>525.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>12122.0</v>
+        <v>12140.0</v>
       </c>
       <c r="G101" t="n">
         <v>14.0</v>
@@ -2982,7 +2982,7 @@
         <v>49</v>
       </c>
       <c r="F107" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -1162,7 +1162,7 @@
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1708,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="F58" t="n">
-        <v>1204.0</v>
+        <v>1206.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -92,61 +92,61 @@
     <t>Lodi</t>
   </si>
   <si>
+    <t>Pavia</t>
+  </si>
+  <si>
+    <t>Alessandria</t>
+  </si>
+  <si>
+    <t>Asti</t>
+  </si>
+  <si>
+    <t>Cuneo</t>
+  </si>
+  <si>
+    <t>Lucca</t>
+  </si>
+  <si>
+    <t>Pistoia</t>
+  </si>
+  <si>
+    <t>Reggio emilia</t>
+  </si>
+  <si>
+    <t>Genova</t>
+  </si>
+  <si>
+    <t>La spezia</t>
+  </si>
+  <si>
+    <t>Massa</t>
+  </si>
+  <si>
+    <t>Massa-carrara</t>
+  </si>
+  <si>
+    <t>Brescia</t>
+  </si>
+  <si>
+    <t>Cremona</t>
+  </si>
+  <si>
     <t>Milano</t>
   </si>
   <si>
-    <t>Pavia</t>
-  </si>
-  <si>
     <t>Varese</t>
   </si>
   <si>
-    <t>Alessandria</t>
-  </si>
-  <si>
-    <t>Asti</t>
-  </si>
-  <si>
-    <t>Cuneo</t>
+    <t>Biella</t>
   </si>
   <si>
     <t>Novara</t>
   </si>
   <si>
+    <t>Torino</t>
+  </si>
+  <si>
     <t>Vercelli</t>
-  </si>
-  <si>
-    <t>Lucca</t>
-  </si>
-  <si>
-    <t>Pistoia</t>
-  </si>
-  <si>
-    <t>Reggio emilia</t>
-  </si>
-  <si>
-    <t>Genova</t>
-  </si>
-  <si>
-    <t>La spezia</t>
-  </si>
-  <si>
-    <t>Massa</t>
-  </si>
-  <si>
-    <t>Massa-carrara</t>
-  </si>
-  <si>
-    <t>Brescia</t>
-  </si>
-  <si>
-    <t>Cremona</t>
-  </si>
-  <si>
-    <t>Biella</t>
-  </si>
-  <si>
-    <t>Torino</t>
   </si>
   <si>
     <t>Pisa</t>
@@ -278,7 +278,7 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>329.0</v>
+        <v>353.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -304,10 +304,10 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>757.0</v>
+        <v>723.0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0</v>
@@ -330,13 +330,13 @@
         <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>141.0</v>
+        <v>298.0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -356,7 +356,7 @@
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>240.0</v>
+        <v>655.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -408,7 +408,7 @@
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>64.0</v>
+        <v>22.0</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
@@ -434,13 +434,13 @@
         <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>119.0</v>
+        <v>1090.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="10">
@@ -451,7 +451,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -460,13 +460,13 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>65.0</v>
+        <v>1134.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="11">
@@ -477,7 +477,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -486,10 +486,10 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>161.0</v>
+        <v>922.0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -512,10 +512,10 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>379.0</v>
+        <v>3299.0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
@@ -538,10 +538,10 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>940.0</v>
+        <v>313.0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0</v>
@@ -555,7 +555,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
@@ -564,10 +564,10 @@
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>3298.0</v>
+        <v>128.0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -578,25 +578,25 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>572.0</v>
+        <v>294.0</v>
       </c>
       <c r="G15" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -604,25 +604,25 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>144.0</v>
+        <v>2946.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0</v>
+        <v>352.0</v>
       </c>
     </row>
     <row r="17">
@@ -630,25 +630,25 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>313.0</v>
+        <v>1681.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>42.0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0</v>
+        <v>225.0</v>
       </c>
     </row>
     <row r="18">
@@ -656,25 +656,25 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
       </c>
       <c r="F18" t="n">
-        <v>128.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="19">
@@ -688,19 +688,19 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>77.0</v>
+        <v>561.0</v>
       </c>
       <c r="G19" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -711,22 +711,22 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>2898.0</v>
+        <v>10544.0</v>
       </c>
       <c r="G20" t="n">
-        <v>61.0</v>
+        <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>344.0</v>
+        <v>970.0</v>
       </c>
     </row>
     <row r="21">
@@ -737,22 +737,22 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1835.0</v>
+        <v>3049.0</v>
       </c>
       <c r="G21" t="n">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>227.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="22">
@@ -763,22 +763,22 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0</v>
+        <v>4970.0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>39.0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.0</v>
+        <v>215.0</v>
       </c>
     </row>
     <row r="23">
@@ -789,22 +789,22 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
         <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>321.0</v>
+        <v>3552.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="24">
@@ -815,22 +815,22 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>10543.0</v>
+        <v>9736.0</v>
       </c>
       <c r="G24" t="n">
-        <v>146.0</v>
+        <v>20.0</v>
       </c>
       <c r="H24" t="n">
-        <v>970.0</v>
+        <v>715.0</v>
       </c>
     </row>
     <row r="25">
@@ -841,22 +841,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>3049.0</v>
+        <v>5018.0</v>
       </c>
       <c r="G25" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="H25" t="n">
-        <v>58.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="26">
@@ -867,22 +867,22 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>4968.0</v>
+        <v>1268.0</v>
       </c>
       <c r="G26" t="n">
-        <v>38.0</v>
+        <v>4.0</v>
       </c>
       <c r="H26" t="n">
-        <v>213.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -893,22 +893,22 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>515.0</v>
+        <v>655.0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>41.0</v>
+        <v>249.0</v>
       </c>
     </row>
     <row r="28">
@@ -919,22 +919,22 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s">
         <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>5745.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>310.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="29">
@@ -945,22 +945,22 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E29" t="s">
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>11026.0</v>
+        <v>3338.0</v>
       </c>
       <c r="G29" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
       <c r="H29" t="n">
-        <v>718.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -971,22 +971,22 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>5015.0</v>
+        <v>19.0</v>
       </c>
       <c r="G30" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -994,22 +994,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>1268.0</v>
+        <v>554.0</v>
       </c>
       <c r="G31" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1020,25 +1020,25 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
         <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>169.0</v>
+        <v>272.0</v>
       </c>
       <c r="G32" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -1046,19 +1046,19 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
         <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1072,25 +1072,25 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>655.0</v>
+        <v>119.0</v>
       </c>
       <c r="G34" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H34" t="n">
-        <v>249.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -1098,25 +1098,25 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
         <v>48</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0</v>
+        <v>1011.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H35" t="n">
-        <v>216.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -1124,22 +1124,22 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>3338.0</v>
+        <v>1.0</v>
       </c>
       <c r="G36" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1150,19 +1150,19 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E37" t="s">
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>19.0</v>
+        <v>107.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1179,16 +1179,16 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
         <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>554.0</v>
+        <v>50.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1205,22 +1205,22 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E39" t="s">
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>513.0</v>
+        <v>637.0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="40">
@@ -1231,22 +1231,22 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E40" t="s">
         <v>48</v>
       </c>
       <c r="F40" t="n">
-        <v>19.0</v>
+        <v>1169.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="41">
@@ -1257,16 +1257,16 @@
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E41" t="s">
         <v>48</v>
       </c>
       <c r="F41" t="n">
-        <v>3.0</v>
+        <v>737.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1283,22 +1283,22 @@
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>774.0</v>
+        <v>582.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="43">
@@ -1309,19 +1309,19 @@
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>1011.0</v>
+        <v>714.0</v>
       </c>
       <c r="G43" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1335,7 +1335,7 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D44" t="s">
         <v>41</v>
@@ -1361,19 +1361,19 @@
         <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>107.0</v>
+        <v>2010.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1387,22 +1387,22 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
         <v>48</v>
       </c>
       <c r="F46" t="n">
+        <v>2779.0</v>
+      </c>
+      <c r="G46" t="n">
         <v>8.0</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H46" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="47">
@@ -1413,16 +1413,16 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
         <v>48</v>
       </c>
       <c r="F47" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1439,19 +1439,19 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>576.0</v>
+        <v>1464.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1465,16 +1465,16 @@
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>34.0</v>
+        <v>761.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1491,19 +1491,19 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>696.0</v>
+        <v>1.0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1517,19 +1517,19 @@
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
         <v>48</v>
       </c>
       <c r="F51" t="n">
+        <v>1206.0</v>
+      </c>
+      <c r="G51" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1540,22 +1540,22 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>2010.0</v>
+        <v>2.0</v>
       </c>
       <c r="G52" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1566,22 +1566,22 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>2026.0</v>
+        <v>41.0</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1592,19 +1592,19 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1.0</v>
+        <v>2138.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1618,22 +1618,22 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1312.0</v>
+        <v>1036.0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1644,19 +1644,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>761.0</v>
+        <v>36.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1670,19 +1670,19 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1696,22 +1696,22 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F58" t="n">
-        <v>1206.0</v>
+        <v>493.0</v>
       </c>
       <c r="G58" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1725,22 +1725,22 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>51.0</v>
+        <v>2026.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0</v>
+        <v>12782.0</v>
       </c>
     </row>
     <row r="60">
@@ -1751,16 +1751,16 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E60" t="s">
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>2499.0</v>
+        <v>182.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1777,16 +1777,16 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E61" t="s">
         <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>1070.0</v>
+        <v>109.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1803,19 +1803,19 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E62" t="s">
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>42.0</v>
+        <v>311.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1829,16 +1829,16 @@
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
         <v>49</v>
       </c>
       <c r="F63" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1855,22 +1855,22 @@
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>5054.0</v>
+        <v>18.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H64" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1878,19 +1878,19 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E65" t="s">
         <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>788.0</v>
+        <v>42.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1904,25 +1904,25 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>1007.0</v>
+        <v>2111.0</v>
       </c>
       <c r="G66" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1930,25 +1930,25 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>54.0</v>
+        <v>3270.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="68">
@@ -1956,19 +1956,19 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
         <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>108.0</v>
+        <v>43.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -1982,22 +1982,22 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E69" t="s">
         <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>311.0</v>
+        <v>31.0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -2008,25 +2008,25 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E70" t="s">
         <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>204.0</v>
+        <v>24.0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H70" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -2034,19 +2034,19 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
         <v>49</v>
       </c>
       <c r="F71" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2060,22 +2060,22 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
         <v>49</v>
       </c>
       <c r="F72" t="n">
-        <v>18.0</v>
+        <v>5.0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2089,22 +2089,22 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E73" t="s">
         <v>49</v>
       </c>
       <c r="F73" t="n">
-        <v>5.0</v>
+        <v>74.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="74">
@@ -2115,19 +2115,19 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>4.0</v>
+        <v>1055.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2141,19 +2141,19 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s">
         <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>1703.0</v>
+        <v>16.0</v>
       </c>
       <c r="G75" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2167,22 +2167,22 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E76" t="s">
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>3006.0</v>
+        <v>8.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2193,16 +2193,16 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E77" t="s">
         <v>49</v>
       </c>
       <c r="F77" t="n">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2216,19 +2216,19 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E78" t="s">
         <v>49</v>
       </c>
       <c r="F78" t="n">
-        <v>31.0</v>
+        <v>3.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2242,22 +2242,22 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E79" t="s">
         <v>49</v>
       </c>
       <c r="F79" t="n">
-        <v>24.0</v>
+        <v>245.0</v>
       </c>
       <c r="G79" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2268,19 +2268,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E80" t="s">
         <v>49</v>
       </c>
       <c r="F80" t="n">
-        <v>27.0</v>
+        <v>497.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2294,19 +2294,19 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E81" t="s">
         <v>49</v>
       </c>
       <c r="F81" t="n">
-        <v>7.0</v>
+        <v>254.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2320,25 +2320,25 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
         <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>338.0</v>
+        <v>276.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
       </c>
       <c r="H82" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -2346,25 +2346,25 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
         <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>4939.0</v>
+        <v>14.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
       </c>
       <c r="H83" t="n">
-        <v>12928.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -2372,25 +2372,25 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E84" t="s">
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>1282.0</v>
+        <v>3952.0</v>
       </c>
       <c r="G84" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H84" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -2398,25 +2398,25 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
         <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>16.0</v>
+        <v>7359.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="86">
@@ -2424,25 +2424,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E86" t="s">
         <v>49</v>
       </c>
       <c r="F86" t="n">
-        <v>29.0</v>
+        <v>1203.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>47.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="87">
@@ -2450,25 +2450,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E87" t="s">
         <v>49</v>
       </c>
       <c r="F87" t="n">
-        <v>8.0</v>
+        <v>3846.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="88">
@@ -2476,10 +2476,10 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
         <v>40</v>
@@ -2488,7 +2488,7 @@
         <v>49</v>
       </c>
       <c r="F88" t="n">
-        <v>17.0</v>
+        <v>73.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2505,22 +2505,22 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E89" t="s">
         <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>245.0</v>
+        <v>100.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="90">
@@ -2531,16 +2531,16 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E90" t="s">
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>525.0</v>
+        <v>133.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2557,19 +2557,19 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>291.0</v>
+        <v>12170.0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H91" t="n">
         <v>0.0</v>
@@ -2583,22 +2583,22 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E92" t="s">
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>226.0</v>
+        <v>527.0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="93">
@@ -2609,16 +2609,16 @@
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E93" t="s">
         <v>49</v>
       </c>
       <c r="F93" t="n">
-        <v>312.0</v>
+        <v>4.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2635,22 +2635,22 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E94" t="s">
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>14.0</v>
+        <v>1047.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="95">
@@ -2661,16 +2661,16 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E95" t="s">
         <v>49</v>
       </c>
       <c r="F95" t="n">
-        <v>3952.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2687,19 +2687,19 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E96" t="s">
         <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>2796.0</v>
+        <v>18.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2713,281 +2713,21 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E97" t="s">
         <v>49</v>
       </c>
       <c r="F97" t="n">
-        <v>77.0</v>
+        <v>40.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>8</v>
-      </c>
-      <c r="B98" t="s">
-        <v>11</v>
-      </c>
-      <c r="C98" t="s">
-        <v>14</v>
-      </c>
-      <c r="D98" t="s">
-        <v>28</v>
-      </c>
-      <c r="E98" t="s">
-        <v>49</v>
-      </c>
-      <c r="F98" t="n">
-        <v>73.0</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>8</v>
-      </c>
-      <c r="B99" t="s">
-        <v>11</v>
-      </c>
-      <c r="C99" t="s">
-        <v>15</v>
-      </c>
-      <c r="D99" t="s">
-        <v>29</v>
-      </c>
-      <c r="E99" t="s">
-        <v>49</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>8</v>
-      </c>
-      <c r="B100" t="s">
-        <v>11</v>
-      </c>
-      <c r="C100" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100" t="s">
-        <v>30</v>
-      </c>
-      <c r="E100" t="s">
-        <v>49</v>
-      </c>
-      <c r="F100" t="n">
-        <v>133.0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>8</v>
-      </c>
-      <c r="B101" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101" t="s">
-        <v>15</v>
-      </c>
-      <c r="D101" t="s">
-        <v>31</v>
-      </c>
-      <c r="E101" t="s">
-        <v>49</v>
-      </c>
-      <c r="F101" t="n">
-        <v>12140.0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>8</v>
-      </c>
-      <c r="B102" t="s">
-        <v>11</v>
-      </c>
-      <c r="C102" t="s">
-        <v>15</v>
-      </c>
-      <c r="D102" t="s">
-        <v>32</v>
-      </c>
-      <c r="E102" t="s">
-        <v>49</v>
-      </c>
-      <c r="F102" t="n">
-        <v>293.0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>8</v>
-      </c>
-      <c r="B103" t="s">
-        <v>11</v>
-      </c>
-      <c r="C103" t="s">
-        <v>15</v>
-      </c>
-      <c r="D103" t="s">
-        <v>44</v>
-      </c>
-      <c r="E103" t="s">
-        <v>49</v>
-      </c>
-      <c r="F103" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>8</v>
-      </c>
-      <c r="B104" t="s">
-        <v>11</v>
-      </c>
-      <c r="C104" t="s">
-        <v>15</v>
-      </c>
-      <c r="D104" t="s">
-        <v>33</v>
-      </c>
-      <c r="E104" t="s">
-        <v>49</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1047.0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>8</v>
-      </c>
-      <c r="B105" t="s">
-        <v>11</v>
-      </c>
-      <c r="C105" t="s">
-        <v>18</v>
-      </c>
-      <c r="D105" t="s">
-        <v>47</v>
-      </c>
-      <c r="E105" t="s">
-        <v>49</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>8</v>
-      </c>
-      <c r="B106" t="s">
-        <v>11</v>
-      </c>
-      <c r="C106" t="s">
-        <v>16</v>
-      </c>
-      <c r="D106" t="s">
-        <v>34</v>
-      </c>
-      <c r="E106" t="s">
-        <v>49</v>
-      </c>
-      <c r="F106" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>8</v>
-      </c>
-      <c r="B107" t="s">
-        <v>11</v>
-      </c>
-      <c r="C107" t="s">
-        <v>16</v>
-      </c>
-      <c r="D107" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" t="s">
-        <v>49</v>
-      </c>
-      <c r="F107" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H107" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -434,7 +434,7 @@
         <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>1090.0</v>
+        <v>1099.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>922.0</v>
+        <v>923.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -590,10 +590,10 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H15" t="n">
         <v>2.0</v>
@@ -616,7 +616,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>2946.0</v>
+        <v>2950.0</v>
       </c>
       <c r="G16" t="n">
         <v>66.0</v>
@@ -772,7 +772,7 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4970.0</v>
+        <v>4973.0</v>
       </c>
       <c r="G22" t="n">
         <v>39.0</v>
@@ -798,7 +798,7 @@
         <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>3552.0</v>
+        <v>3556.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -1162,7 +1162,7 @@
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>107.0</v>
+        <v>111.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1240,7 +1240,7 @@
         <v>48</v>
       </c>
       <c r="F40" t="n">
-        <v>1169.0</v>
+        <v>1177.0</v>
       </c>
       <c r="G40" t="n">
         <v>4.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2779.0</v>
+        <v>2783.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2138.0</v>
+        <v>2143.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1036.0</v>
+        <v>1037.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1708,7 +1708,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="n">
-        <v>493.0</v>
+        <v>495.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>2026.0</v>
+        <v>2034.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2111.0</v>
+        <v>2121.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3270.0</v>
+        <v>3272.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>3952.0</v>
+        <v>3954.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2410,7 +2410,7 @@
         <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>7359.0</v>
+        <v>7384.0</v>
       </c>
       <c r="G85" t="n">
         <v>1.0</v>
@@ -2436,7 +2436,7 @@
         <v>49</v>
       </c>
       <c r="F86" t="n">
-        <v>1203.0</v>
+        <v>1205.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2462,7 +2462,7 @@
         <v>49</v>
       </c>
       <c r="F87" t="n">
-        <v>3846.0</v>
+        <v>3864.0</v>
       </c>
       <c r="G87" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>923.0</v>
+        <v>928.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>3299.0</v>
+        <v>3304.0</v>
       </c>
       <c r="G12" t="n">
         <v>4.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>313.0</v>
+        <v>315.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5018.0</v>
+        <v>5045.0</v>
       </c>
       <c r="G25" t="n">
         <v>6.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1268.0</v>
+        <v>1271.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -902,13 +902,13 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>655.0</v>
+        <v>662.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>249.0</v>
+        <v>255.0</v>
       </c>
     </row>
     <row r="28">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>216.0</v>
+        <v>223.0</v>
       </c>
     </row>
     <row r="29">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3338.0</v>
+        <v>3346.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>714.0</v>
+        <v>715.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2010.0</v>
+        <v>2013.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>1464.0</v>
+        <v>1473.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>761.0</v>
+        <v>762.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1206.0</v>
+        <v>1209.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12170.0</v>
+        <v>12188.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>1047.0</v>
+        <v>1049.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>
@@ -2696,7 +2696,7 @@
         <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -460,7 +460,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>1134.0</v>
+        <v>1136.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -648,7 +648,7 @@
         <v>42.0</v>
       </c>
       <c r="H17" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="18">
@@ -726,7 +726,7 @@
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>970.0</v>
+        <v>974.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3049.0</v>
+        <v>3064.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>9736.0</v>
+        <v>9744.0</v>
       </c>
       <c r="G24" t="n">
         <v>20.0</v>
@@ -850,10 +850,10 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5045.0</v>
+        <v>5048.0</v>
       </c>
       <c r="G25" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" t="n">
         <v>21.0</v>
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3346.0</v>
+        <v>3347.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>715.0</v>
+        <v>718.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2013.0</v>
+        <v>2014.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2783.0</v>
+        <v>2785.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>1473.0</v>
+        <v>1476.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>762.0</v>
+        <v>763.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1209.0</v>
+        <v>1212.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2143.0</v>
+        <v>2149.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1037.0</v>
+        <v>1043.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1838,7 +1838,7 @@
         <v>49</v>
       </c>
       <c r="F63" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2121.0</v>
+        <v>2128.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3272.0</v>
+        <v>3294.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1968,7 +1968,7 @@
         <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -1994,7 +1994,7 @@
         <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2124,7 +2124,7 @@
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1055.0</v>
+        <v>1056.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2540,7 +2540,7 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12188.0</v>
+        <v>12203.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>928.0</v>
+        <v>929.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -720,13 +720,13 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>10544.0</v>
+        <v>10550.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>974.0</v>
+        <v>977.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3064.0</v>
+        <v>3067.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -772,7 +772,7 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4973.0</v>
+        <v>4975.0</v>
       </c>
       <c r="G22" t="n">
         <v>39.0</v>
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>662.0</v>
+        <v>664.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1032,7 +1032,7 @@
         <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1084,7 +1084,7 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2014.0</v>
+        <v>2015.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2785.0</v>
+        <v>2801.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12203.0</v>
+        <v>12220.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>529.0</v>
+        <v>530.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -622,7 +622,7 @@
         <v>66.0</v>
       </c>
       <c r="H16" t="n">
-        <v>352.0</v>
+        <v>354.0</v>
       </c>
     </row>
     <row r="17">
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>664.0</v>
+        <v>665.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1212.0</v>
+        <v>1213.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -408,7 +408,7 @@
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
@@ -434,7 +434,7 @@
         <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>1099.0</v>
+        <v>1101.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -460,7 +460,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>1136.0</v>
+        <v>1140.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>3304.0</v>
+        <v>3307.0</v>
       </c>
       <c r="G12" t="n">
         <v>4.0</v>
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3067.0</v>
+        <v>3081.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -798,7 +798,7 @@
         <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>3556.0</v>
+        <v>3570.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5048.0</v>
+        <v>5054.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1271.0</v>
+        <v>1273.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -1162,7 +1162,7 @@
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>582.0</v>
+        <v>583.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>718.0</v>
+        <v>721.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2015.0</v>
+        <v>2017.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2801.0</v>
+        <v>2803.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>1476.0</v>
+        <v>1483.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1812,7 +1812,7 @@
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G62" t="n">
         <v>1.0</v>
@@ -2124,7 +2124,7 @@
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1056.0</v>
+        <v>1058.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2514,7 +2514,7 @@
         <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G89" t="n">
         <v>1.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12220.0</v>
+        <v>12249.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>530.0</v>
+        <v>531.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>1049.0</v>
+        <v>1053.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -252,7 +252,7 @@
         <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>31.0</v>
+        <v>44.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -330,7 +330,7 @@
         <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>298.0</v>
+        <v>302.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -356,7 +356,7 @@
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>655.0</v>
+        <v>664.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>929.0</v>
+        <v>931.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -593,7 +593,7 @@
         <v>295.0</v>
       </c>
       <c r="G15" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" t="n">
         <v>2.0</v>
@@ -616,13 +616,13 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>2950.0</v>
+        <v>2964.0</v>
       </c>
       <c r="G16" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="H16" t="n">
-        <v>354.0</v>
+        <v>355.0</v>
       </c>
     </row>
     <row r="17">
@@ -642,7 +642,7 @@
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>1681.0</v>
+        <v>1686.0</v>
       </c>
       <c r="G17" t="n">
         <v>42.0</v>
@@ -694,7 +694,7 @@
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>561.0</v>
+        <v>567.0</v>
       </c>
       <c r="G19" t="n">
         <v>7.0</v>
@@ -746,13 +746,13 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3081.0</v>
+        <v>3086.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>58.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="22">
@@ -772,13 +772,13 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4975.0</v>
+        <v>4980.0</v>
       </c>
       <c r="G22" t="n">
         <v>39.0</v>
       </c>
       <c r="H22" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="23">
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5054.0</v>
+        <v>5055.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -908,7 +908,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>255.0</v>
+        <v>258.0</v>
       </c>
     </row>
     <row r="28">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>223.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="29">
@@ -1006,7 +1006,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>554.0</v>
+        <v>561.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1032,7 +1032,7 @@
         <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>273.0</v>
+        <v>276.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>721.0</v>
+        <v>731.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>41.0</v>
+        <v>47.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2149.0</v>
+        <v>2164.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1043.0</v>
+        <v>1047.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1656,7 +1656,7 @@
         <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>36.0</v>
+        <v>41.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2128.0</v>
+        <v>2141.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3294.0</v>
+        <v>3300.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12249.0</v>
+        <v>12250.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -252,7 +252,7 @@
         <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -278,7 +278,7 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>353.0</v>
+        <v>358.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -304,7 +304,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>723.0</v>
+        <v>727.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>
@@ -356,7 +356,7 @@
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>664.0</v>
+        <v>666.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -434,7 +434,7 @@
         <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>1101.0</v>
+        <v>1103.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -460,7 +460,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>1140.0</v>
+        <v>1144.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>931.0</v>
+        <v>944.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -512,10 +512,10 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>3307.0</v>
+        <v>3318.0</v>
       </c>
       <c r="G12" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -590,7 +590,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>295.0</v>
+        <v>298.0</v>
       </c>
       <c r="G15" t="n">
         <v>10.0</v>
@@ -616,13 +616,13 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>2964.0</v>
+        <v>2993.0</v>
       </c>
       <c r="G16" t="n">
-        <v>68.0</v>
+        <v>74.0</v>
       </c>
       <c r="H16" t="n">
-        <v>355.0</v>
+        <v>361.0</v>
       </c>
     </row>
     <row r="17">
@@ -642,13 +642,13 @@
         <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>1686.0</v>
+        <v>1688.0</v>
       </c>
       <c r="G17" t="n">
         <v>42.0</v>
       </c>
       <c r="H17" t="n">
-        <v>226.0</v>
+        <v>228.0</v>
       </c>
     </row>
     <row r="18">
@@ -694,7 +694,7 @@
         <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>567.0</v>
+        <v>568.0</v>
       </c>
       <c r="G19" t="n">
         <v>7.0</v>
@@ -720,13 +720,13 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>10550.0</v>
+        <v>10562.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>977.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,13 +746,13 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3086.0</v>
+        <v>3110.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="22">
@@ -772,13 +772,13 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4980.0</v>
+        <v>4991.0</v>
       </c>
       <c r="G22" t="n">
         <v>39.0</v>
       </c>
       <c r="H22" t="n">
-        <v>216.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="23">
@@ -798,7 +798,7 @@
         <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>3570.0</v>
+        <v>3581.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -824,10 +824,10 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>9744.0</v>
+        <v>9752.0</v>
       </c>
       <c r="G24" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="H24" t="n">
         <v>715.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5055.0</v>
+        <v>5072.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1273.0</v>
+        <v>1284.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -902,13 +902,13 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>665.0</v>
+        <v>668.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>258.0</v>
+        <v>268.0</v>
       </c>
     </row>
     <row r="28">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>226.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="29">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3347.0</v>
+        <v>3352.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1006,7 +1006,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>561.0</v>
+        <v>576.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1032,7 +1032,7 @@
         <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>276.0</v>
+        <v>288.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1058,7 +1058,7 @@
         <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1084,7 +1084,7 @@
         <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1162,7 +1162,7 @@
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1214,7 +1214,7 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>637.0</v>
+        <v>639.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -1240,7 +1240,7 @@
         <v>48</v>
       </c>
       <c r="F40" t="n">
-        <v>1177.0</v>
+        <v>1184.0</v>
       </c>
       <c r="G40" t="n">
         <v>4.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>583.0</v>
+        <v>586.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>731.0</v>
+        <v>734.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2017.0</v>
+        <v>2026.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2803.0</v>
+        <v>2808.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>1483.0</v>
+        <v>1493.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>763.0</v>
+        <v>770.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1213.0</v>
+        <v>1221.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>47.0</v>
+        <v>61.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2164.0</v>
+        <v>2183.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1047.0</v>
+        <v>1063.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1708,7 +1708,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="n">
-        <v>495.0</v>
+        <v>502.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>2034.0</v>
+        <v>2054.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1812,7 +1812,7 @@
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="G62" t="n">
         <v>1.0</v>
@@ -1864,7 +1864,7 @@
         <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2141.0</v>
+        <v>2161.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3300.0</v>
+        <v>3332.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2124,7 +2124,7 @@
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1058.0</v>
+        <v>1060.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2280,7 +2280,7 @@
         <v>49</v>
       </c>
       <c r="F80" t="n">
-        <v>497.0</v>
+        <v>500.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2306,7 +2306,7 @@
         <v>49</v>
       </c>
       <c r="F81" t="n">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2358,7 +2358,7 @@
         <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>3954.0</v>
+        <v>3960.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2410,7 +2410,7 @@
         <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>7384.0</v>
+        <v>7389.0</v>
       </c>
       <c r="G85" t="n">
         <v>1.0</v>
@@ -2436,7 +2436,7 @@
         <v>49</v>
       </c>
       <c r="F86" t="n">
-        <v>1205.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2540,7 +2540,7 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12250.0</v>
+        <v>12317.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>531.0</v>
+        <v>537.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>1053.0</v>
+        <v>1058.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>
@@ -2696,7 +2696,7 @@
         <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2722,7 +2722,7 @@
         <v>49</v>
       </c>
       <c r="F97" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>9752.0</v>
+        <v>9759.0</v>
       </c>
       <c r="G24" t="n">
         <v>21.0</v>
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>668.0</v>
+        <v>671.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -980,7 +980,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2026.0</v>
+        <v>2027.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>770.0</v>
+        <v>771.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1812,7 +1812,7 @@
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>313.0</v>
+        <v>314.0</v>
       </c>
       <c r="G62" t="n">
         <v>1.0</v>
@@ -2176,7 +2176,7 @@
         <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12317.0</v>
+        <v>12336.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>3318.0</v>
+        <v>3320.0</v>
       </c>
       <c r="G12" t="n">
         <v>5.0</v>
@@ -619,7 +619,7 @@
         <v>2993.0</v>
       </c>
       <c r="G16" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="H16" t="n">
         <v>361.0</v>
@@ -720,7 +720,7 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>10562.0</v>
+        <v>10573.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3110.0</v>
+        <v>3113.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -772,7 +772,7 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4991.0</v>
+        <v>4993.0</v>
       </c>
       <c r="G22" t="n">
         <v>39.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1284.0</v>
+        <v>1286.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -902,13 +902,13 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>671.0</v>
+        <v>676.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>268.0</v>
+        <v>274.0</v>
       </c>
     </row>
     <row r="28">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>229.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="29">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3352.0</v>
+        <v>3354.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>734.0</v>
+        <v>735.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2808.0</v>
+        <v>2810.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>1493.0</v>
+        <v>1504.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>61.0</v>
+        <v>67.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2183.0</v>
+        <v>2193.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1063.0</v>
+        <v>1066.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1656,7 +1656,7 @@
         <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1890,7 +1890,7 @@
         <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2161.0</v>
+        <v>2167.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3332.0</v>
+        <v>3343.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1968,7 +1968,7 @@
         <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2130,7 +2130,7 @@
         <v>1.0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="75">
@@ -2254,7 +2254,7 @@
         <v>49</v>
       </c>
       <c r="F79" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2280,7 +2280,7 @@
         <v>49</v>
       </c>
       <c r="F80" t="n">
-        <v>500.0</v>
+        <v>502.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2540,7 +2540,7 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12336.0</v>
+        <v>12349.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>537.0</v>
+        <v>538.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -278,7 +278,7 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>358.0</v>
+        <v>367.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -564,7 +564,7 @@
         <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>676.0</v>
+        <v>678.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1032,7 +1032,7 @@
         <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>288.0</v>
+        <v>297.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1221.0</v>
+        <v>1223.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2193.0</v>
+        <v>2195.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -460,7 +460,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>1144.0</v>
+        <v>1152.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>944.0</v>
+        <v>949.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3113.0</v>
+        <v>3116.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -772,13 +772,13 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4993.0</v>
+        <v>4999.0</v>
       </c>
       <c r="G22" t="n">
-        <v>39.0</v>
+        <v>34.0</v>
       </c>
       <c r="H22" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
     </row>
     <row r="23">
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>9759.0</v>
+        <v>9769.0</v>
       </c>
       <c r="G24" t="n">
         <v>21.0</v>
@@ -850,13 +850,13 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5072.0</v>
+        <v>5081.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
       </c>
       <c r="H25" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1286.0</v>
+        <v>1287.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>587.0</v>
+        <v>593.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2027.0</v>
+        <v>2033.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1448,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>1504.0</v>
+        <v>1513.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1066.0</v>
+        <v>1067.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1656,7 +1656,7 @@
         <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1708,7 +1708,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="n">
-        <v>502.0</v>
+        <v>504.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>2054.0</v>
+        <v>2066.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1760,7 +1760,7 @@
         <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2167.0</v>
+        <v>2169.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3343.0</v>
+        <v>3346.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2124,7 +2124,7 @@
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1060.0</v>
+        <v>1061.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>3960.0</v>
+        <v>3962.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2410,7 +2410,7 @@
         <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>7389.0</v>
+        <v>7390.0</v>
       </c>
       <c r="G85" t="n">
         <v>1.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12349.0</v>
+        <v>12375.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>1058.0</v>
+        <v>1062.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -434,7 +434,7 @@
         <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>1103.0</v>
+        <v>1109.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>949.0</v>
+        <v>951.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -616,7 +616,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>2993.0</v>
+        <v>2994.0</v>
       </c>
       <c r="G16" t="n">
         <v>75.0</v>
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3116.0</v>
+        <v>3117.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -772,7 +772,7 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>4999.0</v>
+        <v>5002.0</v>
       </c>
       <c r="G22" t="n">
         <v>34.0</v>
@@ -798,7 +798,7 @@
         <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>3581.0</v>
+        <v>3582.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>9769.0</v>
+        <v>9770.0</v>
       </c>
       <c r="G24" t="n">
         <v>21.0</v>
@@ -850,10 +850,10 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5081.0</v>
+        <v>5085.0</v>
       </c>
       <c r="G25" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="H25" t="n">
         <v>22.0</v>
@@ -879,7 +879,7 @@
         <v>1287.0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -1162,7 +1162,7 @@
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1188,7 +1188,7 @@
         <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1214,7 +1214,7 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>639.0</v>
+        <v>646.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -1266,7 +1266,7 @@
         <v>48</v>
       </c>
       <c r="F41" t="n">
-        <v>737.0</v>
+        <v>738.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>593.0</v>
+        <v>596.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>735.0</v>
+        <v>738.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1396,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>2810.0</v>
+        <v>2811.0</v>
       </c>
       <c r="G46" t="n">
         <v>8.0</v>
@@ -2130,7 +2130,7 @@
         <v>1.0</v>
       </c>
       <c r="H74" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>951.0</v>
+        <v>962.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -512,10 +512,10 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>3320.0</v>
+        <v>3321.0</v>
       </c>
       <c r="G12" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -720,7 +720,7 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>10573.0</v>
+        <v>10576.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3117.0</v>
+        <v>3121.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -772,7 +772,7 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>5002.0</v>
+        <v>5005.0</v>
       </c>
       <c r="G22" t="n">
         <v>34.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5085.0</v>
+        <v>5087.0</v>
       </c>
       <c r="G25" t="n">
         <v>9.0</v>
@@ -876,7 +876,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1287.0</v>
+        <v>1288.0</v>
       </c>
       <c r="G26" t="n">
         <v>6.0</v>
@@ -902,13 +902,13 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>678.0</v>
+        <v>681.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>274.0</v>
+        <v>287.0</v>
       </c>
     </row>
     <row r="28">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>231.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="29">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3354.0</v>
+        <v>3356.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>738.0</v>
+        <v>739.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2033.0</v>
+        <v>2037.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>771.0</v>
+        <v>773.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1812,7 +1812,7 @@
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
       <c r="G62" t="n">
         <v>1.0</v>
@@ -2124,7 +2124,7 @@
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1061.0</v>
+        <v>1062.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12375.0</v>
+        <v>12389.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -460,7 +460,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>1152.0</v>
+        <v>1157.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -720,13 +720,13 @@
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>10576.0</v>
+        <v>10581.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>980.0</v>
+        <v>981.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +746,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>3121.0</v>
+        <v>3124.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -772,7 +772,7 @@
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>5005.0</v>
+        <v>5007.0</v>
       </c>
       <c r="G22" t="n">
         <v>34.0</v>
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>9770.0</v>
+        <v>9781.0</v>
       </c>
       <c r="G24" t="n">
         <v>21.0</v>
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5087.0</v>
+        <v>5088.0</v>
       </c>
       <c r="G25" t="n">
         <v>9.0</v>
@@ -876,10 +876,10 @@
         <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>1288.0</v>
+        <v>1292.0</v>
       </c>
       <c r="G26" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>234.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="29">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3356.0</v>
+        <v>3360.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1292,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>596.0</v>
+        <v>598.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1318,7 +1318,7 @@
         <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>739.0</v>
+        <v>743.0</v>
       </c>
       <c r="G43" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2037.0</v>
+        <v>2039.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>773.0</v>
+        <v>774.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1223.0</v>
+        <v>1224.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -2124,7 +2124,7 @@
         <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>1062.0</v>
+        <v>1063.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12389.0</v>
+        <v>12407.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>538.0</v>
+        <v>541.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>1062.0</v>
+        <v>1065.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -486,7 +486,7 @@
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>962.0</v>
+        <v>963.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>3321.0</v>
+        <v>3325.0</v>
       </c>
       <c r="G12" t="n">
         <v>4.0</v>
@@ -590,10 +590,10 @@
         <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>298.0</v>
+        <v>299.0</v>
       </c>
       <c r="G15" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="H15" t="n">
         <v>2.0</v>
@@ -616,10 +616,10 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>2994.0</v>
+        <v>2995.0</v>
       </c>
       <c r="G16" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="H16" t="n">
         <v>361.0</v>
@@ -645,7 +645,7 @@
         <v>1688.0</v>
       </c>
       <c r="G17" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="H17" t="n">
         <v>228.0</v>
@@ -697,7 +697,7 @@
         <v>568.0</v>
       </c>
       <c r="G19" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -778,7 +778,7 @@
         <v>34.0</v>
       </c>
       <c r="H22" t="n">
-        <v>221.0</v>
+        <v>224.0</v>
       </c>
     </row>
     <row r="23">
@@ -850,7 +850,7 @@
         <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>5088.0</v>
+        <v>5091.0</v>
       </c>
       <c r="G25" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>681.0</v>
+        <v>684.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1370,7 +1370,7 @@
         <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>2039.0</v>
+        <v>2040.0</v>
       </c>
       <c r="G45" t="n">
         <v>10.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>774.0</v>
+        <v>775.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1224.0</v>
+        <v>1226.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2195.0</v>
+        <v>2216.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1630,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1067.0</v>
+        <v>1073.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1656,7 +1656,7 @@
         <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>49.0</v>
+        <v>57.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1890,7 +1890,7 @@
         <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1916,7 +1916,7 @@
         <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>2169.0</v>
+        <v>2183.0</v>
       </c>
       <c r="G66" t="n">
         <v>2.0</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>3346.0</v>
+        <v>3368.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1968,7 +1968,7 @@
         <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2566,7 +2566,7 @@
         <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>12407.0</v>
+        <v>12419.0</v>
       </c>
       <c r="G91" t="n">
         <v>14.0</v>
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>541.0</v>
+        <v>543.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>1065.0</v>
+        <v>1066.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -538,7 +538,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>316.0</v>
+        <v>319.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -902,13 +902,13 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>684.0</v>
+        <v>686.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>287.0</v>
+        <v>291.0</v>
       </c>
     </row>
     <row r="28">
@@ -954,7 +954,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>3360.0</v>
+        <v>3364.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="F49" t="n">
-        <v>775.0</v>
+        <v>776.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1526,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="n">
-        <v>1226.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="51">
   <si>
     <t>Area</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
   </si>
   <si>
     <t>LIM</t>
@@ -243,13 +246,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>46.0</v>
@@ -269,13 +272,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>367.0</v>
@@ -295,13 +298,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
         <v>727.0</v>
@@ -321,22 +324,22 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>302.0</v>
+        <v>293.0</v>
       </c>
       <c r="G5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -347,13 +350,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>666.0</v>
@@ -373,13 +376,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>2179.0</v>
@@ -399,13 +402,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>26.0</v>
@@ -425,13 +428,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
         <v>1109.0</v>
@@ -451,16 +454,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1157.0</v>
+        <v>1161.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -477,16 +480,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>963.0</v>
+        <v>966.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -503,16 +506,16 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3325.0</v>
+        <v>3326.0</v>
       </c>
       <c r="G12" t="n">
         <v>4.0</v>
@@ -529,13 +532,13 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
         <v>319.0</v>
@@ -555,13 +558,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
         <v>129.0</v>
@@ -581,13 +584,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
         <v>299.0</v>
@@ -607,13 +610,13 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
         <v>2995.0</v>
@@ -622,7 +625,7 @@
         <v>76.0</v>
       </c>
       <c r="H16" t="n">
-        <v>361.0</v>
+        <v>362.0</v>
       </c>
     </row>
     <row r="17">
@@ -633,22 +636,22 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1688.0</v>
+        <v>1697.0</v>
       </c>
       <c r="G17" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="H17" t="n">
-        <v>228.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="18">
@@ -659,13 +662,13 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
         <v>0.0</v>
@@ -685,13 +688,13 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
         <v>568.0</v>
@@ -711,16 +714,16 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10581.0</v>
+        <v>10587.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -737,16 +740,16 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3124.0</v>
+        <v>3126.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -763,22 +766,22 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5007.0</v>
+        <v>4991.0</v>
       </c>
       <c r="G22" t="n">
         <v>34.0</v>
       </c>
       <c r="H22" t="n">
-        <v>224.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="23">
@@ -789,13 +792,13 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
         <v>3582.0</v>
@@ -815,22 +818,22 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>9781.0</v>
+        <v>7444.0</v>
       </c>
       <c r="G24" t="n">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" t="n">
-        <v>715.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="25">
@@ -841,22 +844,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>5091.0</v>
+        <v>3377.0</v>
       </c>
       <c r="G25" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="H25" t="n">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="26">
@@ -867,19 +870,19 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>1292.0</v>
+        <v>690.0</v>
       </c>
       <c r="G26" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -893,13 +896,13 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
         <v>686.0</v>
@@ -919,13 +922,13 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -945,13 +948,13 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
         <v>3364.0</v>
@@ -971,13 +974,13 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
         <v>20.0</v>
@@ -997,22 +1000,22 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>576.0</v>
+        <v>16.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="32">
@@ -1023,22 +1026,22 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>297.0</v>
+        <v>2343.0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="33">
@@ -1049,22 +1052,22 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>17.0</v>
+        <v>1715.0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="34">
@@ -1075,19 +1078,19 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>121.0</v>
+        <v>604.0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1098,22 +1101,22 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>1011.0</v>
+        <v>576.0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1124,19 +1127,19 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0</v>
+        <v>297.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1150,19 +1153,19 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>114.0</v>
+        <v>17.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1176,19 +1179,19 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>51.0</v>
+        <v>121.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1202,25 +1205,25 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>646.0</v>
+        <v>1012.0</v>
       </c>
       <c r="G39" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H39" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -1228,25 +1231,25 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>1184.0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>81.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -1254,19 +1257,19 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>738.0</v>
+        <v>114.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1280,25 +1283,25 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>598.0</v>
+        <v>51.0</v>
       </c>
       <c r="G42" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -1306,25 +1309,25 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>743.0</v>
+        <v>646.0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="44">
@@ -1332,25 +1335,25 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0</v>
+        <v>1184.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="45">
@@ -1358,22 +1361,22 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>2040.0</v>
+        <v>738.0</v>
       </c>
       <c r="G45" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1384,25 +1387,25 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>2811.0</v>
+        <v>601.0</v>
       </c>
       <c r="G46" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H46" t="n">
-        <v>64.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="47">
@@ -1410,22 +1413,22 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F47" t="n">
+        <v>744.0</v>
+      </c>
+      <c r="G47" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1436,22 +1439,22 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1513.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1462,7 +1465,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
         <v>16</v>
@@ -1471,13 +1474,13 @@
         <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>776.0</v>
+        <v>2041.0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1488,25 +1491,25 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
         <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>1.0</v>
+        <v>2812.0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="51">
@@ -1514,22 +1517,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>1229.0</v>
+        <v>1.0</v>
       </c>
       <c r="G51" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1540,22 +1543,22 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0</v>
+        <v>1519.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1566,19 +1569,19 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E53" t="s">
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>79.0</v>
+        <v>776.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1592,19 +1595,19 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>2216.0</v>
+        <v>1.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1618,22 +1621,22 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1073.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1647,16 +1650,16 @@
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>57.0</v>
+        <v>79.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1676,13 +1679,13 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>9.0</v>
+        <v>2216.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1699,16 +1702,16 @@
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>504.0</v>
+        <v>498.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1725,22 +1728,22 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>2066.0</v>
+        <v>57.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
       </c>
       <c r="H59" t="n">
-        <v>12782.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1751,16 +1754,16 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>185.0</v>
+        <v>9.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1780,13 +1783,13 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>109.0</v>
+        <v>504.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1806,19 +1809,19 @@
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>315.0</v>
+        <v>2066.0</v>
       </c>
       <c r="G62" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0</v>
+        <v>12782.0</v>
       </c>
     </row>
     <row r="63">
@@ -1832,13 +1835,13 @@
         <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>19.0</v>
+        <v>185.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1858,16 +1861,16 @@
         <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>19.0</v>
+        <v>109.0</v>
       </c>
       <c r="G64" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1878,22 +1881,22 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>46.0</v>
+        <v>316.0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1904,22 +1907,22 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>2183.0</v>
+        <v>19.0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1930,25 +1933,25 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F67" t="n">
-        <v>3368.0</v>
+        <v>19.0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H67" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1959,16 +1962,16 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F68" t="n">
-        <v>46.0</v>
+        <v>2.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -1988,13 +1991,13 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>32.0</v>
+        <v>46.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2014,16 +2017,16 @@
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>24.0</v>
+        <v>2183.0</v>
       </c>
       <c r="G70" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2040,19 +2043,19 @@
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E71" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>27.0</v>
+        <v>3943.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="72">
@@ -2063,16 +2066,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>5.0</v>
+        <v>46.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2092,19 +2095,19 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>74.0</v>
+        <v>32.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2115,19 +2118,19 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>1063.0</v>
+        <v>24.0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2141,16 +2144,16 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>16.0</v>
+        <v>27.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2167,16 +2170,16 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F76" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2193,22 +2196,22 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E77" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F77" t="n">
-        <v>17.0</v>
+        <v>74.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="78">
@@ -2216,22 +2219,22 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>3.0</v>
+        <v>960.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2242,19 +2245,19 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>246.0</v>
+        <v>13.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2268,19 +2271,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>502.0</v>
+        <v>9.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2294,19 +2297,19 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>256.0</v>
+        <v>17.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2323,16 +2326,16 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E82" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>276.0</v>
+        <v>105.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2349,16 +2352,16 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2372,19 +2375,19 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E84" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F84" t="n">
-        <v>3962.0</v>
+        <v>3.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2398,25 +2401,25 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>7390.0</v>
+        <v>246.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -2424,25 +2427,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>1208.0</v>
+        <v>502.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2450,25 +2453,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>3864.0</v>
+        <v>256.0</v>
       </c>
       <c r="G87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -2476,19 +2479,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>73.0</v>
+        <v>276.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2502,25 +2505,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F89" t="n">
-        <v>101.0</v>
+        <v>15.0</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2528,19 +2531,19 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
         <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E90" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>139.0</v>
+        <v>3962.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2554,25 +2557,25 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>12419.0</v>
+        <v>7390.0</v>
       </c>
       <c r="G91" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="92">
@@ -2580,25 +2583,25 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>543.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
-        <v>105.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="93">
@@ -2606,25 +2609,25 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>4.0</v>
+        <v>3864.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="94">
@@ -2632,25 +2635,25 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>1066.0</v>
+        <v>73.0</v>
       </c>
       <c r="G94" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H94" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2658,25 +2661,25 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E95" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F95" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="G95" t="n">
         <v>1.0</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H95" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="96">
@@ -2684,19 +2687,19 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>20.0</v>
+        <v>140.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2710,24 +2713,180 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
       </c>
       <c r="D97" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" t="s">
+        <v>50</v>
+      </c>
+      <c r="F97" t="n">
+        <v>12446.0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" t="s">
+        <v>50</v>
+      </c>
+      <c r="F98" t="n">
+        <v>543.0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" t="s">
+        <v>44</v>
+      </c>
+      <c r="E99" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" t="s">
+        <v>50</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1066.0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" t="s">
+        <v>48</v>
+      </c>
+      <c r="E101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
         <v>31</v>
       </c>
-      <c r="E97" t="s">
-        <v>49</v>
-      </c>
-      <c r="F97" t="n">
+      <c r="E102" t="s">
+        <v>50</v>
+      </c>
+      <c r="F102" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" t="s">
+        <v>50</v>
+      </c>
+      <c r="F103" t="n">
         <v>41.0</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H97" t="n">
+      <c r="G103" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H103" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>367.0</v>
+        <v>368.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>727.0</v>
+        <v>738.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>
@@ -333,10 +333,10 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>293.0</v>
+        <v>299.0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H5" t="n">
         <v>1.0</v>
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>666.0</v>
+        <v>667.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1109.0</v>
+        <v>1116.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>966.0</v>
+        <v>967.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -593,7 +593,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>299.0</v>
+        <v>301.0</v>
       </c>
       <c r="G15" t="n">
         <v>11.0</v>
@@ -619,7 +619,7 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>2995.0</v>
+        <v>3010.0</v>
       </c>
       <c r="G16" t="n">
         <v>76.0</v>
@@ -645,10 +645,10 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1697.0</v>
+        <v>1702.0</v>
       </c>
       <c r="G17" t="n">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="H17" t="n">
         <v>229.0</v>
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>568.0</v>
+        <v>569.0</v>
       </c>
       <c r="G19" t="n">
         <v>8.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10587.0</v>
+        <v>10596.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>981.0</v>
+        <v>983.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3126.0</v>
+        <v>3128.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>4991.0</v>
+        <v>4992.0</v>
       </c>
       <c r="G22" t="n">
         <v>34.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3582.0</v>
+        <v>3586.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3377.0</v>
+        <v>3382.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>291.0</v>
+        <v>294.0</v>
       </c>
     </row>
     <row r="28">
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>576.0</v>
+        <v>601.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>297.0</v>
+        <v>315.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>114.0</v>
+        <v>117.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>646.0</v>
+        <v>654.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2216.0</v>
+        <v>2221.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>504.0</v>
+        <v>509.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2066.0</v>
+        <v>2077.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2183.0</v>
+        <v>2188.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3943.0</v>
+        <v>3947.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>3962.0</v>
+        <v>3965.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>7390.0</v>
+        <v>7395.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>1208.0</v>
+        <v>1209.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2673,7 +2673,7 @@
         <v>50</v>
       </c>
       <c r="F95" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G95" t="n">
         <v>1.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>967.0</v>
+        <v>975.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3326.0</v>
+        <v>3328.0</v>
       </c>
       <c r="G12" t="n">
         <v>4.0</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -619,13 +619,13 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3010.0</v>
+        <v>3013.0</v>
       </c>
       <c r="G16" t="n">
         <v>76.0</v>
       </c>
       <c r="H16" t="n">
-        <v>362.0</v>
+        <v>366.0</v>
       </c>
     </row>
     <row r="17">
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10596.0</v>
+        <v>10600.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>983.0</v>
+        <v>984.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3128.0</v>
+        <v>3130.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -778,7 +778,7 @@
         <v>4992.0</v>
       </c>
       <c r="G22" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="H22" t="n">
         <v>212.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7444.0</v>
+        <v>7445.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3382.0</v>
+        <v>3383.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>690.0</v>
+        <v>694.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -905,7 +905,7 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>686.0</v>
+        <v>688.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1715.0</v>
+        <v>1720.0</v>
       </c>
       <c r="G33" t="n">
         <v>6.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>604.0</v>
+        <v>605.0</v>
       </c>
       <c r="G34" t="n">
         <v>4.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>601.0</v>
+        <v>604.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>601.0</v>
+        <v>603.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>744.0</v>
+        <v>745.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2041.0</v>
+        <v>2046.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>776.0</v>
+        <v>777.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>79.0</v>
+        <v>87.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2221.0</v>
+        <v>2229.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2188.0</v>
+        <v>2195.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3947.0</v>
+        <v>3964.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>960.0</v>
+        <v>961.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2413,7 +2413,7 @@
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>246.0</v>
+        <v>249.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2491,7 +2491,7 @@
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12446.0</v>
+        <v>12467.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>543.0</v>
+        <v>546.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1161.0</v>
+        <v>1163.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>131.0</v>
+        <v>135.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10600.0</v>
+        <v>10602.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3130.0</v>
+        <v>3132.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>4992.0</v>
+        <v>4994.0</v>
       </c>
       <c r="G22" t="n">
         <v>35.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7445.0</v>
+        <v>7447.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3383.0</v>
+        <v>3385.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1720.0</v>
+        <v>1721.0</v>
       </c>
       <c r="G33" t="n">
         <v>6.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>603.0</v>
+        <v>607.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2046.0</v>
+        <v>2047.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1519.0</v>
+        <v>1521.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1229.0</v>
+        <v>1233.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>317.0</v>
+        <v>319.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>961.0</v>
+        <v>963.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12467.0</v>
+        <v>12488.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -625,7 +625,7 @@
         <v>76.0</v>
       </c>
       <c r="H16" t="n">
-        <v>366.0</v>
+        <v>368.0</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>294.0</v>
+        <v>307.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>237.0</v>
+        <v>241.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3364.0</v>
+        <v>3368.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>777.0</v>
+        <v>778.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -333,7 +333,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>299.0</v>
+        <v>300.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1163.0</v>
+        <v>1166.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -515,10 +515,10 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3328.0</v>
+        <v>3331.0</v>
       </c>
       <c r="G12" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -619,7 +619,7 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3013.0</v>
+        <v>3017.0</v>
       </c>
       <c r="G16" t="n">
         <v>76.0</v>
@@ -645,7 +645,7 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1702.0</v>
+        <v>1707.0</v>
       </c>
       <c r="G17" t="n">
         <v>49.0</v>
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>569.0</v>
+        <v>571.0</v>
       </c>
       <c r="G19" t="n">
         <v>8.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10602.0</v>
+        <v>10604.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>984.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3132.0</v>
+        <v>3139.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>4994.0</v>
+        <v>5000.0</v>
       </c>
       <c r="G22" t="n">
         <v>35.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3385.0</v>
+        <v>3392.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>694.0</v>
+        <v>695.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="G34" t="n">
         <v>4.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>607.0</v>
+        <v>610.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2047.0</v>
+        <v>2052.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2229.0</v>
+        <v>2235.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>498.0</v>
+        <v>506.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2195.0</v>
+        <v>2201.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3964.0</v>
+        <v>3973.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12488.0</v>
+        <v>12513.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>546.0</v>
+        <v>547.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1066.0</v>
+        <v>1068.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -411,7 +411,7 @@
         <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1116.0</v>
+        <v>1121.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1166.0</v>
+        <v>1167.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>975.0</v>
+        <v>978.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -625,7 +625,7 @@
         <v>76.0</v>
       </c>
       <c r="H16" t="n">
-        <v>368.0</v>
+        <v>372.0</v>
       </c>
     </row>
     <row r="17">
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10604.0</v>
+        <v>10609.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7447.0</v>
+        <v>7453.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3392.0</v>
+        <v>3394.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>307.0</v>
+        <v>308.0</v>
       </c>
     </row>
     <row r="28">
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>117.0</v>
+        <v>121.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>654.0</v>
+        <v>658.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>610.0</v>
+        <v>611.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>509.0</v>
+        <v>510.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2077.0</v>
+        <v>2084.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>963.0</v>
+        <v>964.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2335,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>3965.0</v>
+        <v>3970.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>1209.0</v>
+        <v>1211.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2647,7 +2647,7 @@
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>368.0</v>
+        <v>369.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>738.0</v>
+        <v>744.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1167.0</v>
+        <v>1172.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3331.0</v>
+        <v>3340.0</v>
       </c>
       <c r="G12" t="n">
         <v>9.0</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>135.0</v>
+        <v>138.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -596,7 +596,7 @@
         <v>301.0</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H15" t="n">
         <v>2.0</v>
@@ -619,7 +619,7 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3017.0</v>
+        <v>3030.0</v>
       </c>
       <c r="G16" t="n">
         <v>76.0</v>
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>571.0</v>
+        <v>572.0</v>
       </c>
       <c r="G19" t="n">
         <v>8.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3139.0</v>
+        <v>3148.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7453.0</v>
+        <v>7455.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3394.0</v>
+        <v>3395.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3368.0</v>
+        <v>3371.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>604.0</v>
+        <v>606.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>611.0</v>
+        <v>615.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2052.0</v>
+        <v>2060.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1521.0</v>
+        <v>1522.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>778.0</v>
+        <v>780.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1233.0</v>
+        <v>1236.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>88.0</v>
+        <v>94.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2235.0</v>
+        <v>2244.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>506.0</v>
+        <v>512.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>61.0</v>
+        <v>67.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2201.0</v>
+        <v>2209.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3973.0</v>
+        <v>3982.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2413,7 +2413,7 @@
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2673,7 +2673,7 @@
         <v>50</v>
       </c>
       <c r="F95" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G95" t="n">
         <v>1.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12513.0</v>
+        <v>12528.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1068.0</v>
+        <v>1070.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -385,7 +385,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>2179.0</v>
+        <v>2184.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3340.0</v>
+        <v>3341.0</v>
       </c>
       <c r="G12" t="n">
         <v>9.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10609.0</v>
+        <v>10618.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -775,13 +775,13 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5000.0</v>
+        <v>5022.0</v>
       </c>
       <c r="G22" t="n">
         <v>35.0</v>
       </c>
       <c r="H22" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="23">
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7455.0</v>
+        <v>7457.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>308.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>241.0</v>
+        <v>243.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3371.0</v>
+        <v>3378.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1064,7 +1064,7 @@
         <v>1721.0</v>
       </c>
       <c r="G33" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H33" t="n">
         <v>2.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>615.0</v>
+        <v>616.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>745.0</v>
+        <v>747.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2060.0</v>
+        <v>2065.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1236.0</v>
+        <v>1246.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2335,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12528.0</v>
+        <v>12544.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>547.0</v>
+        <v>548.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1070.0</v>
+        <v>1071.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>667.0</v>
+        <v>669.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1172.0</v>
+        <v>1175.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3341.0</v>
+        <v>3342.0</v>
       </c>
       <c r="G12" t="n">
         <v>9.0</v>
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>572.0</v>
+        <v>575.0</v>
       </c>
       <c r="G19" t="n">
         <v>8.0</v>
@@ -781,7 +781,7 @@
         <v>35.0</v>
       </c>
       <c r="H22" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="23">
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7457.0</v>
+        <v>7460.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>695.0</v>
+        <v>696.0</v>
       </c>
       <c r="G26" t="n">
         <v>4.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>606.0</v>
+        <v>609.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1522.0</v>
+        <v>1523.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>780.0</v>
+        <v>781.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1246.0</v>
+        <v>1247.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2244.0</v>
+        <v>2246.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>512.0</v>
+        <v>515.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2209.0</v>
+        <v>2218.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3982.0</v>
+        <v>3994.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12544.0</v>
+        <v>12558.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>548.0</v>
+        <v>550.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -729,7 +729,7 @@
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>985.0</v>
+        <v>987.0</v>
       </c>
     </row>
     <row r="21">

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>744.0</v>
+        <v>745.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>
@@ -333,7 +333,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>300.0</v>
+        <v>302.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1121.0</v>
+        <v>1124.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1175.0</v>
+        <v>1178.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>978.0</v>
+        <v>983.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -593,7 +593,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>301.0</v>
+        <v>305.0</v>
       </c>
       <c r="G15" t="n">
         <v>12.0</v>
@@ -619,13 +619,13 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3030.0</v>
+        <v>3031.0</v>
       </c>
       <c r="G16" t="n">
         <v>76.0</v>
       </c>
       <c r="H16" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="17">
@@ -645,7 +645,7 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1707.0</v>
+        <v>1708.0</v>
       </c>
       <c r="G17" t="n">
         <v>49.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10618.0</v>
+        <v>10622.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3148.0</v>
+        <v>3155.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -781,7 +781,7 @@
         <v>35.0</v>
       </c>
       <c r="H22" t="n">
-        <v>214.0</v>
+        <v>218.0</v>
       </c>
     </row>
     <row r="23">
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3586.0</v>
+        <v>3588.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -882,7 +882,7 @@
         <v>696.0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1721.0</v>
+        <v>1724.0</v>
       </c>
       <c r="G33" t="n">
         <v>7.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="G34" t="n">
         <v>4.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>609.0</v>
+        <v>615.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>317.0</v>
+        <v>338.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>121.0</v>
+        <v>124.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1184.0</v>
+        <v>1189.0</v>
       </c>
       <c r="G44" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>747.0</v>
+        <v>748.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2065.0</v>
+        <v>2068.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1523.0</v>
+        <v>1527.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2246.0</v>
+        <v>2258.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>515.0</v>
+        <v>518.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2084.0</v>
+        <v>2093.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2218.0</v>
+        <v>2222.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3994.0</v>
+        <v>3999.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2179,7 +2179,7 @@
         <v>50</v>
       </c>
       <c r="F76" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>3970.0</v>
+        <v>3974.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>7395.0</v>
+        <v>7396.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12558.0</v>
+        <v>12592.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1071.0</v>
+        <v>1075.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1178.0</v>
+        <v>1180.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>983.0</v>
+        <v>990.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>321.0</v>
+        <v>324.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -596,7 +596,7 @@
         <v>305.0</v>
       </c>
       <c r="G15" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H15" t="n">
         <v>2.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="19">
@@ -775,10 +775,10 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5022.0</v>
+        <v>5025.0</v>
       </c>
       <c r="G22" t="n">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="H22" t="n">
         <v>218.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7460.0</v>
+        <v>7464.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -905,13 +905,13 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>688.0</v>
+        <v>694.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>312.0</v>
+        <v>323.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>243.0</v>
+        <v>246.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3378.0</v>
+        <v>3379.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>615.0</v>
+        <v>619.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1217,7 +1217,7 @@
         <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>1012.0</v>
+        <v>1013.0</v>
       </c>
       <c r="G39" t="n">
         <v>4.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>616.0</v>
+        <v>618.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>748.0</v>
+        <v>749.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2068.0</v>
+        <v>2069.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>781.0</v>
+        <v>786.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1247.0</v>
+        <v>1250.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2258.0</v>
+        <v>2263.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>518.0</v>
+        <v>523.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2222.0</v>
+        <v>2226.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>3999.0</v>
+        <v>4011.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>964.0</v>
+        <v>965.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2335,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2413,7 +2413,7 @@
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2439,7 +2439,7 @@
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>502.0</v>
+        <v>503.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12592.0</v>
+        <v>12606.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>745.0</v>
+        <v>746.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>
@@ -492,7 +492,7 @@
         <v>990.0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -622,7 +622,7 @@
         <v>3031.0</v>
       </c>
       <c r="G16" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="H16" t="n">
         <v>373.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10622.0</v>
+        <v>10641.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>987.0</v>
+        <v>989.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3155.0</v>
+        <v>3169.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5025.0</v>
+        <v>5027.0</v>
       </c>
       <c r="G22" t="n">
         <v>38.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3395.0</v>
+        <v>3397.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>246.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="29">
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>608.0</v>
+        <v>609.0</v>
       </c>
       <c r="G34" t="n">
         <v>4.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>618.0</v>
+        <v>619.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>749.0</v>
+        <v>751.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2069.0</v>
+        <v>2074.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1503,7 +1503,7 @@
         <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>2812.0</v>
+        <v>2813.0</v>
       </c>
       <c r="G50" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1527.0</v>
+        <v>1528.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>786.0</v>
+        <v>787.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1250.0</v>
+        <v>1254.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>98.0</v>
+        <v>103.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2263.0</v>
+        <v>2269.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2226.0</v>
+        <v>2231.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>4011.0</v>
+        <v>4019.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12606.0</v>
+        <v>12625.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>550.0</v>
+        <v>551.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1180.0</v>
+        <v>1181.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>990.0</v>
+        <v>991.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10641.0</v>
+        <v>10642.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>989.0</v>
+        <v>995.0</v>
       </c>
     </row>
     <row r="21">
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7464.0</v>
+        <v>7471.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>323.0</v>
+        <v>326.0</v>
       </c>
     </row>
     <row r="28">
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2074.0</v>
+        <v>2076.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1503,7 +1503,7 @@
         <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>2813.0</v>
+        <v>2814.0</v>
       </c>
       <c r="G50" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1528.0</v>
+        <v>1534.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12625.0</v>
+        <v>12637.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -625,7 +625,7 @@
         <v>77.0</v>
       </c>
       <c r="H16" t="n">
-        <v>373.0</v>
+        <v>375.0</v>
       </c>
     </row>
     <row r="17">
@@ -781,7 +781,7 @@
         <v>38.0</v>
       </c>
       <c r="H22" t="n">
-        <v>218.0</v>
+        <v>221.0</v>
       </c>
     </row>
     <row r="23">
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1254.0</v>
+        <v>1256.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3169.0</v>
+        <v>3171.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5027.0</v>
+        <v>5030.0</v>
       </c>
       <c r="G22" t="n">
         <v>38.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>696.0</v>
+        <v>697.0</v>
       </c>
       <c r="G26" t="n">
         <v>5.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>326.0</v>
+        <v>332.0</v>
       </c>
     </row>
     <row r="28">
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>609.0</v>
+        <v>610.0</v>
       </c>
       <c r="G34" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2076.0</v>
+        <v>2077.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1534.0</v>
+        <v>1536.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12637.0</v>
+        <v>12663.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>551.0</v>
+        <v>552.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1124.0</v>
+        <v>1133.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>324.0</v>
+        <v>327.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>77.0</v>
       </c>
       <c r="H16" t="n">
-        <v>375.0</v>
+        <v>376.0</v>
       </c>
     </row>
     <row r="17">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3171.0</v>
+        <v>3173.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3588.0</v>
+        <v>3593.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7471.0</v>
+        <v>7472.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -905,13 +905,13 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>694.0</v>
+        <v>696.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>332.0</v>
+        <v>335.0</v>
       </c>
     </row>
     <row r="28">
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>124.0</v>
+        <v>127.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>658.0</v>
+        <v>663.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>738.0</v>
+        <v>741.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>620.0</v>
+        <v>622.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>751.0</v>
+        <v>752.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>511.0</v>
+        <v>515.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2093.0</v>
+        <v>2099.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>965.0</v>
+        <v>966.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>3974.0</v>
+        <v>3975.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>7396.0</v>
+        <v>7398.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>1211.0</v>
+        <v>1212.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>552.0</v>
+        <v>553.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1075.0</v>
+        <v>1079.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>746.0</v>
+        <v>750.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>
@@ -333,7 +333,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>991.0</v>
+        <v>992.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3342.0</v>
+        <v>3344.0</v>
       </c>
       <c r="G12" t="n">
         <v>9.0</v>
@@ -619,7 +619,7 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3031.0</v>
+        <v>3038.0</v>
       </c>
       <c r="G16" t="n">
         <v>77.0</v>
@@ -645,7 +645,7 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1708.0</v>
+        <v>1710.0</v>
       </c>
       <c r="G17" t="n">
         <v>49.0</v>
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>575.0</v>
+        <v>576.0</v>
       </c>
       <c r="G19" t="n">
         <v>8.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10642.0</v>
+        <v>10651.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>995.0</v>
+        <v>996.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3173.0</v>
+        <v>3176.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5030.0</v>
+        <v>5031.0</v>
       </c>
       <c r="G22" t="n">
         <v>38.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3397.0</v>
+        <v>3399.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -879,10 +879,10 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>697.0</v>
+        <v>702.0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -905,7 +905,7 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>696.0</v>
+        <v>697.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>251.0</v>
+        <v>259.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3379.0</v>
+        <v>3385.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>619.0</v>
+        <v>623.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>338.0</v>
+        <v>341.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>752.0</v>
+        <v>760.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2077.0</v>
+        <v>2083.0</v>
       </c>
       <c r="G49" t="n">
         <v>10.0</v>
@@ -1555,10 +1555,10 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1536.0</v>
+        <v>1537.0</v>
       </c>
       <c r="G52" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>787.0</v>
+        <v>788.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1256.0</v>
+        <v>1257.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>103.0</v>
+        <v>107.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2269.0</v>
+        <v>2274.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>523.0</v>
+        <v>527.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>323.0</v>
+        <v>324.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2231.0</v>
+        <v>2237.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>4019.0</v>
+        <v>4022.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2075,7 +2075,7 @@
         <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>257.0</v>
+        <v>262.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12663.0</v>
+        <v>12681.0</v>
       </c>
       <c r="G97" t="n">
         <v>14.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1079.0</v>
+        <v>1080.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="51">
   <si>
     <t>Area</t>
   </si>
@@ -307,10 +307,10 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>750.0</v>
+        <v>154.0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0</v>
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>669.0</v>
+        <v>683.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -385,7 +385,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>2184.0</v>
+        <v>2128.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -515,10 +515,10 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>3344.0</v>
+        <v>1782.0</v>
       </c>
       <c r="G12" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -619,10 +619,10 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3038.0</v>
+        <v>3634.0</v>
       </c>
       <c r="G16" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="H16" t="n">
         <v>376.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10651.0</v>
+        <v>10654.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -749,13 +749,13 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3176.0</v>
+        <v>3178.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="22">
@@ -775,10 +775,10 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5031.0</v>
+        <v>5475.0</v>
       </c>
       <c r="G22" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="H22" t="n">
         <v>221.0</v>
@@ -879,10 +879,10 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>702.0</v>
+        <v>2813.0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -1191,7 +1191,7 @@
         <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>121.0</v>
+        <v>107.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1217,10 +1217,10 @@
         <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>1013.0</v>
+        <v>626.0</v>
       </c>
       <c r="G39" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>663.0</v>
+        <v>664.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>741.0</v>
+        <v>743.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>622.0</v>
+        <v>625.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>760.0</v>
+        <v>763.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,10 +1477,10 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2083.0</v>
+        <v>1535.0</v>
       </c>
       <c r="G49" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1537.0</v>
+        <v>1538.0</v>
       </c>
       <c r="G52" t="n">
         <v>2.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>788.0</v>
+        <v>789.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2274.0</v>
+        <v>1942.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>74.0</v>
+        <v>79.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1763,7 +1763,7 @@
         <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1893,10 +1893,10 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>324.0</v>
+        <v>54.0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2237.0</v>
+        <v>2569.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>966.0</v>
+        <v>967.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2274,19 +2274,19 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>9.0</v>
+        <v>274.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2303,13 +2303,13 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E81" t="s">
         <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E82" t="s">
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>108.0</v>
+        <v>17.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2355,13 +2355,13 @@
         <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E83" t="s">
         <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>3.0</v>
+        <v>109.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2375,13 +2375,13 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
         <v>50</v>
@@ -2404,16 +2404,16 @@
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E85" t="s">
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>251.0</v>
+        <v>3.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2433,13 +2433,13 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>503.0</v>
+        <v>251.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2459,13 +2459,13 @@
         <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>262.0</v>
+        <v>503.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2485,13 +2485,13 @@
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E88" t="s">
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>277.0</v>
+        <v>262.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2508,16 +2508,16 @@
         <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E89" t="s">
         <v>50</v>
       </c>
       <c r="F89" t="n">
-        <v>15.0</v>
+        <v>272.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2534,16 +2534,16 @@
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>3975.0</v>
+        <v>14.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2563,19 +2563,19 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E91" t="s">
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>7398.0</v>
+        <v>3975.0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -2589,19 +2589,19 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E92" t="s">
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>1212.0</v>
+        <v>7398.0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H92" t="n">
-        <v>670.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="93">
@@ -2615,19 +2615,19 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E93" t="s">
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>3864.0</v>
+        <v>1212.0</v>
       </c>
       <c r="G93" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>19.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="94">
@@ -2641,19 +2641,19 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E94" t="s">
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>74.0</v>
+        <v>3864.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="95">
@@ -2664,22 +2664,22 @@
         <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
       </c>
       <c r="F95" t="n">
-        <v>103.0</v>
+        <v>74.0</v>
       </c>
       <c r="G95" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H95" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -2693,19 +2693,19 @@
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E96" t="s">
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>142.0</v>
+        <v>104.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="97">
@@ -2719,16 +2719,16 @@
         <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>12681.0</v>
+        <v>142.0</v>
       </c>
       <c r="G97" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2745,19 +2745,19 @@
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E98" t="s">
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>553.0</v>
+        <v>12695.0</v>
       </c>
       <c r="G98" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H98" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -2771,19 +2771,19 @@
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E99" t="s">
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>4.0</v>
+        <v>555.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="100">
@@ -2797,19 +2797,19 @@
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E100" t="s">
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>1080.0</v>
+        <v>4.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
@@ -2820,22 +2820,22 @@
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E101" t="s">
         <v>50</v>
       </c>
       <c r="F101" t="n">
+        <v>1080.0</v>
+      </c>
+      <c r="G101" t="n">
         <v>1.0</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H101" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="102">
@@ -2846,16 +2846,16 @@
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E102" t="s">
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -2875,18 +2875,44 @@
         <v>17</v>
       </c>
       <c r="D103" t="s">
+        <v>31</v>
+      </c>
+      <c r="E103" t="s">
+        <v>50</v>
+      </c>
+      <c r="F103" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
         <v>32</v>
       </c>
-      <c r="E103" t="s">
-        <v>50</v>
-      </c>
-      <c r="F103" t="n">
+      <c r="E104" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" t="n">
         <v>41.0</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H103" t="n">
+      <c r="G104" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H104" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1181.0</v>
+        <v>1185.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -729,7 +729,7 @@
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>996.0</v>
+        <v>1001.0</v>
       </c>
     </row>
     <row r="21">
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7472.0</v>
+        <v>7474.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>335.0</v>
+        <v>347.0</v>
       </c>
     </row>
     <row r="28">
@@ -1041,7 +1041,7 @@
         <v>13.0</v>
       </c>
       <c r="H32" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="33">
@@ -1067,7 +1067,7 @@
         <v>7.0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="34">
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>625.0</v>
+        <v>626.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1535.0</v>
+        <v>1538.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1538.0</v>
+        <v>1539.0</v>
       </c>
       <c r="G52" t="n">
         <v>2.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>789.0</v>
+        <v>792.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1257.0</v>
+        <v>1258.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12695.0</v>
+        <v>12705.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2907,7 +2907,7 @@
         <v>50</v>
       </c>
       <c r="F104" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -905,7 +905,7 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>697.0</v>
+        <v>698.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>792.0</v>
+        <v>793.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1258.0</v>
+        <v>1260.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1133.0</v>
+        <v>1136.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>992.0</v>
+        <v>994.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>1782.0</v>
+        <v>1783.0</v>
       </c>
       <c r="G12" t="n">
         <v>3.0</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>327.0</v>
+        <v>330.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10654.0</v>
+        <v>10658.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>1001.0</v>
+        <v>1003.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3178.0</v>
+        <v>3183.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5475.0</v>
+        <v>5486.0</v>
       </c>
       <c r="G22" t="n">
         <v>39.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3593.0</v>
+        <v>3597.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7474.0</v>
+        <v>7482.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>2813.0</v>
+        <v>2814.0</v>
       </c>
       <c r="G26" t="n">
         <v>12.0</v>
@@ -905,13 +905,13 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>698.0</v>
+        <v>699.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>347.0</v>
+        <v>356.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>259.0</v>
+        <v>261.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3385.0</v>
+        <v>3387.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>610.0</v>
+        <v>611.0</v>
       </c>
       <c r="G34" t="n">
         <v>4.0</v>
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>664.0</v>
+        <v>681.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>743.0</v>
+        <v>744.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>626.0</v>
+        <v>627.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1538.0</v>
+        <v>1544.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>793.0</v>
+        <v>795.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1260.0</v>
+        <v>1261.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>515.0</v>
+        <v>521.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2099.0</v>
+        <v>2112.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>967.0</v>
+        <v>968.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>274.0</v>
+        <v>277.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>3975.0</v>
+        <v>3976.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>7398.0</v>
+        <v>7402.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2673,7 +2673,7 @@
         <v>50</v>
       </c>
       <c r="F95" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12705.0</v>
+        <v>12751.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>555.0</v>
+        <v>559.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3183.0</v>
+        <v>3182.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3399.0</v>
+        <v>3400.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>356.0</v>
+        <v>362.0</v>
       </c>
     </row>
     <row r="28">
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1724.0</v>
+        <v>1726.0</v>
       </c>
       <c r="G33" t="n">
         <v>7.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>627.0</v>
+        <v>629.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>795.0</v>
+        <v>796.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1261.0</v>
+        <v>1263.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12751.0</v>
+        <v>12766.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>559.0</v>
+        <v>563.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1080.0</v>
+        <v>1081.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -2907,7 +2907,7 @@
         <v>50</v>
       </c>
       <c r="F104" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>369.0</v>
+        <v>373.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>154.0</v>
+        <v>166.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>683.0</v>
+        <v>684.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -596,7 +596,7 @@
         <v>305.0</v>
       </c>
       <c r="G15" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="H15" t="n">
         <v>2.0</v>
@@ -619,10 +619,10 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3634.0</v>
+        <v>3637.0</v>
       </c>
       <c r="G16" t="n">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="H16" t="n">
         <v>376.0</v>
@@ -645,10 +645,10 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1710.0</v>
+        <v>1712.0</v>
       </c>
       <c r="G17" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="H17" t="n">
         <v>229.0</v>
@@ -700,7 +700,7 @@
         <v>576.0</v>
       </c>
       <c r="G19" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3182.0</v>
+        <v>3183.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -905,13 +905,13 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>699.0</v>
+        <v>701.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>362.0</v>
+        <v>363.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>261.0</v>
+        <v>267.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3387.0</v>
+        <v>3394.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>623.0</v>
+        <v>634.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>341.0</v>
+        <v>350.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1217,7 +1217,7 @@
         <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>626.0</v>
+        <v>627.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>629.0</v>
+        <v>630.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1263.0</v>
+        <v>1267.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12766.0</v>
+        <v>12789.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>796.0</v>
+        <v>797.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1267.0</v>
+        <v>1268.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1136.0</v>
+        <v>1140.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>994.0</v>
+        <v>997.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10658.0</v>
+        <v>10671.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>1003.0</v>
+        <v>1008.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3183.0</v>
+        <v>3184.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,10 +775,10 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5486.0</v>
+        <v>5491.0</v>
       </c>
       <c r="G22" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="H22" t="n">
         <v>221.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3597.0</v>
+        <v>3598.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -879,10 +879,10 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>2814.0</v>
+        <v>2819.0</v>
       </c>
       <c r="G26" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1295,7 +1295,7 @@
         <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1189.0</v>
+        <v>1191.0</v>
       </c>
       <c r="G44" t="n">
         <v>4.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>744.0</v>
+        <v>745.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1544.0</v>
+        <v>1545.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2112.0</v>
+        <v>2119.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>968.0</v>
+        <v>969.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2361,7 +2361,7 @@
         <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>3976.0</v>
+        <v>3977.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>7402.0</v>
+        <v>7404.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>1212.0</v>
+        <v>1211.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2647,7 +2647,7 @@
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>3864.0</v>
+        <v>3865.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12789.0</v>
+        <v>12807.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -625,7 +625,7 @@
         <v>81.0</v>
       </c>
       <c r="H16" t="n">
-        <v>376.0</v>
+        <v>378.0</v>
       </c>
     </row>
     <row r="17">

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -521,7 +521,7 @@
         <v>3.0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="G19" t="n">
         <v>16.0</v>
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
     </row>
     <row r="29">
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>634.0</v>
+        <v>637.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>350.0</v>
+        <v>357.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>1942.0</v>
+        <v>1945.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>563.0</v>
+        <v>564.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>81.0</v>
       </c>
       <c r="H16" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
     </row>
     <row r="17">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10671.0</v>
+        <v>10674.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -755,7 +755,7 @@
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="22">
@@ -775,10 +775,10 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5491.0</v>
+        <v>5493.0</v>
       </c>
       <c r="G22" t="n">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="H22" t="n">
         <v>221.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>2819.0</v>
+        <v>2820.0</v>
       </c>
       <c r="G26" t="n">
         <v>15.0</v>
@@ -905,13 +905,13 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>701.0</v>
+        <v>702.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>363.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>268.0</v>
+        <v>276.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3394.0</v>
+        <v>3395.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1529,7 +1529,7 @@
         <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1268.0</v>
+        <v>1270.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12807.0</v>
+        <v>12815.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>564.0</v>
+        <v>565.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1081.0</v>
+        <v>1086.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -775,13 +775,13 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5493.0</v>
+        <v>5495.0</v>
       </c>
       <c r="G22" t="n">
         <v>43.0</v>
       </c>
       <c r="H22" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="23">
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7482.0</v>
+        <v>7488.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -885,7 +885,7 @@
         <v>15.0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="27">
@@ -1217,7 +1217,7 @@
         <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1545.0</v>
+        <v>1547.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1539.0</v>
+        <v>1540.0</v>
       </c>
       <c r="G52" t="n">
         <v>2.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>797.0</v>
+        <v>799.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1270.0</v>
+        <v>1272.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12815.0</v>
+        <v>12836.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="19">
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1272.0</v>
+        <v>1274.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3184.0</v>
+        <v>3186.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,10 +775,10 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5495.0</v>
+        <v>5499.0</v>
       </c>
       <c r="G22" t="n">
-        <v>43.0</v>
+        <v>40.0</v>
       </c>
       <c r="H22" t="n">
         <v>222.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7488.0</v>
+        <v>7489.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>373.0</v>
+        <v>376.0</v>
       </c>
     </row>
     <row r="28">
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1726.0</v>
+        <v>1727.0</v>
       </c>
       <c r="G33" t="n">
         <v>7.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1547.0</v>
+        <v>1548.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1503,7 +1503,7 @@
         <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>2814.0</v>
+        <v>2815.0</v>
       </c>
       <c r="G50" t="n">
         <v>8.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>142.0</v>
+        <v>144.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12836.0</v>
+        <v>12870.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1140.0</v>
+        <v>1141.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -625,7 +625,7 @@
         <v>81.0</v>
       </c>
       <c r="H16" t="n">
-        <v>379.0</v>
+        <v>381.0</v>
       </c>
     </row>
     <row r="17">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10674.0</v>
+        <v>10679.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -749,13 +749,13 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3186.0</v>
+        <v>3189.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="22">
@@ -775,13 +775,13 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5499.0</v>
+        <v>5519.0</v>
       </c>
       <c r="G22" t="n">
         <v>40.0</v>
       </c>
       <c r="H22" t="n">
-        <v>222.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="23">
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3598.0</v>
+        <v>3601.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3400.0</v>
+        <v>3404.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -905,7 +905,7 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>702.0</v>
+        <v>703.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1064,7 +1064,7 @@
         <v>1727.0</v>
       </c>
       <c r="G33" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H33" t="n">
         <v>4.0</v>
@@ -1217,7 +1217,7 @@
         <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>628.0</v>
+        <v>629.0</v>
       </c>
       <c r="G39" t="n">
         <v>3.0</v>
@@ -1295,7 +1295,7 @@
         <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>681.0</v>
+        <v>682.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1191.0</v>
+        <v>1197.0</v>
       </c>
       <c r="G44" t="n">
         <v>4.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>745.0</v>
+        <v>746.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>799.0</v>
+        <v>804.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>522.0</v>
+        <v>524.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2119.0</v>
+        <v>2125.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>3977.0</v>
+        <v>3978.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>7404.0</v>
+        <v>7407.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>1211.0</v>
+        <v>1213.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>565.0</v>
+        <v>567.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>997.0</v>
+        <v>999.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>81.0</v>
       </c>
       <c r="H16" t="n">
-        <v>381.0</v>
+        <v>382.0</v>
       </c>
     </row>
     <row r="17">
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7489.0</v>
+        <v>7490.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3404.0</v>
+        <v>3406.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -882,7 +882,7 @@
         <v>2820.0</v>
       </c>
       <c r="G26" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="H26" t="n">
         <v>2.0</v>
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>276.0</v>
+        <v>281.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3395.0</v>
+        <v>3396.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1067,7 +1067,7 @@
         <v>8.0</v>
       </c>
       <c r="H33" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="34">
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1548.0</v>
+        <v>1549.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1540.0</v>
+        <v>1542.0</v>
       </c>
       <c r="G52" t="n">
         <v>2.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1274.0</v>
+        <v>1284.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>969.0</v>
+        <v>970.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12870.0</v>
+        <v>12897.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>373.0</v>
+        <v>374.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -333,7 +333,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>684.0</v>
+        <v>687.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -593,7 +593,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="G15" t="n">
         <v>15.0</v>
@@ -619,10 +619,10 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3637.0</v>
+        <v>3685.0</v>
       </c>
       <c r="G16" t="n">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
       <c r="H16" t="n">
         <v>382.0</v>
@@ -645,7 +645,7 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1712.0</v>
+        <v>1719.0</v>
       </c>
       <c r="G17" t="n">
         <v>50.0</v>
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>577.0</v>
+        <v>580.0</v>
       </c>
       <c r="G19" t="n">
         <v>16.0</v>
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10679.0</v>
+        <v>10686.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>1008.0</v>
+        <v>1009.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3189.0</v>
+        <v>3205.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>376.0</v>
+        <v>382.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>281.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3396.0</v>
+        <v>3397.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>637.0</v>
+        <v>654.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>357.0</v>
+        <v>376.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1191,7 +1191,7 @@
         <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1549.0</v>
+        <v>1552.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1284.0</v>
+        <v>1289.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>107.0</v>
+        <v>167.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>1945.0</v>
+        <v>2038.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>527.0</v>
+        <v>554.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>79.0</v>
+        <v>94.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>53.0</v>
+        <v>63.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2569.0</v>
+        <v>2640.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>4022.0</v>
+        <v>4124.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2075,7 +2075,7 @@
         <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2439,7 +2439,7 @@
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>503.0</v>
+        <v>511.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2491,7 +2491,7 @@
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>262.0</v>
+        <v>268.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2517,7 +2517,7 @@
         <v>50</v>
       </c>
       <c r="F89" t="n">
-        <v>272.0</v>
+        <v>276.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12897.0</v>
+        <v>12924.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1086.0</v>
+        <v>1087.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -515,10 +515,10 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>1783.0</v>
+        <v>1784.0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H12" t="n">
         <v>1.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="19">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3205.0</v>
+        <v>3207.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -905,7 +905,7 @@
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>703.0</v>
+        <v>705.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>289.0</v>
+        <v>295.0</v>
       </c>
     </row>
     <row r="29">
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1552.0</v>
+        <v>1554.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1542.0</v>
+        <v>1543.0</v>
       </c>
       <c r="G52" t="n">
         <v>2.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12924.0</v>
+        <v>12938.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>567.0</v>
+        <v>569.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1087.0</v>
+        <v>1090.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -625,7 +625,7 @@
         <v>84.0</v>
       </c>
       <c r="H16" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
     </row>
     <row r="17">
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="19">
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1289.0</v>
+        <v>1295.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -2335,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -515,13 +515,13 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>1784.0</v>
+        <v>1785.0</v>
       </c>
       <c r="G12" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13">
@@ -749,13 +749,13 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3207.0</v>
+        <v>3208.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="22">
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5519.0</v>
+        <v>5520.0</v>
       </c>
       <c r="G22" t="n">
         <v>40.0</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12938.0</v>
+        <v>12968.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>374.0</v>
+        <v>378.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -333,7 +333,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>313.0</v>
+        <v>314.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1141.0</v>
+        <v>1142.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -463,7 +463,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1185.0</v>
+        <v>1187.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -593,7 +593,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>306.0</v>
+        <v>310.0</v>
       </c>
       <c r="G15" t="n">
         <v>15.0</v>
@@ -619,13 +619,13 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3685.0</v>
+        <v>3687.0</v>
       </c>
       <c r="G16" t="n">
         <v>84.0</v>
       </c>
       <c r="H16" t="n">
-        <v>383.0</v>
+        <v>386.0</v>
       </c>
     </row>
     <row r="17">
@@ -645,7 +645,7 @@
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1719.0</v>
+        <v>1721.0</v>
       </c>
       <c r="G17" t="n">
         <v>50.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3208.0</v>
+        <v>3212.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3601.0</v>
+        <v>3603.0</v>
       </c>
       <c r="G23" t="n">
         <v>7.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>654.0</v>
+        <v>673.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1139,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>376.0</v>
+        <v>392.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>682.0</v>
+        <v>688.0</v>
       </c>
       <c r="G43" t="n">
         <v>3.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1197.0</v>
+        <v>1200.0</v>
       </c>
       <c r="G44" t="n">
         <v>4.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>630.0</v>
+        <v>632.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1554.0</v>
+        <v>1555.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>167.0</v>
+        <v>171.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2038.0</v>
+        <v>2046.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>554.0</v>
+        <v>556.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1737,7 +1737,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>94.0</v>
+        <v>98.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>524.0</v>
+        <v>528.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2125.0</v>
+        <v>2135.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>194.0</v>
+        <v>197.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2640.0</v>
+        <v>2649.0</v>
       </c>
       <c r="G70" t="n">
         <v>2.0</v>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>4124.0</v>
+        <v>4142.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>970.0</v>
+        <v>972.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2309,7 +2309,7 @@
         <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2387,7 +2387,7 @@
         <v>50</v>
       </c>
       <c r="F84" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2491,7 +2491,7 @@
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>268.0</v>
+        <v>271.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>3978.0</v>
+        <v>3980.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>7407.0</v>
+        <v>7410.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>1213.0</v>
+        <v>1214.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>569.0</v>
+        <v>570.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>999.0</v>
+        <v>1004.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -515,10 +515,10 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>1785.0</v>
+        <v>1788.0</v>
       </c>
       <c r="G12" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H12" t="n">
         <v>2.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="19">
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5520.0</v>
+        <v>5534.0</v>
       </c>
       <c r="G22" t="n">
         <v>40.0</v>
@@ -827,7 +827,7 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7490.0</v>
+        <v>7493.0</v>
       </c>
       <c r="G24" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3406.0</v>
+        <v>3409.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -882,7 +882,7 @@
         <v>2820.0</v>
       </c>
       <c r="G26" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="H26" t="n">
         <v>2.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>382.0</v>
+        <v>395.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>295.0</v>
+        <v>303.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3397.0</v>
+        <v>3398.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>632.0</v>
+        <v>633.0</v>
       </c>
       <c r="G46" t="n">
         <v>4.0</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>763.0</v>
+        <v>764.0</v>
       </c>
       <c r="G47" t="n">
         <v>1.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1555.0</v>
+        <v>1558.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>804.0</v>
+        <v>807.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1295.0</v>
+        <v>1300.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>281.0</v>
+        <v>284.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12968.0</v>
+        <v>12982.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10686.0</v>
+        <v>10697.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
       </c>
       <c r="H20" t="n">
-        <v>1009.0</v>
+        <v>1012.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3212.0</v>
+        <v>3222.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,13 +775,13 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5534.0</v>
+        <v>5535.0</v>
       </c>
       <c r="G22" t="n">
         <v>40.0</v>
       </c>
       <c r="H22" t="n">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>303.0</v>
+        <v>306.0</v>
       </c>
     </row>
     <row r="29">
@@ -1061,10 +1061,10 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1727.0</v>
+        <v>1728.0</v>
       </c>
       <c r="G33" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H33" t="n">
         <v>5.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1558.0</v>
+        <v>1559.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1581,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>807.0</v>
+        <v>808.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1300.0</v>
+        <v>1305.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12982.0</v>
+        <v>13014.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1090.0</v>
+        <v>1093.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -625,7 +625,7 @@
         <v>84.0</v>
       </c>
       <c r="H16" t="n">
-        <v>386.0</v>
+        <v>388.0</v>
       </c>
     </row>
     <row r="17">
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>306.0</v>
+        <v>308.0</v>
       </c>
     </row>
     <row r="29">
@@ -1503,7 +1503,7 @@
         <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>2815.0</v>
+        <v>2816.0</v>
       </c>
       <c r="G50" t="n">
         <v>8.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1305.0</v>
+        <v>1306.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>13014.0</v>
+        <v>13027.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1093.0</v>
+        <v>1094.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -781,7 +781,7 @@
         <v>40.0</v>
       </c>
       <c r="H22" t="n">
-        <v>230.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="23">
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3398.0</v>
+        <v>3405.0</v>
       </c>
       <c r="G29" t="n">
         <v>3.0</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>1306.0</v>
+        <v>1312.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -515,10 +515,10 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>1788.0</v>
+        <v>1792.0</v>
       </c>
       <c r="G12" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="H12" t="n">
         <v>2.0</v>
@@ -625,7 +625,7 @@
         <v>84.0</v>
       </c>
       <c r="H16" t="n">
-        <v>388.0</v>
+        <v>389.0</v>
       </c>
     </row>
     <row r="17">
@@ -651,7 +651,7 @@
         <v>50.0</v>
       </c>
       <c r="H17" t="n">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="18">
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10697.0</v>
+        <v>10706.0</v>
       </c>
       <c r="G20" t="n">
         <v>146.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3222.0</v>
+        <v>3229.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5535.0</v>
+        <v>5537.0</v>
       </c>
       <c r="G22" t="n">
         <v>40.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3409.0</v>
+        <v>3411.0</v>
       </c>
       <c r="G25" t="n">
         <v>3.0</v>
@@ -911,7 +911,7 @@
         <v>1.0</v>
       </c>
       <c r="H27" t="n">
-        <v>395.0</v>
+        <v>396.0</v>
       </c>
     </row>
     <row r="28">
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1559.0</v>
+        <v>1560.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>972.0</v>
+        <v>973.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>13027.0</v>
+        <v>13060.0</v>
       </c>
       <c r="G98" t="n">
         <v>14.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>570.0</v>
+        <v>571.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -385,7 +385,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>2128.0</v>
+        <v>2130.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1142.0</v>
+        <v>1147.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -521,7 +521,7 @@
         <v>14.0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="13">
@@ -625,7 +625,7 @@
         <v>84.0</v>
       </c>
       <c r="H16" t="n">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
     </row>
     <row r="17">
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="19">
@@ -749,13 +749,13 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3229.0</v>
+        <v>3231.0</v>
       </c>
       <c r="G21" t="n">
         <v>20.0</v>
       </c>
       <c r="H21" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="22">
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5537.0</v>
+        <v>5541.0</v>
       </c>
       <c r="G22" t="n">
         <v>40.0</v>
@@ -937,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="n">
-        <v>308.0</v>
+        <v>311.0</v>
       </c>
     </row>
     <row r="29">
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1200.0</v>
+        <v>1205.0</v>
       </c>
       <c r="G44" t="n">
         <v>4.0</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1560.0</v>
+        <v>1561.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1543.0</v>
+        <v>1544.0</v>
       </c>
       <c r="G52" t="n">
         <v>2.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2135.0</v>
+        <v>2142.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>3980.0</v>
+        <v>3982.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>1214.0</v>
+        <v>1215.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>571.0</v>
+        <v>573.0</v>
       </c>
       <c r="G99" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -92,46 +92,46 @@
     <t>Savona</t>
   </si>
   <si>
+    <t>Pavia</t>
+  </si>
+  <si>
+    <t>Alessandria</t>
+  </si>
+  <si>
+    <t>Asti</t>
+  </si>
+  <si>
+    <t>Cuneo</t>
+  </si>
+  <si>
+    <t>Lucca</t>
+  </si>
+  <si>
+    <t>Pistoia</t>
+  </si>
+  <si>
+    <t>Reggio emilia</t>
+  </si>
+  <si>
+    <t>Genova</t>
+  </si>
+  <si>
+    <t>La spezia</t>
+  </si>
+  <si>
+    <t>Massa</t>
+  </si>
+  <si>
+    <t>Massa-carrara</t>
+  </si>
+  <si>
+    <t>Brescia</t>
+  </si>
+  <si>
+    <t>Cremona</t>
+  </si>
+  <si>
     <t>Lodi</t>
-  </si>
-  <si>
-    <t>Pavia</t>
-  </si>
-  <si>
-    <t>Alessandria</t>
-  </si>
-  <si>
-    <t>Asti</t>
-  </si>
-  <si>
-    <t>Cuneo</t>
-  </si>
-  <si>
-    <t>Lucca</t>
-  </si>
-  <si>
-    <t>Pistoia</t>
-  </si>
-  <si>
-    <t>Reggio emilia</t>
-  </si>
-  <si>
-    <t>Genova</t>
-  </si>
-  <si>
-    <t>La spezia</t>
-  </si>
-  <si>
-    <t>Massa</t>
-  </si>
-  <si>
-    <t>Massa-carrara</t>
-  </si>
-  <si>
-    <t>Brescia</t>
-  </si>
-  <si>
-    <t>Cremona</t>
   </si>
   <si>
     <t>Milano</t>
@@ -307,7 +307,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -333,7 +333,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>687.0</v>
+        <v>693.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -411,13 +411,13 @@
         <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>27.0</v>
+        <v>761.0</v>
       </c>
       <c r="G8" t="n">
         <v>1.0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="9">
@@ -428,7 +428,7 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -437,13 +437,13 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1147.0</v>
+        <v>1413.0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" t="n">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,13 +463,13 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>1187.0</v>
+        <v>1856.0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -489,10 +489,10 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>1004.0</v>
+        <v>1271.0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>30</v>
@@ -515,13 +515,13 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>1792.0</v>
+        <v>333.0</v>
       </c>
       <c r="G12" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>332.0</v>
+        <v>141.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -555,25 +555,25 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>141.0</v>
+        <v>311.0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
@@ -587,19 +587,19 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>310.0</v>
+        <v>3697.0</v>
       </c>
       <c r="G15" t="n">
-        <v>15.0</v>
+        <v>84.0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0</v>
+        <v>390.0</v>
       </c>
     </row>
     <row r="16">
@@ -613,19 +613,19 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>3687.0</v>
+        <v>1730.0</v>
       </c>
       <c r="G16" t="n">
-        <v>84.0</v>
+        <v>50.0</v>
       </c>
       <c r="H16" t="n">
-        <v>390.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="17">
@@ -639,19 +639,19 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
         <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>1721.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>230.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="18">
@@ -665,19 +665,19 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
         <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0</v>
+        <v>582.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H18" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -688,22 +688,22 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>580.0</v>
+        <v>10706.0</v>
       </c>
       <c r="G19" t="n">
-        <v>16.0</v>
+        <v>146.0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0</v>
+        <v>1012.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>10706.0</v>
+        <v>3231.0</v>
       </c>
       <c r="G20" t="n">
-        <v>146.0</v>
+        <v>20.0</v>
       </c>
       <c r="H20" t="n">
-        <v>1012.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="21">
@@ -743,19 +743,19 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>3231.0</v>
+        <v>5541.0</v>
       </c>
       <c r="G21" t="n">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="H21" t="n">
-        <v>73.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="22">
@@ -766,22 +766,22 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>5541.0</v>
+        <v>3603.0</v>
       </c>
       <c r="G22" t="n">
-        <v>40.0</v>
+        <v>7.0</v>
       </c>
       <c r="H22" t="n">
-        <v>233.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="23">
@@ -792,7 +792,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -801,13 +801,13 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>3603.0</v>
+        <v>6189.0</v>
       </c>
       <c r="G23" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H23" t="n">
-        <v>208.0</v>
+        <v>572.0</v>
       </c>
     </row>
     <row r="24">
@@ -827,13 +827,13 @@
         <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>7493.0</v>
+        <v>1745.0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" t="n">
-        <v>580.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="25">
@@ -853,13 +853,13 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3411.0</v>
+        <v>3425.0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.0</v>
+        <v>29.0</v>
       </c>
       <c r="H25" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="26">
@@ -870,7 +870,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -879,13 +879,13 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>2820.0</v>
+        <v>705.0</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0</v>
+        <v>396.0</v>
       </c>
     </row>
     <row r="27">
@@ -899,19 +899,19 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
         <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>705.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>396.0</v>
+        <v>314.0</v>
       </c>
     </row>
     <row r="28">
@@ -931,13 +931,13 @@
         <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>3407.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H28" t="n">
-        <v>311.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -951,16 +951,16 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>3405.0</v>
+        <v>20.0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -971,25 +971,25 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
         <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="31">
@@ -1000,22 +1000,22 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>16.0</v>
+        <v>2343.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H31" t="n">
-        <v>12.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="32">
@@ -1035,13 +1035,13 @@
         <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>2343.0</v>
+        <v>1728.0</v>
       </c>
       <c r="G32" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="H32" t="n">
-        <v>143.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="33">
@@ -1061,13 +1061,13 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>1728.0</v>
+        <v>611.0</v>
       </c>
       <c r="G33" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H33" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1075,22 +1075,22 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>611.0</v>
+        <v>679.0</v>
       </c>
       <c r="G34" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1107,13 +1107,13 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>673.0</v>
+        <v>396.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1133,13 +1133,13 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
         <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>392.0</v>
+        <v>34.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1159,13 +1159,13 @@
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>34.0</v>
+        <v>110.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1182,19 +1182,19 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
         <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>110.0</v>
+        <v>629.0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1208,19 +1208,19 @@
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
         <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>629.0</v>
+        <v>1.0</v>
       </c>
       <c r="G39" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1243,7 +1243,7 @@
         <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0</v>
+        <v>131.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1269,10 +1269,10 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>131.0</v>
+        <v>80.0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1289,19 +1289,19 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
         <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>53.0</v>
+        <v>688.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="43">
@@ -1315,19 +1315,19 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E43" t="s">
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>688.0</v>
+        <v>1591.0</v>
       </c>
       <c r="G43" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H43" t="n">
-        <v>41.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="44">
@@ -1341,19 +1341,19 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E44" t="s">
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>1205.0</v>
+        <v>746.0</v>
       </c>
       <c r="G44" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H44" t="n">
-        <v>81.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -1364,22 +1364,22 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>746.0</v>
+        <v>1711.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="46">
@@ -1399,13 +1399,13 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>633.0</v>
+        <v>1578.0</v>
       </c>
       <c r="G46" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1419,16 +1419,16 @@
         <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E47" t="s">
         <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>764.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1445,16 +1445,16 @@
         <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>1477.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1471,19 +1471,19 @@
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E49" t="s">
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>1561.0</v>
+        <v>2816.0</v>
       </c>
       <c r="G49" t="n">
         <v>8.0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="50">
@@ -1497,19 +1497,19 @@
         <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
         <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>2816.0</v>
+        <v>2.0</v>
       </c>
       <c r="G50" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H50" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -1523,16 +1523,16 @@
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
         <v>49</v>
       </c>
       <c r="F51" t="n">
+        <v>1544.0</v>
+      </c>
+      <c r="G51" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1546,19 +1546,19 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>1544.0</v>
+        <v>809.0</v>
       </c>
       <c r="G52" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1575,13 +1575,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
         <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>808.0</v>
+        <v>1.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1601,16 +1601,16 @@
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
         <v>49</v>
       </c>
       <c r="F54" t="n">
+        <v>1314.0</v>
+      </c>
+      <c r="G54" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1621,22 +1621,22 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>1312.0</v>
+        <v>187.0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1653,13 +1653,13 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E56" t="s">
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>171.0</v>
+        <v>2064.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1679,13 +1679,13 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E57" t="s">
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>2046.0</v>
+        <v>560.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1705,13 +1705,13 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>556.0</v>
+        <v>112.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1728,16 +1728,16 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>98.0</v>
+        <v>10.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1754,16 +1754,16 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E60" t="s">
         <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1789,13 +1789,13 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>528.0</v>
+        <v>2129.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="62">
@@ -1806,7 +1806,7 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
         <v>27</v>
@@ -1815,13 +1815,13 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>2142.0</v>
+        <v>839.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H62" t="n">
-        <v>12782.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>199.0</v>
+        <v>125.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1867,10 +1867,10 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>112.0</v>
+        <v>170.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1884,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
         <v>30</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="n">
-        <v>56.0</v>
+        <v>19.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1922,7 +1922,7 @@
         <v>19.0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1933,22 +1933,22 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E67" t="s">
         <v>50</v>
       </c>
       <c r="F67" t="n">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="G67" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1962,16 +1962,16 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E68" t="s">
         <v>50</v>
       </c>
       <c r="F68" t="n">
-        <v>2.0</v>
+        <v>64.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -1991,16 +1991,16 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E69" t="s">
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>63.0</v>
+        <v>2666.0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -2017,19 +2017,19 @@
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>2649.0</v>
+        <v>4178.0</v>
       </c>
       <c r="G70" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="71">
@@ -2043,19 +2043,19 @@
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>4142.0</v>
+        <v>49.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2066,16 +2066,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E72" t="s">
         <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>49.0</v>
+        <v>32.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2101,10 +2101,10 @@
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>32.0</v>
+        <v>24.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2121,16 +2121,16 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
         <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="G74" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2144,16 +2144,16 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E75" t="s">
         <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2179,13 +2179,13 @@
         <v>50</v>
       </c>
       <c r="F76" t="n">
-        <v>6.0</v>
+        <v>74.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="77">
@@ -2196,7 +2196,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
         <v>27</v>
@@ -2205,13 +2205,13 @@
         <v>50</v>
       </c>
       <c r="F77" t="n">
-        <v>74.0</v>
+        <v>134.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2231,10 +2231,10 @@
         <v>50</v>
       </c>
       <c r="F78" t="n">
-        <v>973.0</v>
+        <v>1.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2257,10 +2257,10 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>18.0</v>
+        <v>317.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2274,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
         <v>30</v>
@@ -2283,10 +2283,10 @@
         <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>284.0</v>
+        <v>10.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2303,13 +2303,13 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E81" t="s">
         <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E82" t="s">
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>18.0</v>
+        <v>110.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2361,7 +2361,7 @@
         <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>110.0</v>
+        <v>4.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2375,19 +2375,19 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E84" t="s">
         <v>50</v>
       </c>
       <c r="F84" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2404,16 +2404,16 @@
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>3.0</v>
+        <v>252.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2433,13 +2433,13 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E86" t="s">
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>252.0</v>
+        <v>513.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2459,13 +2459,13 @@
         <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E87" t="s">
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>511.0</v>
+        <v>275.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2485,13 +2485,13 @@
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E88" t="s">
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>271.0</v>
+        <v>1.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2517,7 +2517,7 @@
         <v>50</v>
       </c>
       <c r="F89" t="n">
-        <v>276.0</v>
+        <v>281.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2563,7 +2563,7 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E91" t="s">
         <v>50</v>
@@ -2589,13 +2589,13 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E92" t="s">
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>7410.0</v>
+        <v>7937.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2641,19 +2641,19 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E94" t="s">
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>3865.0</v>
+        <v>3878.0</v>
       </c>
       <c r="G94" t="n">
         <v>1.0</v>
       </c>
       <c r="H94" t="n">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="95">
@@ -2693,13 +2693,13 @@
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E96" t="s">
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>107.0</v>
+        <v>306.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2719,13 +2719,13 @@
         <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E97" t="s">
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2745,16 +2745,16 @@
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E98" t="s">
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>13060.0</v>
+        <v>12913.0</v>
       </c>
       <c r="G98" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2875,7 +2875,7 @@
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E103" t="s">
         <v>50</v>
@@ -2901,13 +2901,13 @@
         <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E104" t="s">
         <v>50</v>
       </c>
       <c r="F104" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>378.0</v>
+        <v>384.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>311.0</v>
+        <v>313.0</v>
       </c>
       <c r="G14" t="n">
         <v>15.0</v>
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="18">
@@ -697,13 +697,13 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>10706.0</v>
+        <v>10722.0</v>
       </c>
       <c r="G19" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1012.0</v>
+        <v>1017.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3231.0</v>
+        <v>3240.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6189.0</v>
+        <v>6192.0</v>
       </c>
       <c r="G23" t="n">
         <v>8.0</v>
@@ -856,7 +856,7 @@
         <v>3425.0</v>
       </c>
       <c r="G25" t="n">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
       <c r="H25" t="n">
         <v>10.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>679.0</v>
+        <v>684.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>396.0</v>
+        <v>403.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1477.0</v>
+        <v>1480.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>2064.0</v>
+        <v>2073.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>560.0</v>
+        <v>564.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>170.0</v>
+        <v>174.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1971,7 +1971,7 @@
         <v>50</v>
       </c>
       <c r="F68" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>2666.0</v>
+        <v>2670.0</v>
       </c>
       <c r="G69" t="n">
         <v>2.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>4178.0</v>
+        <v>4194.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>317.0</v>
+        <v>320.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2335,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12913.0</v>
+        <v>12958.0</v>
       </c>
       <c r="G98" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -437,7 +437,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1413.0</v>
+        <v>1417.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -697,13 +697,13 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>10722.0</v>
+        <v>10729.0</v>
       </c>
       <c r="G19" t="n">
         <v>147.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1017.0</v>
+        <v>1018.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3240.0</v>
+        <v>3244.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>5541.0</v>
+        <v>5543.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6192.0</v>
+        <v>6194.0</v>
       </c>
       <c r="G23" t="n">
         <v>8.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3425.0</v>
+        <v>3426.0</v>
       </c>
       <c r="G25" t="n">
         <v>32.0</v>
@@ -885,7 +885,7 @@
         <v>1.0</v>
       </c>
       <c r="H26" t="n">
-        <v>396.0</v>
+        <v>397.0</v>
       </c>
     </row>
     <row r="27">
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>314.0</v>
+        <v>319.0</v>
       </c>
     </row>
     <row r="28">
@@ -931,7 +931,7 @@
         <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>3407.0</v>
+        <v>3410.0</v>
       </c>
       <c r="G28" t="n">
         <v>3.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>1711.0</v>
+        <v>1712.0</v>
       </c>
       <c r="G45" t="n">
         <v>4.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1480.0</v>
+        <v>1481.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1529,7 +1529,7 @@
         <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>1544.0</v>
+        <v>1554.0</v>
       </c>
       <c r="G51" t="n">
         <v>2.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>809.0</v>
+        <v>810.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1314.0</v>
+        <v>1316.0</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2205,7 +2205,7 @@
         <v>50</v>
       </c>
       <c r="F77" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2699,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>307.0</v>
+        <v>311.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12958.0</v>
+        <v>12971.0</v>
       </c>
       <c r="G98" t="n">
         <v>13.0</v>
@@ -2829,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1094.0</v>
+        <v>1098.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -2907,7 +2907,7 @@
         <v>50</v>
       </c>
       <c r="F104" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="51">
   <si>
     <t>Area</t>
   </si>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>810.0</v>
+        <v>812.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1316.0</v>
+        <v>1320.0</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
@@ -2303,19 +2303,19 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E81" t="s">
         <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="82">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E82" t="s">
         <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>111.0</v>
+        <v>18.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2355,13 +2355,13 @@
         <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E83" t="s">
         <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>4.0</v>
+        <v>111.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2375,19 +2375,19 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E84" t="s">
         <v>50</v>
       </c>
       <c r="F84" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2404,16 +2404,16 @@
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E85" t="s">
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>252.0</v>
+        <v>3.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2433,13 +2433,13 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>513.0</v>
+        <v>252.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2459,13 +2459,13 @@
         <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>276.0</v>
+        <v>513.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2485,13 +2485,13 @@
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E88" t="s">
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>1.0</v>
+        <v>276.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2511,13 +2511,13 @@
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E89" t="s">
         <v>50</v>
       </c>
       <c r="F89" t="n">
-        <v>281.0</v>
+        <v>1.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2534,16 +2534,16 @@
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E90" t="s">
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>14.0</v>
+        <v>281.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2560,16 +2560,16 @@
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
         <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>3982.0</v>
+        <v>14.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2589,19 +2589,19 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>7937.0</v>
+        <v>3982.0</v>
       </c>
       <c r="G92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -2615,19 +2615,19 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E93" t="s">
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>1215.0</v>
+        <v>7937.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H93" t="n">
-        <v>670.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="94">
@@ -2641,19 +2641,19 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E94" t="s">
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>3878.0</v>
+        <v>1215.0</v>
       </c>
       <c r="G94" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H94" t="n">
-        <v>23.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="95">
@@ -2667,19 +2667,19 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
       </c>
       <c r="F95" t="n">
-        <v>75.0</v>
+        <v>3878.0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="96">
@@ -2690,22 +2690,22 @@
         <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E96" t="s">
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>311.0</v>
+        <v>75.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="97">
@@ -2719,19 +2719,19 @@
         <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E97" t="s">
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>150.0</v>
+        <v>311.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="98">
@@ -2745,16 +2745,16 @@
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E98" t="s">
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>12971.0</v>
+        <v>150.0</v>
       </c>
       <c r="G98" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2771,19 +2771,19 @@
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>573.0</v>
+        <v>12971.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H99" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -2797,19 +2797,19 @@
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E100" t="s">
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>4.0</v>
+        <v>573.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="101">
@@ -2823,19 +2823,19 @@
         <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E101" t="s">
         <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>1098.0</v>
+        <v>4.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -2846,22 +2846,22 @@
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E102" t="s">
         <v>50</v>
       </c>
       <c r="F102" t="n">
+        <v>1098.0</v>
+      </c>
+      <c r="G102" t="n">
         <v>1.0</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H102" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="103">
@@ -2872,16 +2872,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E103" t="s">
         <v>50</v>
       </c>
       <c r="F103" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2901,18 +2901,44 @@
         <v>17</v>
       </c>
       <c r="D104" t="s">
+        <v>30</v>
+      </c>
+      <c r="E104" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" t="s">
         <v>31</v>
       </c>
-      <c r="E104" t="s">
-        <v>50</v>
-      </c>
-      <c r="F104" t="n">
+      <c r="E105" t="s">
+        <v>50</v>
+      </c>
+      <c r="F105" t="n">
         <v>45.0</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H104" t="n">
+      <c r="G105" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H105" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -593,13 +593,13 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>3697.0</v>
+        <v>3698.0</v>
       </c>
       <c r="G15" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="H15" t="n">
-        <v>390.0</v>
+        <v>394.0</v>
       </c>
     </row>
     <row r="16">
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="18">
@@ -853,13 +853,13 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3426.0</v>
+        <v>3431.0</v>
       </c>
       <c r="G25" t="n">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="H25" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="26">
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>684.0</v>
+        <v>691.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>1712.0</v>
+        <v>1714.0</v>
       </c>
       <c r="G45" t="n">
         <v>4.0</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>189.0</v>
+        <v>193.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>2073.0</v>
+        <v>2088.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>564.0</v>
+        <v>567.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>112.0</v>
+        <v>117.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1815,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>839.0</v>
+        <v>840.0</v>
       </c>
       <c r="G62" t="n">
         <v>1.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>2670.0</v>
+        <v>2682.0</v>
       </c>
       <c r="G69" t="n">
         <v>2.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>4194.0</v>
+        <v>4198.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>513.0</v>
+        <v>514.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>281.0</v>
+        <v>283.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="G97" t="n">
         <v>1.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>12971.0</v>
+        <v>12993.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>573.0</v>
+        <v>577.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
@@ -2855,7 +2855,7 @@
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>1098.0</v>
+        <v>1099.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -599,7 +599,7 @@
         <v>86.0</v>
       </c>
       <c r="H15" t="n">
-        <v>394.0</v>
+        <v>397.0</v>
       </c>
     </row>
     <row r="16">
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>10729.0</v>
+        <v>10739.0</v>
       </c>
       <c r="G19" t="n">
         <v>147.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3244.0</v>
+        <v>3254.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>5543.0</v>
+        <v>5551.0</v>
       </c>
       <c r="G21" t="n">
         <v>40.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>3603.0</v>
+        <v>3605.0</v>
       </c>
       <c r="G22" t="n">
         <v>7.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6194.0</v>
+        <v>6199.0</v>
       </c>
       <c r="G23" t="n">
         <v>8.0</v>
@@ -853,10 +853,10 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3431.0</v>
+        <v>3433.0</v>
       </c>
       <c r="G25" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="H25" t="n">
         <v>9.0</v>
@@ -1191,7 +1191,7 @@
         <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>629.0</v>
+        <v>630.0</v>
       </c>
       <c r="G38" t="n">
         <v>3.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>1591.0</v>
+        <v>1593.0</v>
       </c>
       <c r="G43" t="n">
         <v>4.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>746.0</v>
+        <v>747.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>1714.0</v>
+        <v>1715.0</v>
       </c>
       <c r="G45" t="n">
         <v>4.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>1578.0</v>
+        <v>1579.0</v>
       </c>
       <c r="G46" t="n">
         <v>2.0</v>
@@ -1529,7 +1529,7 @@
         <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>1554.0</v>
+        <v>1555.0</v>
       </c>
       <c r="G51" t="n">
         <v>2.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>2129.0</v>
+        <v>2148.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2153,7 +2153,7 @@
         <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>3982.0</v>
+        <v>3983.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>7937.0</v>
+        <v>7940.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -2647,7 +2647,7 @@
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>1215.0</v>
+        <v>1218.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2855,7 +2855,7 @@
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>1099.0</v>
+        <v>1100.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>384.0</v>
+        <v>387.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>693.0</v>
+        <v>697.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -547,7 +547,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>313.0</v>
+        <v>314.0</v>
       </c>
       <c r="G14" t="n">
         <v>15.0</v>
@@ -593,13 +593,13 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>3698.0</v>
+        <v>3700.0</v>
       </c>
       <c r="G15" t="n">
         <v>86.0</v>
       </c>
       <c r="H15" t="n">
-        <v>397.0</v>
+        <v>399.0</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +619,13 @@
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>1730.0</v>
+        <v>1731.0</v>
       </c>
       <c r="G16" t="n">
         <v>50.0</v>
       </c>
       <c r="H16" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="17">
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="18">
@@ -671,7 +671,7 @@
         <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>582.0</v>
+        <v>588.0</v>
       </c>
       <c r="G18" t="n">
         <v>17.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3254.0</v>
+        <v>3277.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -749,10 +749,10 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>5551.0</v>
+        <v>5556.0</v>
       </c>
       <c r="G21" t="n">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
       <c r="H21" t="n">
         <v>233.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>691.0</v>
+        <v>698.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1113,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>404.0</v>
+        <v>409.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1165,7 +1165,7 @@
         <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1481.0</v>
+        <v>1483.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>812.0</v>
+        <v>814.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>193.0</v>
+        <v>200.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>2088.0</v>
+        <v>2095.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>567.0</v>
+        <v>569.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>174.0</v>
+        <v>176.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>2682.0</v>
+        <v>2686.0</v>
       </c>
       <c r="G69" t="n">
         <v>2.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>4198.0</v>
+        <v>4220.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>514.0</v>
+        <v>515.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2491,7 +2491,7 @@
         <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>283.0</v>
+        <v>285.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>12993.0</v>
+        <v>13012.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -547,7 +547,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14">
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="18">
@@ -697,13 +697,13 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>10739.0</v>
+        <v>10744.0</v>
       </c>
       <c r="G19" t="n">
         <v>147.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1018.0</v>
+        <v>1019.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3277.0</v>
+        <v>3282.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6199.0</v>
+        <v>6200.0</v>
       </c>
       <c r="G23" t="n">
         <v>8.0</v>
@@ -879,7 +879,7 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>705.0</v>
+        <v>707.0</v>
       </c>
       <c r="G26" t="n">
         <v>1.0</v>
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>319.0</v>
+        <v>323.0</v>
       </c>
     </row>
     <row r="28">
@@ -931,7 +931,7 @@
         <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>3410.0</v>
+        <v>3412.0</v>
       </c>
       <c r="G28" t="n">
         <v>3.0</v>
@@ -957,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>611.0</v>
+        <v>612.0</v>
       </c>
       <c r="G33" t="n">
         <v>4.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>1715.0</v>
+        <v>1716.0</v>
       </c>
       <c r="G45" t="n">
         <v>4.0</v>
@@ -1607,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1320.0</v>
+        <v>1329.0</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
@@ -2205,7 +2205,7 @@
         <v>50</v>
       </c>
       <c r="F77" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>13012.0</v>
+        <v>13029.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>577.0</v>
+        <v>578.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
@@ -2855,7 +2855,7 @@
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>1100.0</v>
+        <v>1108.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -359,7 +359,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>697.0</v>
+        <v>699.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>1271.0</v>
+        <v>1272.0</v>
       </c>
       <c r="G11" t="n">
         <v>5.0</v>
@@ -567,7 +567,7 @@
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
       <c r="G14" t="n">
         <v>15.0</v>
@@ -593,13 +593,13 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>3700.0</v>
+        <v>3702.0</v>
       </c>
       <c r="G15" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="H15" t="n">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="16">
@@ -674,7 +674,7 @@
         <v>588.0</v>
       </c>
       <c r="G18" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>3605.0</v>
+        <v>3609.0</v>
       </c>
       <c r="G22" t="n">
         <v>7.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6200.0</v>
+        <v>6203.0</v>
       </c>
       <c r="G23" t="n">
         <v>8.0</v>
@@ -856,7 +856,7 @@
         <v>3433.0</v>
       </c>
       <c r="G25" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="H25" t="n">
         <v>9.0</v>
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>323.0</v>
+        <v>326.0</v>
       </c>
     </row>
     <row r="28">
@@ -1009,7 +1009,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>2343.0</v>
+        <v>2346.0</v>
       </c>
       <c r="G31" t="n">
         <v>13.0</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>698.0</v>
+        <v>707.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>747.0</v>
+        <v>748.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1483.0</v>
+        <v>1487.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>200.0</v>
+        <v>203.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>2095.0</v>
+        <v>2111.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>569.0</v>
+        <v>571.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>2148.0</v>
+        <v>2154.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>2686.0</v>
+        <v>2699.0</v>
       </c>
       <c r="G69" t="n">
         <v>2.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>4220.0</v>
+        <v>4233.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>323.0</v>
+        <v>324.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2543,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>7940.0</v>
+        <v>7941.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>13029.0</v>
+        <v>13048.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>578.0</v>
+        <v>579.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
@@ -2855,7 +2855,7 @@
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>1108.0</v>
+        <v>1109.0</v>
       </c>
       <c r="G102" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -492,7 +492,7 @@
         <v>1272.0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3282.0</v>
+        <v>3294.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -749,10 +749,10 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>5556.0</v>
+        <v>5561.0</v>
       </c>
       <c r="G21" t="n">
-        <v>36.0</v>
+        <v>42.0</v>
       </c>
       <c r="H21" t="n">
         <v>233.0</v>
@@ -853,7 +853,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3433.0</v>
+        <v>3441.0</v>
       </c>
       <c r="G25" t="n">
         <v>32.0</v>
@@ -1061,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>612.0</v>
+        <v>613.0</v>
       </c>
       <c r="G33" t="n">
         <v>4.0</v>
@@ -1373,7 +1373,7 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>1716.0</v>
+        <v>1717.0</v>
       </c>
       <c r="G45" t="n">
         <v>4.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>1579.0</v>
+        <v>1580.0</v>
       </c>
       <c r="G46" t="n">
         <v>2.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1487.0</v>
+        <v>1488.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="G97" t="n">
         <v>1.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>13048.0</v>
+        <v>13071.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>
@@ -2803,7 +2803,7 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>579.0</v>
+        <v>581.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>10744.0</v>
+        <v>10767.0</v>
       </c>
       <c r="G19" t="n">
         <v>147.0</v>
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3294.0</v>
+        <v>3295.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -749,7 +749,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>5561.0</v>
+        <v>5567.0</v>
       </c>
       <c r="G21" t="n">
         <v>42.0</v>
@@ -775,7 +775,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>3609.0</v>
+        <v>3614.0</v>
       </c>
       <c r="G22" t="n">
         <v>7.0</v>
@@ -879,13 +879,13 @@
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>707.0</v>
+        <v>717.0</v>
       </c>
       <c r="G26" t="n">
         <v>1.0</v>
       </c>
       <c r="H26" t="n">
-        <v>397.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="27">
@@ -1243,7 +1243,7 @@
         <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G41" t="n">
         <v>1.0</v>
@@ -1295,7 +1295,7 @@
         <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>688.0</v>
+        <v>689.0</v>
       </c>
       <c r="G42" t="n">
         <v>3.0</v>
@@ -1321,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>1593.0</v>
+        <v>1594.0</v>
       </c>
       <c r="G43" t="n">
         <v>4.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1488.0</v>
+        <v>1490.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1607,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1329.0</v>
+        <v>1331.0</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
@@ -1789,7 +1789,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>2154.0</v>
+        <v>2166.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>3983.0</v>
+        <v>3984.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2621,7 +2621,7 @@
         <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>7941.0</v>
+        <v>7942.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -2647,7 +2647,7 @@
         <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>1218.0</v>
+        <v>1219.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>13071.0</v>
+        <v>13087.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -281,7 +281,7 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -385,7 +385,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>2130.0</v>
+        <v>2134.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -593,13 +593,13 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>3702.0</v>
+        <v>3720.0</v>
       </c>
       <c r="G15" t="n">
         <v>88.0</v>
       </c>
       <c r="H15" t="n">
-        <v>400.0</v>
+        <v>402.0</v>
       </c>
     </row>
     <row r="16">
@@ -651,7 +651,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="18">
@@ -703,7 +703,7 @@
         <v>147.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1019.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3295.0</v>
+        <v>3311.0</v>
       </c>
       <c r="G20" t="n">
         <v>20.0</v>
@@ -801,7 +801,7 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6203.0</v>
+        <v>6206.0</v>
       </c>
       <c r="G23" t="n">
         <v>8.0</v>
@@ -853,10 +853,10 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3441.0</v>
+        <v>3442.0</v>
       </c>
       <c r="G25" t="n">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="H25" t="n">
         <v>9.0</v>
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>326.0</v>
+        <v>334.0</v>
       </c>
     </row>
     <row r="28">
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>707.0</v>
+        <v>723.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1347,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>748.0</v>
+        <v>749.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1399,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>1580.0</v>
+        <v>1581.0</v>
       </c>
       <c r="G46" t="n">
         <v>2.0</v>
@@ -1451,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1490.0</v>
+        <v>1498.0</v>
       </c>
       <c r="G48" t="n">
         <v>6.0</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>203.0</v>
+        <v>210.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>2111.0</v>
+        <v>2125.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>571.0</v>
+        <v>576.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>119.0</v>
+        <v>126.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1841,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1867,7 +1867,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>177.0</v>
+        <v>179.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1971,7 +1971,7 @@
         <v>50</v>
       </c>
       <c r="F68" t="n">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>2699.0</v>
+        <v>2707.0</v>
       </c>
       <c r="G69" t="n">
         <v>2.0</v>
@@ -2023,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>4233.0</v>
+        <v>4251.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2257,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>324.0</v>
+        <v>325.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2439,7 +2439,7 @@
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>515.0</v>
+        <v>517.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>13087.0</v>
+        <v>13089.0</v>
       </c>
       <c r="G99" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -32,10 +32,10 @@
     <t>Negative</t>
   </si>
   <si>
+    <t>Positive</t>
+  </si>
+  <si>
     <t>Unsuitable for analysis</t>
-  </si>
-  <si>
-    <t>Positive</t>
   </si>
   <si>
     <t>Pl</t>
@@ -281,10 +281,10 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>388.0</v>
+        <v>389.0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0</v>
@@ -310,10 +310,10 @@
         <v>168.0</v>
       </c>
       <c r="G4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -385,13 +385,13 @@
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>2134.0</v>
+        <v>2135.0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="8">
@@ -414,10 +414,10 @@
         <v>761.0</v>
       </c>
       <c r="G8" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>16.0</v>
       </c>
     </row>
     <row r="9">
@@ -437,13 +437,13 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1417.0</v>
+        <v>1419.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H9" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -466,10 +466,10 @@
         <v>1856.0</v>
       </c>
       <c r="G10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H10" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -489,13 +489,13 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>1272.0</v>
+        <v>1275.0</v>
       </c>
       <c r="G11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H11" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -515,7 +515,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>334.0</v>
+        <v>337.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -544,10 +544,10 @@
         <v>141.0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +570,10 @@
         <v>315.0</v>
       </c>
       <c r="G14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H14" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="15">
@@ -593,13 +593,13 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>3720.0</v>
+        <v>3725.0</v>
       </c>
       <c r="G15" t="n">
+        <v>402.0</v>
+      </c>
+      <c r="H15" t="n">
         <v>88.0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>402.0</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         <v>1731.0</v>
       </c>
       <c r="G16" t="n">
-        <v>50.0</v>
+        <v>231.0</v>
       </c>
       <c r="H16" t="n">
-        <v>231.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>46.0</v>
       </c>
       <c r="H17" t="n">
-        <v>46.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -674,10 +674,10 @@
         <v>588.0</v>
       </c>
       <c r="G18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H18" t="n">
         <v>18.0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -700,10 +700,10 @@
         <v>10767.0</v>
       </c>
       <c r="G19" t="n">
+        <v>1021.0</v>
+      </c>
+      <c r="H19" t="n">
         <v>147.0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1021.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,13 +723,13 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>3311.0</v>
+        <v>3318.0</v>
       </c>
       <c r="G20" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="H20" t="n">
         <v>20.0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>73.0</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>5567.0</v>
+        <v>5568.0</v>
       </c>
       <c r="G21" t="n">
+        <v>233.0</v>
+      </c>
+      <c r="H21" t="n">
         <v>42.0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>233.0</v>
       </c>
     </row>
     <row r="22">
@@ -778,10 +778,10 @@
         <v>3614.0</v>
       </c>
       <c r="G22" t="n">
+        <v>208.0</v>
+      </c>
+      <c r="H22" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>208.0</v>
       </c>
     </row>
     <row r="23">
@@ -801,13 +801,13 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>6206.0</v>
+        <v>6207.0</v>
       </c>
       <c r="G23" t="n">
+        <v>572.0</v>
+      </c>
+      <c r="H23" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>572.0</v>
       </c>
     </row>
     <row r="24">
@@ -830,10 +830,10 @@
         <v>1745.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="H24" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -853,13 +853,13 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>3442.0</v>
+        <v>3443.0</v>
       </c>
       <c r="G25" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="H25" t="n">
         <v>31.0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>9.0</v>
       </c>
     </row>
     <row r="26">
@@ -882,10 +882,10 @@
         <v>717.0</v>
       </c>
       <c r="G26" t="n">
+        <v>402.0</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>400.0</v>
       </c>
     </row>
     <row r="27">
@@ -908,10 +908,10 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>334.0</v>
       </c>
       <c r="H27" t="n">
-        <v>334.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -931,13 +931,13 @@
         <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>3412.0</v>
+        <v>3420.0</v>
       </c>
       <c r="G28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H28" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -986,10 +986,10 @@
         <v>16.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H30" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -1012,10 +1012,10 @@
         <v>2346.0</v>
       </c>
       <c r="G31" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="H31" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>143.0</v>
       </c>
     </row>
     <row r="32">
@@ -1038,10 +1038,10 @@
         <v>1728.0</v>
       </c>
       <c r="G32" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H32" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="33">
@@ -1061,13 +1061,13 @@
         <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>613.0</v>
+        <v>614.0</v>
       </c>
       <c r="G33" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H33" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1194,10 +1194,10 @@
         <v>630.0</v>
       </c>
       <c r="G38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H38" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -1272,10 +1272,10 @@
         <v>81.0</v>
       </c>
       <c r="G41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H41" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -1298,10 +1298,10 @@
         <v>689.0</v>
       </c>
       <c r="G42" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="H42" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>41.0</v>
       </c>
     </row>
     <row r="43">
@@ -1324,10 +1324,10 @@
         <v>1594.0</v>
       </c>
       <c r="G43" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="H43" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>86.0</v>
       </c>
     </row>
     <row r="44">
@@ -1373,13 +1373,13 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>1717.0</v>
+        <v>1718.0</v>
       </c>
       <c r="G45" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H45" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="46">
@@ -1399,13 +1399,13 @@
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>1581.0</v>
+        <v>1582.0</v>
       </c>
       <c r="G46" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H46" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1451,13 +1451,13 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>1498.0</v>
+        <v>1499.0</v>
       </c>
       <c r="G48" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H48" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -1477,13 +1477,13 @@
         <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>2816.0</v>
+        <v>2817.0</v>
       </c>
       <c r="G49" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="H49" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>64.0</v>
       </c>
     </row>
     <row r="50">
@@ -1532,10 +1532,10 @@
         <v>1555.0</v>
       </c>
       <c r="G51" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H51" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1555,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>814.0</v>
+        <v>815.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -1607,13 +1607,13 @@
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1331.0</v>
+        <v>1334.0</v>
       </c>
       <c r="G54" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H54" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1659,7 +1659,7 @@
         <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>2125.0</v>
+        <v>2140.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1685,7 +1685,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>576.0</v>
+        <v>579.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1792,10 +1792,10 @@
         <v>2166.0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
       <c r="H61" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1815,13 +1815,13 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>840.0</v>
+        <v>843.0</v>
       </c>
       <c r="G62" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H62" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1870,10 +1870,10 @@
         <v>179.0</v>
       </c>
       <c r="G64" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H64" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1922,10 +1922,10 @@
         <v>19.0</v>
       </c>
       <c r="G66" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H66" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1997,13 +1997,13 @@
         <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>2707.0</v>
+        <v>2716.0</v>
       </c>
       <c r="G69" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H69" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -2023,13 +2023,13 @@
         <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>4251.0</v>
+        <v>4260.0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
       <c r="H70" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2104,10 +2104,10 @@
         <v>24.0</v>
       </c>
       <c r="G73" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H73" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2182,10 +2182,10 @@
         <v>74.0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="H76" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2260,10 +2260,10 @@
         <v>325.0</v>
       </c>
       <c r="G79" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H79" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2312,10 +2312,10 @@
         <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H81" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -2624,10 +2624,10 @@
         <v>7942.0</v>
       </c>
       <c r="G93" t="n">
+        <v>16913.0</v>
+      </c>
+      <c r="H93" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>16913.0</v>
       </c>
     </row>
     <row r="94">
@@ -2650,10 +2650,10 @@
         <v>1219.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
       <c r="H94" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2676,10 +2676,10 @@
         <v>3878.0</v>
       </c>
       <c r="G95" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="H95" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>23.0</v>
       </c>
     </row>
     <row r="96">
@@ -2725,13 +2725,13 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>313.0</v>
+        <v>316.0</v>
       </c>
       <c r="G97" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="H97" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>29.0</v>
       </c>
     </row>
     <row r="98">
@@ -2777,13 +2777,13 @@
         <v>50</v>
       </c>
       <c r="F99" t="n">
-        <v>13089.0</v>
+        <v>13125.0</v>
       </c>
       <c r="G99" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H99" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -2803,13 +2803,13 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>581.0</v>
+        <v>582.0</v>
       </c>
       <c r="G100" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="H100" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>105.0</v>
       </c>
     </row>
     <row r="101">
@@ -2855,13 +2855,13 @@
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>1109.0</v>
+        <v>1112.0</v>
       </c>
       <c r="G102" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H102" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="103">

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="53">
   <si>
     <t>Area</t>
   </si>
@@ -32,12 +32,12 @@
     <t>Negative</t>
   </si>
   <si>
+    <t>Unsuitable for analysis</t>
+  </si>
+  <si>
     <t>Positive</t>
   </si>
   <si>
-    <t>Unsuitable for analysis</t>
-  </si>
-  <si>
     <t>Pl</t>
   </si>
   <si>
@@ -107,9 +107,15 @@
     <t>Lucca</t>
   </si>
   <si>
+    <t>Pisa</t>
+  </si>
+  <si>
     <t>Pistoia</t>
   </si>
   <si>
+    <t>Prato</t>
+  </si>
+  <si>
     <t>Reggio emilia</t>
   </si>
   <si>
@@ -152,7 +158,7 @@
     <t>Vercelli</t>
   </si>
   <si>
-    <t>Pisa</t>
+    <t>Firenze</t>
   </si>
   <si>
     <t>Salerno</t>
@@ -252,10 +258,10 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>46.0</v>
+        <v>103.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -278,13 +284,13 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>389.0</v>
+        <v>411.0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0</v>
@@ -304,16 +310,16 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
         <v>168.0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -330,7 +336,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
         <v>315.0</v>
@@ -356,7 +362,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
         <v>699.0</v>
@@ -382,16 +388,16 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>2135.0</v>
+        <v>1232.0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -408,16 +414,16 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>761.0</v>
+        <v>760.0</v>
       </c>
       <c r="G8" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H8" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="9">
@@ -434,16 +440,16 @@
         <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
         <v>1419.0</v>
       </c>
       <c r="G9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -460,16 +466,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1856.0</v>
+        <v>1857.0</v>
       </c>
       <c r="G10" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="11">
@@ -486,16 +492,16 @@
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>1275.0</v>
+        <v>520.0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H11" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -512,10 +518,10 @@
         <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>337.0</v>
+        <v>721.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -538,13 +544,13 @@
         <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>141.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0</v>
@@ -555,25 +561,25 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>315.0</v>
+        <v>439.0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -581,25 +587,25 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>3725.0</v>
+        <v>94.0</v>
       </c>
       <c r="G15" t="n">
-        <v>402.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" t="n">
-        <v>88.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -613,19 +619,19 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>1731.0</v>
+        <v>110.0</v>
       </c>
       <c r="G16" t="n">
-        <v>231.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -639,19 +645,19 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0</v>
+        <v>362.0</v>
       </c>
       <c r="G17" t="n">
-        <v>46.0</v>
+        <v>15.0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
@@ -665,19 +671,19 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>588.0</v>
+        <v>3725.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>88.0</v>
       </c>
       <c r="H18" t="n">
-        <v>18.0</v>
+        <v>404.0</v>
       </c>
     </row>
     <row r="19">
@@ -688,22 +694,22 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>10767.0</v>
+        <v>1731.0</v>
       </c>
       <c r="G19" t="n">
-        <v>1021.0</v>
+        <v>52.0</v>
       </c>
       <c r="H19" t="n">
-        <v>147.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="20">
@@ -714,22 +720,22 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>3318.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>74.0</v>
+        <v>0.0</v>
       </c>
       <c r="H20" t="n">
-        <v>20.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="21">
@@ -740,22 +746,22 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>5568.0</v>
+        <v>588.0</v>
       </c>
       <c r="G21" t="n">
-        <v>233.0</v>
+        <v>18.0</v>
       </c>
       <c r="H21" t="n">
-        <v>42.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -766,22 +772,22 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3614.0</v>
+        <v>10778.0</v>
       </c>
       <c r="G22" t="n">
-        <v>208.0</v>
+        <v>147.0</v>
       </c>
       <c r="H22" t="n">
-        <v>7.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="23">
@@ -792,22 +798,22 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6207.0</v>
+        <v>3326.0</v>
       </c>
       <c r="G23" t="n">
-        <v>572.0</v>
+        <v>20.0</v>
       </c>
       <c r="H23" t="n">
-        <v>8.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="24">
@@ -818,22 +824,22 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>1745.0</v>
+        <v>6538.0</v>
       </c>
       <c r="G24" t="n">
-        <v>19.0</v>
+        <v>41.0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="25">
@@ -844,22 +850,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>3443.0</v>
+        <v>3614.0</v>
       </c>
       <c r="G25" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="H25" t="n">
-        <v>31.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="26">
@@ -870,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>717.0</v>
+        <v>6207.0</v>
       </c>
       <c r="G26" t="n">
-        <v>402.0</v>
+        <v>8.0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0</v>
+        <v>572.0</v>
       </c>
     </row>
     <row r="27">
@@ -896,22 +902,22 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0</v>
+        <v>1745.0</v>
       </c>
       <c r="G27" t="n">
-        <v>334.0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="28">
@@ -922,22 +928,22 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>3420.0</v>
+        <v>4560.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="29">
@@ -951,19 +957,19 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>21.0</v>
+        <v>1074.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0</v>
+        <v>402.0</v>
       </c>
     </row>
     <row r="30">
@@ -971,25 +977,25 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="31">
@@ -997,25 +1003,25 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>2346.0</v>
+        <v>3420.0</v>
       </c>
       <c r="G31" t="n">
-        <v>143.0</v>
+        <v>3.0</v>
       </c>
       <c r="H31" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -1023,25 +1029,25 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>1728.0</v>
+        <v>1064.0</v>
       </c>
       <c r="G32" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="33">
@@ -1052,22 +1058,22 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F33" t="n">
-        <v>614.0</v>
+        <v>16.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
       </c>
       <c r="H33" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="34">
@@ -1075,25 +1081,25 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F34" t="n">
-        <v>723.0</v>
+        <v>2346.0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="35">
@@ -1101,25 +1107,25 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F35" t="n">
-        <v>409.0</v>
+        <v>1728.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="36">
@@ -1127,22 +1133,22 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>34.0</v>
+        <v>614.0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1159,13 +1165,13 @@
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>112.0</v>
+        <v>556.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1182,22 +1188,22 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>630.0</v>
+        <v>340.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -1208,16 +1214,16 @@
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F39" t="n">
-        <v>1.0</v>
+        <v>34.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1234,16 +1240,16 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F40" t="n">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1260,22 +1266,22 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>81.0</v>
+        <v>567.0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -1289,19 +1295,19 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>689.0</v>
+        <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -1315,19 +1321,19 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>1594.0</v>
+        <v>132.0</v>
       </c>
       <c r="G43" t="n">
-        <v>86.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -1344,13 +1350,13 @@
         <v>41</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>749.0</v>
+        <v>81.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1364,22 +1370,22 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>1718.0</v>
+        <v>689.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H45" t="n">
-        <v>4.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="46">
@@ -1390,22 +1396,22 @@
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F46" t="n">
-        <v>1582.0</v>
+        <v>1594.0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="47">
@@ -1416,16 +1422,16 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>749.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1445,19 +1451,19 @@
         <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F48" t="n">
-        <v>1499.0</v>
+        <v>1718.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H48" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="49">
@@ -1471,19 +1477,19 @@
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>2817.0</v>
+        <v>1582.0</v>
       </c>
       <c r="G49" t="n">
-        <v>64.0</v>
+        <v>2.0</v>
       </c>
       <c r="H49" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1500,10 +1506,10 @@
         <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F50" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -1523,19 +1529,19 @@
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>1555.0</v>
+        <v>1150.0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1546,22 +1552,22 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>815.0</v>
+        <v>2817.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="53">
@@ -1572,16 +1578,16 @@
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
         <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1598,22 +1604,22 @@
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1334.0</v>
+        <v>1555.0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1621,19 +1627,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>211.0</v>
+        <v>1.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1647,19 +1653,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F56" t="n">
-        <v>2140.0</v>
+        <v>77.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1673,19 +1679,19 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>579.0</v>
+        <v>12.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1705,13 +1711,13 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F58" t="n">
-        <v>128.0</v>
+        <v>21.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1728,16 +1734,16 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E59" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F59" t="n">
-        <v>10.0</v>
+        <v>199.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1754,16 +1760,16 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F60" t="n">
-        <v>1.0</v>
+        <v>2140.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1780,19 +1786,19 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F61" t="n">
-        <v>2166.0</v>
+        <v>579.0</v>
       </c>
       <c r="G61" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1806,22 +1812,22 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F62" t="n">
-        <v>843.0</v>
+        <v>128.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1832,16 +1838,16 @@
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F63" t="n">
-        <v>128.0</v>
+        <v>9.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1858,22 +1864,22 @@
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>179.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1884,22 +1890,22 @@
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>19.0</v>
+        <v>2166.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="66">
@@ -1910,22 +1916,22 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D66" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>19.0</v>
+        <v>843.0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1933,19 +1939,19 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D67" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>2.0</v>
+        <v>128.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1959,22 +1965,22 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E68" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>68.0</v>
+        <v>954.0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1985,25 +1991,25 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E69" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>2716.0</v>
+        <v>28.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
       </c>
       <c r="H69" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -2011,22 +2017,22 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F70" t="n">
-        <v>4260.0</v>
+        <v>24.0</v>
       </c>
       <c r="G70" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2037,19 +2043,19 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E71" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>50.0</v>
+        <v>17.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2066,16 +2072,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E72" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F72" t="n">
-        <v>32.0</v>
+        <v>2.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2092,22 +2098,22 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2118,16 +2124,16 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>27.0</v>
+        <v>82.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2144,19 +2150,19 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E75" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F75" t="n">
-        <v>7.0</v>
+        <v>2716.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2170,22 +2176,22 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E76" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F76" t="n">
-        <v>74.0</v>
+        <v>4260.0</v>
       </c>
       <c r="G76" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="77">
@@ -2196,16 +2202,16 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F77" t="n">
-        <v>136.0</v>
+        <v>50.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2222,16 +2228,16 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F78" t="n">
-        <v>1.0</v>
+        <v>32.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2248,22 +2254,22 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E79" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>325.0</v>
+        <v>24.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2274,16 +2280,16 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E80" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2300,19 +2306,19 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G81" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2326,22 +2332,22 @@
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F82" t="n">
-        <v>18.0</v>
+        <v>74.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="83">
@@ -2349,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
         <v>16</v>
@@ -2358,10 +2364,10 @@
         <v>27</v>
       </c>
       <c r="E83" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F83" t="n">
-        <v>111.0</v>
+        <v>136.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2375,7 +2381,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
         <v>16</v>
@@ -2384,10 +2390,10 @@
         <v>28</v>
       </c>
       <c r="E84" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F84" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2401,22 +2407,22 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>3.0</v>
+        <v>328.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2427,19 +2433,19 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F86" t="n">
-        <v>253.0</v>
+        <v>17.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2453,25 +2459,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E87" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F87" t="n">
-        <v>517.0</v>
+        <v>0.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="88">
@@ -2479,19 +2485,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E88" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F88" t="n">
-        <v>277.0</v>
+        <v>19.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2505,25 +2511,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E89" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F89" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G89" t="n">
         <v>1.0</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="90">
@@ -2531,19 +2537,19 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>286.0</v>
+        <v>111.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2557,19 +2563,19 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E91" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F91" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2586,16 +2592,16 @@
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E92" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F92" t="n">
-        <v>3984.0</v>
+        <v>3.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2612,22 +2618,22 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F93" t="n">
-        <v>7942.0</v>
+        <v>231.0</v>
       </c>
       <c r="G93" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -2638,19 +2644,19 @@
         <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F94" t="n">
-        <v>1219.0</v>
+        <v>515.0</v>
       </c>
       <c r="G94" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2664,22 +2670,22 @@
         <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E95" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F95" t="n">
-        <v>3878.0</v>
+        <v>277.0</v>
       </c>
       <c r="G95" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
       <c r="H95" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -2690,16 +2696,16 @@
         <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F96" t="n">
-        <v>75.0</v>
+        <v>1.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2716,22 +2722,22 @@
         <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F97" t="n">
-        <v>316.0</v>
+        <v>286.0</v>
       </c>
       <c r="G97" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="98">
@@ -2742,16 +2748,16 @@
         <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E98" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F98" t="n">
-        <v>150.0</v>
+        <v>13.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2768,22 +2774,22 @@
         <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E99" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F99" t="n">
-        <v>13125.0</v>
+        <v>3984.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
       </c>
       <c r="H99" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -2794,22 +2800,22 @@
         <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E100" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F100" t="n">
-        <v>582.0</v>
+        <v>7942.0</v>
       </c>
       <c r="G100" t="n">
-        <v>105.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
-        <v>1.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="101">
@@ -2820,22 +2826,22 @@
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E101" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F101" t="n">
-        <v>4.0</v>
+        <v>1219.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="102">
@@ -2846,22 +2852,22 @@
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E102" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F102" t="n">
-        <v>1112.0</v>
+        <v>3878.0</v>
       </c>
       <c r="G102" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
-        <v>1.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="103">
@@ -2872,16 +2878,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E103" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>75.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2898,22 +2904,22 @@
         <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E104" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F104" t="n">
-        <v>20.0</v>
+        <v>316.0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="105">
@@ -2924,21 +2930,177 @@
         <v>12</v>
       </c>
       <c r="C105" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" t="s">
+        <v>52</v>
+      </c>
+      <c r="F105" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" t="s">
+        <v>52</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12370.0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" t="s">
+        <v>45</v>
+      </c>
+      <c r="E107" t="s">
+        <v>52</v>
+      </c>
+      <c r="F107" t="n">
+        <v>582.0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" t="s">
+        <v>46</v>
+      </c>
+      <c r="E108" t="s">
+        <v>52</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" t="s">
+        <v>47</v>
+      </c>
+      <c r="E109" t="s">
+        <v>52</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1112.0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" t="s">
+        <v>50</v>
+      </c>
+      <c r="E110" t="s">
+        <v>52</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" t="s">
         <v>17</v>
       </c>
-      <c r="D105" t="s">
-        <v>31</v>
-      </c>
-      <c r="E105" t="s">
-        <v>50</v>
-      </c>
-      <c r="F105" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H105" t="n">
+      <c r="D111" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111" t="s">
+        <v>52</v>
+      </c>
+      <c r="F111" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H111" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>721.0</v>
+        <v>722.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -573,7 +573,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>439.0</v>
+        <v>444.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -865,7 +865,7 @@
         <v>7.0</v>
       </c>
       <c r="H25" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="26">
@@ -995,7 +995,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
     </row>
     <row r="31">
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>1064.0</v>
+        <v>1066.0</v>
       </c>
       <c r="G32" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>103.0</v>
+        <v>128.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>411.0</v>
+        <v>413.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>699.0</v>
+        <v>703.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>110.0</v>
+        <v>116.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -651,13 +651,13 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>362.0</v>
+        <v>363.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="18">
@@ -677,7 +677,7 @@
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>3725.0</v>
+        <v>3735.0</v>
       </c>
       <c r="G18" t="n">
         <v>88.0</v>
@@ -703,7 +703,7 @@
         <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>1731.0</v>
+        <v>1734.0</v>
       </c>
       <c r="G19" t="n">
         <v>52.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>588.0</v>
+        <v>602.0</v>
       </c>
       <c r="G21" t="n">
         <v>18.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>10778.0</v>
+        <v>10786.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>3326.0</v>
+        <v>3330.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>6538.0</v>
+        <v>6539.0</v>
       </c>
       <c r="G24" t="n">
         <v>41.0</v>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>4560.0</v>
+        <v>4562.0</v>
       </c>
       <c r="G28" t="n">
         <v>35.0</v>
@@ -1145,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>614.0</v>
+        <v>615.0</v>
       </c>
       <c r="G36" t="n">
         <v>4.0</v>
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>556.0</v>
+        <v>582.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1197,7 +1197,7 @@
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>340.0</v>
+        <v>342.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>567.0</v>
+        <v>568.0</v>
       </c>
       <c r="G41" t="n">
         <v>3.0</v>
@@ -1535,7 +1535,7 @@
         <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>1150.0</v>
+        <v>1152.0</v>
       </c>
       <c r="G51" t="n">
         <v>5.0</v>
@@ -1743,7 +1743,7 @@
         <v>52</v>
       </c>
       <c r="F59" t="n">
-        <v>199.0</v>
+        <v>206.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1769,7 +1769,7 @@
         <v>52</v>
       </c>
       <c r="F60" t="n">
-        <v>2140.0</v>
+        <v>2148.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1795,7 +1795,7 @@
         <v>52</v>
       </c>
       <c r="F61" t="n">
-        <v>579.0</v>
+        <v>581.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>954.0</v>
+        <v>957.0</v>
       </c>
       <c r="G68" t="n">
         <v>1.0</v>
@@ -2159,7 +2159,7 @@
         <v>52</v>
       </c>
       <c r="F75" t="n">
-        <v>2716.0</v>
+        <v>2722.0</v>
       </c>
       <c r="G75" t="n">
         <v>2.0</v>
@@ -2185,7 +2185,7 @@
         <v>52</v>
       </c>
       <c r="F76" t="n">
-        <v>4260.0</v>
+        <v>4265.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2419,7 +2419,7 @@
         <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>328.0</v>
+        <v>332.0</v>
       </c>
       <c r="G85" t="n">
         <v>1.0</v>
@@ -2653,7 +2653,7 @@
         <v>52</v>
       </c>
       <c r="F94" t="n">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12370.0</v>
+        <v>12389.0</v>
       </c>
       <c r="G106" t="n">
         <v>13.0</v>
@@ -2991,7 +2991,7 @@
         <v>52</v>
       </c>
       <c r="F107" t="n">
-        <v>582.0</v>
+        <v>585.0</v>
       </c>
       <c r="G107" t="n">
         <v>1.0</v>
@@ -3043,7 +3043,7 @@
         <v>52</v>
       </c>
       <c r="F109" t="n">
-        <v>1112.0</v>
+        <v>1119.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -391,7 +391,7 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>1232.0</v>
+        <v>1233.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -443,7 +443,7 @@
         <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>1419.0</v>
+        <v>1420.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -683,7 +683,7 @@
         <v>88.0</v>
       </c>
       <c r="H18" t="n">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
     </row>
     <row r="19">
@@ -709,7 +709,7 @@
         <v>52.0</v>
       </c>
       <c r="H19" t="n">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="20">
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>10786.0</v>
+        <v>10793.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>3330.0</v>
+        <v>3331.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>6539.0</v>
+        <v>6546.0</v>
       </c>
       <c r="G24" t="n">
         <v>41.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>3614.0</v>
+        <v>3619.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>1745.0</v>
+        <v>1746.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>4562.0</v>
+        <v>4564.0</v>
       </c>
       <c r="G28" t="n">
         <v>35.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1379,7 +1379,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>689.0</v>
+        <v>690.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1431,7 +1431,7 @@
         <v>51</v>
       </c>
       <c r="F47" t="n">
-        <v>749.0</v>
+        <v>751.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1457,7 +1457,7 @@
         <v>51</v>
       </c>
       <c r="F48" t="n">
-        <v>1718.0</v>
+        <v>1720.0</v>
       </c>
       <c r="G48" t="n">
         <v>4.0</v>
@@ -1483,7 +1483,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>1582.0</v>
+        <v>1583.0</v>
       </c>
       <c r="G49" t="n">
         <v>2.0</v>
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1555.0</v>
+        <v>1556.0</v>
       </c>
       <c r="G54" t="n">
         <v>2.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>2166.0</v>
+        <v>2181.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2783,7 +2783,7 @@
         <v>52</v>
       </c>
       <c r="F99" t="n">
-        <v>3984.0</v>
+        <v>3987.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2809,7 +2809,7 @@
         <v>52</v>
       </c>
       <c r="F100" t="n">
-        <v>7942.0</v>
+        <v>7945.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
@@ -2835,7 +2835,7 @@
         <v>52</v>
       </c>
       <c r="F101" t="n">
-        <v>1219.0</v>
+        <v>1220.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12389.0</v>
+        <v>12410.0</v>
       </c>
       <c r="G106" t="n">
         <v>13.0</v>
@@ -2991,7 +2991,7 @@
         <v>52</v>
       </c>
       <c r="F107" t="n">
-        <v>585.0</v>
+        <v>587.0</v>
       </c>
       <c r="G107" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -495,7 +495,7 @@
         <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>722.0</v>
+        <v>724.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -573,7 +573,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>444.0</v>
+        <v>447.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -599,7 +599,7 @@
         <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -677,7 +677,7 @@
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>3735.0</v>
+        <v>3737.0</v>
       </c>
       <c r="G18" t="n">
         <v>88.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>602.0</v>
+        <v>605.0</v>
       </c>
       <c r="G21" t="n">
         <v>18.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>3331.0</v>
+        <v>3339.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>6546.0</v>
+        <v>6547.0</v>
       </c>
       <c r="G24" t="n">
         <v>41.0</v>
@@ -937,10 +937,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>4564.0</v>
+        <v>4573.0</v>
       </c>
       <c r="G28" t="n">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="H28" t="n">
         <v>9.0</v>
@@ -963,7 +963,7 @@
         <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>1074.0</v>
+        <v>1077.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>3420.0</v>
+        <v>3421.0</v>
       </c>
       <c r="G31" t="n">
         <v>3.0</v>
@@ -1041,13 +1041,13 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>1066.0</v>
+        <v>1073.0</v>
       </c>
       <c r="G32" t="n">
         <v>1.0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="33">
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>582.0</v>
+        <v>583.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1457,7 +1457,7 @@
         <v>51</v>
       </c>
       <c r="F48" t="n">
-        <v>1720.0</v>
+        <v>1723.0</v>
       </c>
       <c r="G48" t="n">
         <v>4.0</v>
@@ -1483,7 +1483,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>1583.0</v>
+        <v>1586.0</v>
       </c>
       <c r="G49" t="n">
         <v>2.0</v>
@@ -1535,7 +1535,7 @@
         <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>1152.0</v>
+        <v>1154.0</v>
       </c>
       <c r="G51" t="n">
         <v>5.0</v>
@@ -1665,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="F56" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1743,7 +1743,7 @@
         <v>52</v>
       </c>
       <c r="F59" t="n">
-        <v>206.0</v>
+        <v>213.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1769,7 +1769,7 @@
         <v>52</v>
       </c>
       <c r="F60" t="n">
-        <v>2148.0</v>
+        <v>2149.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1795,7 +1795,7 @@
         <v>52</v>
       </c>
       <c r="F61" t="n">
-        <v>581.0</v>
+        <v>585.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1821,7 +1821,7 @@
         <v>52</v>
       </c>
       <c r="F62" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>957.0</v>
+        <v>958.0</v>
       </c>
       <c r="G68" t="n">
         <v>1.0</v>
@@ -2159,7 +2159,7 @@
         <v>52</v>
       </c>
       <c r="F75" t="n">
-        <v>2722.0</v>
+        <v>2728.0</v>
       </c>
       <c r="G75" t="n">
         <v>2.0</v>
@@ -2185,7 +2185,7 @@
         <v>52</v>
       </c>
       <c r="F76" t="n">
-        <v>4265.0</v>
+        <v>4280.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2679,7 +2679,7 @@
         <v>52</v>
       </c>
       <c r="F95" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12410.0</v>
+        <v>12429.0</v>
       </c>
       <c r="G106" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1857.0</v>
+        <v>1862.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -599,7 +599,7 @@
         <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>605.0</v>
+        <v>606.0</v>
       </c>
       <c r="G21" t="n">
         <v>18.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>10793.0</v>
+        <v>10798.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -813,7 +813,7 @@
         <v>20.0</v>
       </c>
       <c r="H23" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="24">
@@ -839,7 +839,7 @@
         <v>41.0</v>
       </c>
       <c r="H24" t="n">
-        <v>233.0</v>
+        <v>238.0</v>
       </c>
     </row>
     <row r="25">
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>1746.0</v>
+        <v>1747.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -937,10 +937,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>4573.0</v>
+        <v>4588.0</v>
       </c>
       <c r="G28" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="H28" t="n">
         <v>9.0</v>
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>1073.0</v>
+        <v>1084.0</v>
       </c>
       <c r="G32" t="n">
         <v>1.0</v>
@@ -1145,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>615.0</v>
+        <v>616.0</v>
       </c>
       <c r="G36" t="n">
         <v>4.0</v>
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>583.0</v>
+        <v>585.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1457,7 +1457,7 @@
         <v>51</v>
       </c>
       <c r="F48" t="n">
-        <v>1723.0</v>
+        <v>1725.0</v>
       </c>
       <c r="G48" t="n">
         <v>4.0</v>
@@ -1561,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>2817.0</v>
+        <v>2818.0</v>
       </c>
       <c r="G52" t="n">
         <v>8.0</v>
@@ -1743,7 +1743,7 @@
         <v>52</v>
       </c>
       <c r="F59" t="n">
-        <v>213.0</v>
+        <v>218.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1795,7 +1795,7 @@
         <v>52</v>
       </c>
       <c r="F61" t="n">
-        <v>585.0</v>
+        <v>586.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>958.0</v>
+        <v>962.0</v>
       </c>
       <c r="G68" t="n">
         <v>1.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2185,7 +2185,7 @@
         <v>52</v>
       </c>
       <c r="F76" t="n">
-        <v>4280.0</v>
+        <v>4287.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2627,7 +2627,7 @@
         <v>52</v>
       </c>
       <c r="F93" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2913,7 +2913,7 @@
         <v>52</v>
       </c>
       <c r="F104" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G104" t="n">
         <v>1.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12429.0</v>
+        <v>12438.0</v>
       </c>
       <c r="G106" t="n">
         <v>13.0</v>
@@ -2991,7 +2991,7 @@
         <v>52</v>
       </c>
       <c r="F107" t="n">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="G107" t="n">
         <v>1.0</v>
@@ -3043,7 +3043,7 @@
         <v>52</v>
       </c>
       <c r="F109" t="n">
-        <v>1119.0</v>
+        <v>1123.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -391,7 +391,7 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>1233.0</v>
+        <v>1234.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1862.0</v>
+        <v>1863.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>724.0</v>
+        <v>725.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -735,7 +735,7 @@
         <v>0.0</v>
       </c>
       <c r="H20" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>3339.0</v>
+        <v>3341.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>6547.0</v>
+        <v>6555.0</v>
       </c>
       <c r="G24" t="n">
         <v>41.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>3619.0</v>
+        <v>3623.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -995,7 +995,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>338.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="31">
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>3421.0</v>
+        <v>3428.0</v>
       </c>
       <c r="G31" t="n">
         <v>3.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>134.0</v>
+        <v>137.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1535,7 +1535,7 @@
         <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>1154.0</v>
+        <v>1155.0</v>
       </c>
       <c r="G51" t="n">
         <v>5.0</v>
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1556.0</v>
+        <v>1557.0</v>
       </c>
       <c r="G54" t="n">
         <v>2.0</v>
@@ -1665,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="F56" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>2181.0</v>
+        <v>2186.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>962.0</v>
+        <v>968.0</v>
       </c>
       <c r="G68" t="n">
         <v>1.0</v>
@@ -2419,7 +2419,7 @@
         <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="G85" t="n">
         <v>1.0</v>
@@ -2783,7 +2783,7 @@
         <v>52</v>
       </c>
       <c r="F99" t="n">
-        <v>3987.0</v>
+        <v>3988.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2913,7 +2913,7 @@
         <v>52</v>
       </c>
       <c r="F104" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G104" t="n">
         <v>1.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12438.0</v>
+        <v>12456.0</v>
       </c>
       <c r="G106" t="n">
         <v>13.0</v>
@@ -2991,7 +2991,7 @@
         <v>52</v>
       </c>
       <c r="F107" t="n">
-        <v>588.0</v>
+        <v>589.0</v>
       </c>
       <c r="G107" t="n">
         <v>1.0</v>
@@ -3043,7 +3043,7 @@
         <v>52</v>
       </c>
       <c r="F109" t="n">
-        <v>1123.0</v>
+        <v>1127.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>725.0</v>
+        <v>727.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -573,7 +573,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>447.0</v>
+        <v>452.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>1084.0</v>
+        <v>1085.0</v>
       </c>
       <c r="G32" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="53">
   <si>
     <t>Area</t>
   </si>
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>703.0</v>
+        <v>705.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1863.0</v>
+        <v>1866.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -619,19 +619,19 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>116.0</v>
+        <v>320.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="17">
@@ -645,19 +645,19 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>363.0</v>
+        <v>3724.0</v>
       </c>
       <c r="G17" t="n">
-        <v>15.0</v>
+        <v>88.0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.0</v>
+        <v>405.0</v>
       </c>
     </row>
     <row r="18">
@@ -671,19 +671,19 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>3737.0</v>
+        <v>1734.0</v>
       </c>
       <c r="G18" t="n">
-        <v>88.0</v>
+        <v>52.0</v>
       </c>
       <c r="H18" t="n">
-        <v>405.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="19">
@@ -697,19 +697,19 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
         <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>1734.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
       <c r="H19" t="n">
-        <v>232.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,19 +723,19 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
         <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0</v>
+        <v>604.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H20" t="n">
-        <v>47.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -746,22 +746,22 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>606.0</v>
+        <v>10798.0</v>
       </c>
       <c r="G21" t="n">
-        <v>18.0</v>
+        <v>147.0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="22">
@@ -775,19 +775,19 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>10798.0</v>
+        <v>3343.0</v>
       </c>
       <c r="G22" t="n">
-        <v>147.0</v>
+        <v>20.0</v>
       </c>
       <c r="H22" t="n">
-        <v>1021.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="23">
@@ -801,19 +801,19 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>3341.0</v>
+        <v>6555.0</v>
       </c>
       <c r="G23" t="n">
-        <v>20.0</v>
+        <v>41.0</v>
       </c>
       <c r="H23" t="n">
-        <v>76.0</v>
+        <v>238.0</v>
       </c>
     </row>
     <row r="24">
@@ -824,22 +824,22 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>6555.0</v>
+        <v>3623.0</v>
       </c>
       <c r="G24" t="n">
-        <v>41.0</v>
+        <v>7.0</v>
       </c>
       <c r="H24" t="n">
-        <v>238.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="25">
@@ -850,22 +850,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>3623.0</v>
+        <v>6207.0</v>
       </c>
       <c r="G25" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" t="n">
-        <v>209.0</v>
+        <v>572.0</v>
       </c>
     </row>
     <row r="26">
@@ -879,19 +879,19 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>6207.0</v>
+        <v>1747.0</v>
       </c>
       <c r="G26" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" t="n">
-        <v>572.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="27">
@@ -905,19 +905,19 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>1747.0</v>
+        <v>4589.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H27" t="n">
-        <v>19.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="28">
@@ -928,22 +928,22 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>4588.0</v>
+        <v>977.0</v>
       </c>
       <c r="G28" t="n">
-        <v>32.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.0</v>
+        <v>402.0</v>
       </c>
     </row>
     <row r="29">
@@ -957,19 +957,19 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
         <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>1077.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>402.0</v>
+        <v>194.0</v>
       </c>
     </row>
     <row r="30">
@@ -983,19 +983,19 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0</v>
+        <v>2063.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H30" t="n">
-        <v>343.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -1003,22 +1003,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>3428.0</v>
+        <v>116.0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1029,25 +1029,25 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>1085.0</v>
+        <v>43.0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
@@ -1058,22 +1058,22 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
         <v>51</v>
       </c>
       <c r="F33" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
       </c>
       <c r="H33" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1084,22 +1084,22 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
         <v>51</v>
       </c>
       <c r="F34" t="n">
-        <v>2346.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H34" t="n">
-        <v>143.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -1110,22 +1110,22 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
         <v>51</v>
       </c>
       <c r="F35" t="n">
-        <v>1728.0</v>
+        <v>16.0</v>
       </c>
       <c r="G35" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="36">
@@ -1139,19 +1139,19 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>616.0</v>
+        <v>2346.0</v>
       </c>
       <c r="G36" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="37">
@@ -1159,25 +1159,25 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>585.0</v>
+        <v>1728.0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="38">
@@ -1185,22 +1185,22 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>342.0</v>
+        <v>617.0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1211,19 +1211,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>51</v>
       </c>
       <c r="F39" t="n">
-        <v>34.0</v>
+        <v>100.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1237,25 +1237,25 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
         <v>51</v>
       </c>
       <c r="F40" t="n">
-        <v>112.0</v>
+        <v>0.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="41">
@@ -1263,22 +1263,22 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E41" t="s">
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>568.0</v>
+        <v>1365.0</v>
       </c>
       <c r="G41" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1289,25 +1289,25 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E42" t="s">
         <v>51</v>
       </c>
       <c r="F42" t="n">
+        <v>1085.0</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.0</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H42" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="43">
@@ -1318,16 +1318,16 @@
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>137.0</v>
+        <v>585.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1344,19 +1344,19 @@
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>81.0</v>
+        <v>342.0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1370,22 +1370,22 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
         <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>690.0</v>
+        <v>34.0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H45" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1396,22 +1396,22 @@
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
         <v>51</v>
       </c>
       <c r="F46" t="n">
-        <v>1594.0</v>
+        <v>112.0</v>
       </c>
       <c r="G46" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H46" t="n">
-        <v>86.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1422,19 +1422,19 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E47" t="s">
         <v>51</v>
       </c>
       <c r="F47" t="n">
-        <v>751.0</v>
+        <v>568.0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1448,22 +1448,22 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E48" t="s">
         <v>51</v>
       </c>
       <c r="F48" t="n">
-        <v>1725.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -1474,19 +1474,19 @@
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E49" t="s">
         <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>1586.0</v>
+        <v>137.0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1500,19 +1500,19 @@
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E50" t="s">
         <v>51</v>
       </c>
       <c r="F50" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1526,22 +1526,22 @@
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E51" t="s">
         <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>1155.0</v>
+        <v>690.0</v>
       </c>
       <c r="G51" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="52">
@@ -1552,22 +1552,22 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
         <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>2818.0</v>
+        <v>1594.0</v>
       </c>
       <c r="G52" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H52" t="n">
-        <v>64.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="53">
@@ -1578,16 +1578,16 @@
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E53" t="s">
         <v>51</v>
       </c>
       <c r="F53" t="n">
-        <v>2.0</v>
+        <v>751.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1607,19 +1607,19 @@
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1557.0</v>
+        <v>1725.0</v>
       </c>
       <c r="G54" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="55">
@@ -1630,19 +1630,19 @@
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E55" t="s">
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1.0</v>
+        <v>1587.0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1656,16 +1656,16 @@
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E56" t="s">
         <v>51</v>
       </c>
       <c r="F56" t="n">
-        <v>79.0</v>
+        <v>1.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1682,19 +1682,19 @@
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E57" t="s">
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>13.0</v>
+        <v>1157.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1705,25 +1705,25 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>21.0</v>
+        <v>2818.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="59">
@@ -1731,19 +1731,19 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F59" t="n">
-        <v>218.0</v>
+        <v>2.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -1757,22 +1757,22 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F60" t="n">
-        <v>2149.0</v>
+        <v>1560.0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1783,19 +1783,19 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F61" t="n">
-        <v>586.0</v>
+        <v>1.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1809,19 +1809,19 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F62" t="n">
-        <v>129.0</v>
+        <v>79.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1835,19 +1835,19 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F63" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1864,16 +1864,16 @@
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E64" t="s">
         <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1890,22 +1890,22 @@
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E65" t="s">
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>2186.0</v>
+        <v>221.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
       </c>
       <c r="H65" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1916,19 +1916,19 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>843.0</v>
+        <v>2168.0</v>
       </c>
       <c r="G66" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1942,16 +1942,16 @@
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>129.0</v>
+        <v>589.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1968,19 +1968,19 @@
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>968.0</v>
+        <v>131.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1994,16 +1994,16 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
         <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>28.0</v>
+        <v>9.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2020,16 +2020,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E70" t="s">
         <v>52</v>
       </c>
       <c r="F70" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2046,22 +2046,22 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
         <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>17.0</v>
+        <v>2186.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="72">
@@ -2069,22 +2069,22 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
         <v>52</v>
       </c>
       <c r="F72" t="n">
-        <v>2.0</v>
+        <v>843.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2095,19 +2095,19 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
         <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>1.0</v>
+        <v>129.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2121,22 +2121,22 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E74" t="s">
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>83.0</v>
+        <v>971.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2147,22 +2147,22 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E75" t="s">
         <v>52</v>
       </c>
       <c r="F75" t="n">
-        <v>2728.0</v>
+        <v>28.0</v>
       </c>
       <c r="G75" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2173,25 +2173,25 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E76" t="s">
         <v>52</v>
       </c>
       <c r="F76" t="n">
-        <v>4287.0</v>
+        <v>24.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2199,19 +2199,19 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E77" t="s">
         <v>52</v>
       </c>
       <c r="F77" t="n">
-        <v>50.0</v>
+        <v>17.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2228,16 +2228,16 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E78" t="s">
         <v>52</v>
       </c>
       <c r="F78" t="n">
-        <v>32.0</v>
+        <v>2.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2254,19 +2254,19 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E79" t="s">
         <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>24.0</v>
+        <v>69.0</v>
       </c>
       <c r="G79" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2280,19 +2280,19 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E80" t="s">
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>29.0</v>
+        <v>2739.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2306,22 +2306,22 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E81" t="s">
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>7.0</v>
+        <v>4294.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="82">
@@ -2332,22 +2332,22 @@
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
         <v>52</v>
       </c>
       <c r="F82" t="n">
-        <v>74.0</v>
+        <v>50.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
       </c>
       <c r="H82" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -2358,16 +2358,16 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E83" t="s">
         <v>52</v>
       </c>
       <c r="F83" t="n">
-        <v>136.0</v>
+        <v>32.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2384,19 +2384,19 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E84" t="s">
         <v>52</v>
       </c>
       <c r="F84" t="n">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2410,19 +2410,19 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
         <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>333.0</v>
+        <v>29.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2436,16 +2436,16 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E86" t="s">
         <v>52</v>
       </c>
       <c r="F86" t="n">
-        <v>17.0</v>
+        <v>7.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2462,22 +2462,22 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E87" t="s">
         <v>52</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0</v>
+        <v>74.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>5.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="88">
@@ -2488,16 +2488,16 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E88" t="s">
         <v>52</v>
       </c>
       <c r="F88" t="n">
-        <v>19.0</v>
+        <v>136.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2514,22 +2514,22 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E89" t="s">
         <v>52</v>
       </c>
       <c r="F89" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2537,22 +2537,22 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C90" t="s">
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>111.0</v>
+        <v>333.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2563,19 +2563,19 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
         <v>52</v>
       </c>
       <c r="F91" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2589,19 +2589,19 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
         <v>52</v>
       </c>
       <c r="F92" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2615,7 +2615,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
@@ -2627,7 +2627,7 @@
         <v>52</v>
       </c>
       <c r="F93" t="n">
-        <v>233.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
@@ -2653,7 +2653,7 @@
         <v>52</v>
       </c>
       <c r="F94" t="n">
-        <v>516.0</v>
+        <v>14.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2667,19 +2667,19 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E95" t="s">
         <v>52</v>
       </c>
       <c r="F95" t="n">
-        <v>278.0</v>
+        <v>111.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2693,19 +2693,19 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E96" t="s">
         <v>52</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2719,19 +2719,19 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E97" t="s">
         <v>52</v>
       </c>
       <c r="F97" t="n">
-        <v>286.0</v>
+        <v>7.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2745,25 +2745,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E98" t="s">
         <v>52</v>
       </c>
       <c r="F98" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="99">
@@ -2771,19 +2771,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E99" t="s">
         <v>52</v>
       </c>
       <c r="F99" t="n">
-        <v>3988.0</v>
+        <v>9.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2797,25 +2797,25 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E100" t="s">
         <v>52</v>
       </c>
       <c r="F100" t="n">
-        <v>7945.0</v>
+        <v>40.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
       </c>
       <c r="H100" t="n">
-        <v>16913.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="101">
@@ -2826,22 +2826,22 @@
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E101" t="s">
         <v>52</v>
       </c>
       <c r="F101" t="n">
-        <v>1220.0</v>
+        <v>3.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
       </c>
       <c r="H101" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -2852,22 +2852,22 @@
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E102" t="s">
         <v>52</v>
       </c>
       <c r="F102" t="n">
-        <v>3878.0</v>
+        <v>233.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="103">
@@ -2878,16 +2878,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E103" t="s">
         <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>75.0</v>
+        <v>516.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2904,22 +2904,22 @@
         <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E104" t="s">
         <v>52</v>
       </c>
       <c r="F104" t="n">
-        <v>318.0</v>
+        <v>278.0</v>
       </c>
       <c r="G104" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H104" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="105">
@@ -2930,16 +2930,16 @@
         <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E105" t="s">
         <v>52</v>
       </c>
       <c r="F105" t="n">
-        <v>150.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2956,19 +2956,19 @@
         <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E106" t="s">
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12456.0</v>
+        <v>286.0</v>
       </c>
       <c r="G106" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2982,22 +2982,22 @@
         <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
         <v>52</v>
       </c>
       <c r="F107" t="n">
-        <v>589.0</v>
+        <v>13.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H107" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -3008,16 +3008,16 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E108" t="s">
         <v>52</v>
       </c>
       <c r="F108" t="n">
-        <v>4.0</v>
+        <v>3988.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3034,22 +3034,22 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E109" t="s">
         <v>52</v>
       </c>
       <c r="F109" t="n">
-        <v>1127.0</v>
+        <v>7945.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>
       </c>
       <c r="H109" t="n">
-        <v>6.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="110">
@@ -3060,22 +3060,22 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E110" t="s">
         <v>52</v>
       </c>
       <c r="F110" t="n">
-        <v>1.0</v>
+        <v>1220.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="111">
@@ -3086,21 +3086,255 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" t="s">
+        <v>26</v>
+      </c>
+      <c r="E111" t="s">
+        <v>52</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3878.0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>43</v>
+      </c>
+      <c r="E112" t="s">
+        <v>52</v>
+      </c>
+      <c r="F112" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" t="s">
+        <v>27</v>
+      </c>
+      <c r="E113" t="s">
+        <v>52</v>
+      </c>
+      <c r="F113" t="n">
+        <v>318.0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" t="s">
+        <v>28</v>
+      </c>
+      <c r="E114" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115" t="s">
+        <v>52</v>
+      </c>
+      <c r="F115" t="n">
+        <v>12468.0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" t="s">
+        <v>45</v>
+      </c>
+      <c r="E116" t="s">
+        <v>52</v>
+      </c>
+      <c r="F116" t="n">
+        <v>589.0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" t="s">
+        <v>46</v>
+      </c>
+      <c r="E117" t="s">
+        <v>52</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" t="s">
+        <v>47</v>
+      </c>
+      <c r="E118" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1127.0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>8</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" t="s">
+        <v>50</v>
+      </c>
+      <c r="E119" t="s">
+        <v>52</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" t="s">
         <v>17</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D120" t="s">
         <v>30</v>
       </c>
-      <c r="E111" t="s">
-        <v>52</v>
-      </c>
-      <c r="F111" t="n">
+      <c r="E120" t="s">
+        <v>52</v>
+      </c>
+      <c r="F120" t="n">
         <v>4.0</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H111" t="n">
+      <c r="G120" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H120" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -394,7 +394,7 @@
         <v>1234.0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -443,7 +443,7 @@
         <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>1420.0</v>
+        <v>1422.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>10798.0</v>
+        <v>10805.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3343.0</v>
+        <v>3345.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6555.0</v>
+        <v>6570.0</v>
       </c>
       <c r="G23" t="n">
         <v>41.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6207.0</v>
+        <v>6215.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -1145,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>2346.0</v>
+        <v>2350.0</v>
       </c>
       <c r="G36" t="n">
         <v>13.0</v>
@@ -1307,7 +1307,7 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="43">
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1725.0</v>
+        <v>1726.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -2081,7 +2081,7 @@
         <v>52</v>
       </c>
       <c r="F72" t="n">
-        <v>843.0</v>
+        <v>844.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>971.0</v>
+        <v>972.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3147,7 +3147,7 @@
         <v>52</v>
       </c>
       <c r="F113" t="n">
-        <v>318.0</v>
+        <v>319.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12468.0</v>
+        <v>12492.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1127.0</v>
+        <v>1134.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>414.0</v>
+        <v>453.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -339,7 +339,7 @@
         <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>705.0</v>
+        <v>706.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -443,7 +443,7 @@
         <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>1422.0</v>
+        <v>1425.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -495,7 +495,7 @@
         <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>521.0</v>
+        <v>525.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -573,7 +573,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>452.0</v>
+        <v>455.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -599,7 +599,7 @@
         <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>320.0</v>
+        <v>327.0</v>
       </c>
       <c r="G16" t="n">
         <v>15.0</v>
@@ -651,13 +651,13 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>3724.0</v>
+        <v>3727.0</v>
       </c>
       <c r="G17" t="n">
         <v>88.0</v>
       </c>
       <c r="H17" t="n">
-        <v>405.0</v>
+        <v>408.0</v>
       </c>
     </row>
     <row r="18">
@@ -677,7 +677,7 @@
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>1734.0</v>
+        <v>1737.0</v>
       </c>
       <c r="G18" t="n">
         <v>52.0</v>
@@ -729,7 +729,7 @@
         <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>604.0</v>
+        <v>609.0</v>
       </c>
       <c r="G20" t="n">
         <v>18.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>10805.0</v>
+        <v>10806.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3345.0</v>
+        <v>3350.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6570.0</v>
+        <v>6581.0</v>
       </c>
       <c r="G23" t="n">
         <v>41.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6215.0</v>
+        <v>6221.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4589.0</v>
+        <v>4597.0</v>
       </c>
       <c r="G27" t="n">
         <v>33.0</v>
@@ -937,13 +937,13 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>977.0</v>
+        <v>980.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>402.0</v>
+        <v>411.0</v>
       </c>
     </row>
     <row r="29">
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>2063.0</v>
+        <v>2064.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1041,13 +1041,13 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>43.0</v>
+        <v>51.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="33">
@@ -1145,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>2350.0</v>
+        <v>2351.0</v>
       </c>
       <c r="G36" t="n">
         <v>13.0</v>
@@ -1197,7 +1197,7 @@
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>617.0</v>
+        <v>620.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="41">
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1085.0</v>
+        <v>1087.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1353,7 +1353,7 @@
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>342.0</v>
+        <v>364.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1726.0</v>
+        <v>1727.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1157.0</v>
+        <v>1160.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>221.0</v>
+        <v>225.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2168.0</v>
+        <v>2175.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>589.0</v>
+        <v>591.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>972.0</v>
+        <v>979.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2263,7 +2263,7 @@
         <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2739.0</v>
+        <v>2747.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4294.0</v>
+        <v>4308.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2679,7 +2679,7 @@
         <v>52</v>
       </c>
       <c r="F95" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>516.0</v>
+        <v>517.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12492.0</v>
+        <v>12511.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3225,7 +3225,7 @@
         <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>589.0</v>
+        <v>591.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1134.0</v>
+        <v>1135.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1866.0</v>
+        <v>1867.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>727.0</v>
+        <v>728.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
       <c r="G16" t="n">
         <v>15.0</v>
@@ -755,13 +755,13 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>10806.0</v>
+        <v>10818.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
       </c>
       <c r="H21" t="n">
-        <v>1021.0</v>
+        <v>1022.0</v>
       </c>
     </row>
     <row r="22">
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3350.0</v>
+        <v>3356.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -885,7 +885,7 @@
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>1747.0</v>
+        <v>1748.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4597.0</v>
+        <v>4598.0</v>
       </c>
       <c r="G27" t="n">
         <v>33.0</v>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>980.0</v>
+        <v>981.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="41">
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1087.0</v>
+        <v>1088.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>585.0</v>
+        <v>586.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1353,7 +1353,7 @@
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1639,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1587.0</v>
+        <v>1593.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1160.0</v>
+        <v>1163.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>225.0</v>
+        <v>229.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2175.0</v>
+        <v>2184.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>591.0</v>
+        <v>595.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>979.0</v>
+        <v>981.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2747.0</v>
+        <v>2752.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4308.0</v>
+        <v>4314.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>517.0</v>
+        <v>518.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12511.0</v>
+        <v>12528.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1135.0</v>
+        <v>1136.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -495,7 +495,7 @@
         <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>728.0</v>
+        <v>729.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3356.0</v>
+        <v>3357.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4598.0</v>
+        <v>4600.0</v>
       </c>
       <c r="G27" t="n">
         <v>33.0</v>
@@ -943,7 +943,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>411.0</v>
+        <v>412.0</v>
       </c>
     </row>
     <row r="29">
@@ -1197,7 +1197,7 @@
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>620.0</v>
+        <v>622.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1639,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1593.0</v>
+        <v>1597.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1163.0</v>
+        <v>1166.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1717,7 +1717,7 @@
         <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>2818.0</v>
+        <v>2820.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -1821,7 +1821,7 @@
         <v>51</v>
       </c>
       <c r="F62" t="n">
-        <v>79.0</v>
+        <v>83.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>981.0</v>
+        <v>982.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2752.0</v>
+        <v>2755.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4314.0</v>
+        <v>4317.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -3225,7 +3225,7 @@
         <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>591.0</v>
+        <v>592.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>729.0</v>
+        <v>732.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>981.0</v>
+        <v>982.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -1223,7 +1223,7 @@
         <v>51</v>
       </c>
       <c r="F39" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1088.0</v>
+        <v>1091.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>706.0</v>
+        <v>712.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -391,7 +391,7 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>1234.0</v>
+        <v>1237.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1867.0</v>
+        <v>1868.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -651,7 +651,7 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>3727.0</v>
+        <v>3760.0</v>
       </c>
       <c r="G17" t="n">
         <v>88.0</v>
@@ -677,7 +677,7 @@
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>1737.0</v>
+        <v>1739.0</v>
       </c>
       <c r="G18" t="n">
         <v>52.0</v>
@@ -729,7 +729,7 @@
         <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>609.0</v>
+        <v>619.0</v>
       </c>
       <c r="G20" t="n">
         <v>18.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>10818.0</v>
+        <v>10820.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3357.0</v>
+        <v>3362.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,13 +807,13 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6581.0</v>
+        <v>6586.0</v>
       </c>
       <c r="G23" t="n">
         <v>41.0</v>
       </c>
       <c r="H23" t="n">
-        <v>238.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="24">
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6221.0</v>
+        <v>6225.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -911,10 +911,10 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4600.0</v>
+        <v>4612.0</v>
       </c>
       <c r="G27" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="H27" t="n">
         <v>9.0</v>
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>1728.0</v>
+        <v>1730.0</v>
       </c>
       <c r="G37" t="n">
         <v>7.0</v>
@@ -1379,7 +1379,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1431,7 +1431,7 @@
         <v>51</v>
       </c>
       <c r="F47" t="n">
-        <v>568.0</v>
+        <v>569.0</v>
       </c>
       <c r="G47" t="n">
         <v>3.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1166.0</v>
+        <v>1168.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2184.0</v>
+        <v>2192.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>133.0</v>
+        <v>137.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>982.0</v>
+        <v>987.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2755.0</v>
+        <v>2760.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>286.0</v>
+        <v>288.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3147,7 +3147,7 @@
         <v>52</v>
       </c>
       <c r="F113" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12528.0</v>
+        <v>12550.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1136.0</v>
+        <v>1138.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -391,10 +391,10 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>1237.0</v>
+        <v>1238.0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -657,7 +657,7 @@
         <v>88.0</v>
       </c>
       <c r="H17" t="n">
-        <v>408.0</v>
+        <v>414.0</v>
       </c>
     </row>
     <row r="18">
@@ -683,7 +683,7 @@
         <v>52.0</v>
       </c>
       <c r="H18" t="n">
-        <v>232.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="19">
@@ -709,7 +709,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" t="n">
-        <v>47.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="20">
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>10820.0</v>
+        <v>10829.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3362.0</v>
+        <v>3367.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,10 +807,10 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6586.0</v>
+        <v>6602.0</v>
       </c>
       <c r="G23" t="n">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="H23" t="n">
         <v>251.0</v>
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>3623.0</v>
+        <v>3624.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6225.0</v>
+        <v>6230.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4612.0</v>
+        <v>4615.0</v>
       </c>
       <c r="G27" t="n">
         <v>35.0</v>
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1727.0</v>
+        <v>1729.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>987.0</v>
+        <v>990.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2679,7 +2679,7 @@
         <v>52</v>
       </c>
       <c r="F95" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12550.0</v>
+        <v>12567.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1138.0</v>
+        <v>1139.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -417,7 +417,7 @@
         <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>760.0</v>
+        <v>762.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -573,7 +573,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>455.0</v>
+        <v>456.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -599,7 +599,7 @@
         <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -651,13 +651,13 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>3760.0</v>
+        <v>3764.0</v>
       </c>
       <c r="G17" t="n">
         <v>88.0</v>
       </c>
       <c r="H17" t="n">
-        <v>414.0</v>
+        <v>415.0</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="20">
@@ -729,7 +729,7 @@
         <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="G20" t="n">
         <v>18.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3367.0</v>
+        <v>3378.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>3624.0</v>
+        <v>3627.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -885,7 +885,7 @@
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>1748.0</v>
+        <v>1752.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4615.0</v>
+        <v>4616.0</v>
       </c>
       <c r="G27" t="n">
         <v>35.0</v>
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1047,7 +1047,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="33">
@@ -1177,7 +1177,7 @@
         <v>7.0</v>
       </c>
       <c r="H37" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="38">
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>1365.0</v>
+        <v>1366.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1301,13 +1301,13 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1091.0</v>
+        <v>1092.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="43">
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1535,7 +1535,7 @@
         <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>690.0</v>
+        <v>695.0</v>
       </c>
       <c r="G51" t="n">
         <v>3.0</v>
@@ -1561,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>1594.0</v>
+        <v>1595.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1639,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1597.0</v>
+        <v>1605.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1168.0</v>
+        <v>1170.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1717,7 +1717,7 @@
         <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>2820.0</v>
+        <v>2823.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2192.0</v>
+        <v>2194.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>595.0</v>
+        <v>598.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>990.0</v>
+        <v>992.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2760.0</v>
+        <v>2771.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4317.0</v>
+        <v>4324.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>336.0</v>
+        <v>339.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12567.0</v>
+        <v>12584.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3225,7 +3225,7 @@
         <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>592.0</v>
+        <v>593.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1139.0</v>
+        <v>1140.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1868.0</v>
+        <v>1873.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>732.0</v>
+        <v>733.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3378.0</v>
+        <v>3383.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,13 +807,13 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6602.0</v>
+        <v>6605.0</v>
       </c>
       <c r="G23" t="n">
         <v>43.0</v>
       </c>
       <c r="H23" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
     </row>
     <row r="24">
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>3627.0</v>
+        <v>3632.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6230.0</v>
+        <v>6231.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4616.0</v>
+        <v>4620.0</v>
       </c>
       <c r="G27" t="n">
         <v>35.0</v>
@@ -937,13 +937,13 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>982.0</v>
+        <v>983.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>412.0</v>
+        <v>416.0</v>
       </c>
     </row>
     <row r="29">
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>2064.0</v>
+        <v>2066.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>1366.0</v>
+        <v>1367.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="43">
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1729.0</v>
+        <v>1731.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1639,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1605.0</v>
+        <v>1612.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1170.0</v>
+        <v>1174.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1769,7 +1769,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="n">
-        <v>1560.0</v>
+        <v>1561.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -2081,7 +2081,7 @@
         <v>52</v>
       </c>
       <c r="F72" t="n">
-        <v>844.0</v>
+        <v>845.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>992.0</v>
+        <v>998.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3147,7 +3147,7 @@
         <v>52</v>
       </c>
       <c r="F113" t="n">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12584.0</v>
+        <v>12595.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3225,7 +3225,7 @@
         <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>593.0</v>
+        <v>594.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1140.0</v>
+        <v>1144.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -391,7 +391,7 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>1238.0</v>
+        <v>1239.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1873.0</v>
+        <v>1874.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -657,7 +657,7 @@
         <v>88.0</v>
       </c>
       <c r="H17" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
     </row>
     <row r="18">
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3383.0</v>
+        <v>3390.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6605.0</v>
+        <v>6624.0</v>
       </c>
       <c r="G23" t="n">
         <v>43.0</v>
@@ -937,13 +937,13 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>983.0</v>
+        <v>988.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>416.0</v>
+        <v>419.0</v>
       </c>
     </row>
     <row r="29">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>194.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="30">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="41">
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1092.0</v>
+        <v>1093.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>998.0</v>
+        <v>1002.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12595.0</v>
+        <v>12611.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3225,7 +3225,7 @@
         <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>594.0</v>
+        <v>595.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1144.0</v>
+        <v>1146.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>454.0</v>
+        <v>462.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>712.0</v>
+        <v>723.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>328.0</v>
+        <v>334.0</v>
       </c>
       <c r="G16" t="n">
         <v>15.0</v>
@@ -651,10 +651,10 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>3764.0</v>
+        <v>3765.0</v>
       </c>
       <c r="G17" t="n">
-        <v>88.0</v>
+        <v>99.0</v>
       </c>
       <c r="H17" t="n">
         <v>416.0</v>
@@ -677,10 +677,10 @@
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>1739.0</v>
+        <v>1741.0</v>
       </c>
       <c r="G18" t="n">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="H18" t="n">
         <v>233.0</v>
@@ -729,7 +729,7 @@
         <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>620.0</v>
+        <v>631.0</v>
       </c>
       <c r="G20" t="n">
         <v>18.0</v>
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>2066.0</v>
+        <v>2070.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>1367.0</v>
+        <v>1370.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1093.0</v>
+        <v>1096.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>587.0</v>
+        <v>594.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1353,7 +1353,7 @@
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>365.0</v>
+        <v>384.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1379,7 +1379,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1873,7 +1873,7 @@
         <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>234.0</v>
+        <v>238.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2194.0</v>
+        <v>2201.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>598.0</v>
+        <v>604.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>137.0</v>
+        <v>140.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2263,7 +2263,7 @@
         <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2771.0</v>
+        <v>2779.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4324.0</v>
+        <v>4348.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2653,7 +2653,7 @@
         <v>52</v>
       </c>
       <c r="F94" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>518.0</v>
+        <v>519.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2913,7 +2913,7 @@
         <v>52</v>
       </c>
       <c r="F104" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>132.0</v>
+        <v>146.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -443,7 +443,7 @@
         <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>1425.0</v>
+        <v>1429.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1874.0</v>
+        <v>1876.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -495,7 +495,7 @@
         <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -654,7 +654,7 @@
         <v>3765.0</v>
       </c>
       <c r="G17" t="n">
-        <v>99.0</v>
+        <v>103.0</v>
       </c>
       <c r="H17" t="n">
         <v>416.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3390.0</v>
+        <v>3398.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6624.0</v>
+        <v>6637.0</v>
       </c>
       <c r="G23" t="n">
         <v>43.0</v>
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6231.0</v>
+        <v>6232.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -911,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4620.0</v>
+        <v>4621.0</v>
       </c>
       <c r="G27" t="n">
         <v>35.0</v>
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>120.0</v>
+        <v>122.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1145,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>2351.0</v>
+        <v>2352.0</v>
       </c>
       <c r="G36" t="n">
         <v>13.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>594.0</v>
+        <v>616.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1353,7 +1353,7 @@
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>384.0</v>
+        <v>385.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1405,7 +1405,7 @@
         <v>51</v>
       </c>
       <c r="F46" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1731.0</v>
+        <v>1734.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1639,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1612.0</v>
+        <v>1614.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1174.0</v>
+        <v>1175.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1769,7 +1769,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="n">
-        <v>1561.0</v>
+        <v>1564.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2201.0</v>
+        <v>2208.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>604.0</v>
+        <v>605.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>1002.0</v>
+        <v>1006.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2779.0</v>
+        <v>2783.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4348.0</v>
+        <v>4353.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3147,7 +3147,7 @@
         <v>52</v>
       </c>
       <c r="F113" t="n">
-        <v>323.0</v>
+        <v>325.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12611.0</v>
+        <v>12634.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1146.0</v>
+        <v>1147.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -709,7 +709,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="20">
@@ -833,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>3632.0</v>
+        <v>3638.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -937,13 +937,13 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>988.0</v>
+        <v>998.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>419.0</v>
+        <v>430.0</v>
       </c>
     </row>
     <row r="29">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="30">
@@ -1047,7 +1047,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="33">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="41">
@@ -1483,7 +1483,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1561,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>1595.0</v>
+        <v>1596.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1587,7 +1587,7 @@
         <v>51</v>
       </c>
       <c r="F53" t="n">
-        <v>751.0</v>
+        <v>752.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -2055,7 +2055,7 @@
         <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>2186.0</v>
+        <v>2217.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -3017,7 +3017,7 @@
         <v>52</v>
       </c>
       <c r="F108" t="n">
-        <v>3988.0</v>
+        <v>3996.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3043,7 +3043,7 @@
         <v>52</v>
       </c>
       <c r="F109" t="n">
-        <v>7945.0</v>
+        <v>7949.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>
@@ -3069,7 +3069,7 @@
         <v>52</v>
       </c>
       <c r="F110" t="n">
-        <v>1220.0</v>
+        <v>1224.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -287,7 +287,7 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>463.0</v>
+        <v>470.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -313,7 +313,7 @@
         <v>51</v>
       </c>
       <c r="F4" t="n">
-        <v>168.0</v>
+        <v>187.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -339,7 +339,7 @@
         <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>723.0</v>
+        <v>726.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -521,7 +521,7 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>733.0</v>
+        <v>737.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -651,7 +651,7 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>3765.0</v>
+        <v>3795.0</v>
       </c>
       <c r="G17" t="n">
         <v>103.0</v>
@@ -677,7 +677,7 @@
         <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>1741.0</v>
+        <v>1743.0</v>
       </c>
       <c r="G18" t="n">
         <v>55.0</v>
@@ -729,7 +729,7 @@
         <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>631.0</v>
+        <v>640.0</v>
       </c>
       <c r="G20" t="n">
         <v>18.0</v>
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>2070.0</v>
+        <v>2072.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>1370.0</v>
+        <v>1373.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1096.0</v>
+        <v>1099.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>616.0</v>
+        <v>618.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1379,7 +1379,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1405,7 +1405,7 @@
         <v>51</v>
       </c>
       <c r="F46" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>239.0</v>
+        <v>245.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2208.0</v>
+        <v>2213.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1977,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>140.0</v>
+        <v>144.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2783.0</v>
+        <v>2802.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4353.0</v>
+        <v>4371.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>519.0</v>
+        <v>520.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2965,7 +2965,7 @@
         <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -657,7 +657,7 @@
         <v>103.0</v>
       </c>
       <c r="H17" t="n">
-        <v>416.0</v>
+        <v>417.0</v>
       </c>
     </row>
     <row r="18">
@@ -813,7 +813,7 @@
         <v>43.0</v>
       </c>
       <c r="H23" t="n">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
     </row>
     <row r="24">
@@ -1047,7 +1047,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="33">
@@ -1301,13 +1301,13 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1099.0</v>
+        <v>1106.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="43">

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -443,7 +443,7 @@
         <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>1429.0</v>
+        <v>1432.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -469,7 +469,7 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>1876.0</v>
+        <v>1878.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -755,7 +755,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>10829.0</v>
+        <v>10862.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3398.0</v>
+        <v>3414.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,13 +807,13 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6637.0</v>
+        <v>6649.0</v>
       </c>
       <c r="G23" t="n">
         <v>43.0</v>
       </c>
       <c r="H23" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
     </row>
     <row r="24">
@@ -859,7 +859,7 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>6232.0</v>
+        <v>6236.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -885,7 +885,7 @@
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>1752.0</v>
+        <v>1753.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -911,10 +911,10 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4621.0</v>
+        <v>4630.0</v>
       </c>
       <c r="G27" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="H27" t="n">
         <v>9.0</v>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>998.0</v>
+        <v>1002.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>199.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="30">
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>2072.0</v>
+        <v>2073.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>1730.0</v>
+        <v>1734.0</v>
       </c>
       <c r="G37" t="n">
         <v>7.0</v>
@@ -1197,7 +1197,7 @@
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>622.0</v>
+        <v>625.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>153.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="41">
@@ -1301,13 +1301,13 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1106.0</v>
+        <v>1107.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="43">
@@ -1613,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>1734.0</v>
+        <v>1738.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1639,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>1614.0</v>
+        <v>1615.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="F57" t="n">
-        <v>1175.0</v>
+        <v>1180.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -2081,7 +2081,7 @@
         <v>52</v>
       </c>
       <c r="F72" t="n">
-        <v>845.0</v>
+        <v>846.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2107,7 +2107,7 @@
         <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>1006.0</v>
+        <v>1029.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>340.0</v>
+        <v>343.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12634.0</v>
+        <v>12694.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3225,7 +3225,7 @@
         <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3277,7 +3277,7 @@
         <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>1147.0</v>
+        <v>1149.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -1021,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="32">
@@ -1307,7 +1307,7 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="43">

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -261,7 +261,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -365,7 +365,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>726.0</v>
+        <v>730.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -625,7 +625,7 @@
         <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>334.0</v>
+        <v>336.0</v>
       </c>
       <c r="G16" t="n">
         <v>15.0</v>
@@ -651,13 +651,13 @@
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>3795.0</v>
+        <v>3805.0</v>
       </c>
       <c r="G17" t="n">
         <v>103.0</v>
       </c>
       <c r="H17" t="n">
-        <v>417.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="18">
@@ -781,7 +781,7 @@
         <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>3414.0</v>
+        <v>3418.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -807,7 +807,7 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>6649.0</v>
+        <v>6674.0</v>
       </c>
       <c r="G23" t="n">
         <v>43.0</v>
@@ -911,13 +911,13 @@
         <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>4630.0</v>
+        <v>4636.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
       </c>
       <c r="H27" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>1002.0</v>
+        <v>1005.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>2073.0</v>
+        <v>2076.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="F41" t="n">
-        <v>1373.0</v>
+        <v>1376.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1301,7 +1301,7 @@
         <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>1107.0</v>
+        <v>1108.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>618.0</v>
+        <v>621.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1353,7 +1353,7 @@
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>385.0</v>
+        <v>386.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1717,7 +1717,7 @@
         <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>2823.0</v>
+        <v>2824.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -1769,7 +1769,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="n">
-        <v>1564.0</v>
+        <v>1565.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1873,7 +1873,7 @@
         <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>245.0</v>
+        <v>253.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>2213.0</v>
+        <v>2222.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,7 +1951,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>607.0</v>
+        <v>610.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2133,7 +2133,7 @@
         <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>1029.0</v>
+        <v>1030.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2263,7 +2263,7 @@
         <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2289,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>2802.0</v>
+        <v>2818.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2315,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>4371.0</v>
+        <v>4386.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2861,7 +2861,7 @@
         <v>52</v>
       </c>
       <c r="F102" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>520.0</v>
+        <v>523.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -3199,7 +3199,7 @@
         <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>12694.0</v>
+        <v>12709.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="55">
   <si>
     <t>Area</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Puglia</t>
   </si>
   <si>
+    <t>Umbria</t>
+  </si>
+  <si>
     <t>Bologna</t>
   </si>
   <si>
@@ -165,6 +168,9 @@
   </si>
   <si>
     <t>Bari</t>
+  </si>
+  <si>
+    <t>Perugia</t>
   </si>
   <si>
     <t>Wild boar</t>
@@ -255,10 +261,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>149.0</v>
@@ -281,10 +287,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
         <v>470.0</v>
@@ -307,10 +313,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
         <v>187.0</v>
@@ -333,10 +339,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
         <v>317.0</v>
@@ -359,10 +365,10 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>730.0</v>
@@ -385,10 +391,10 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
         <v>1239.0</v>
@@ -411,10 +417,10 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
         <v>762.0</v>
@@ -437,10 +443,10 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
         <v>1432.0</v>
@@ -463,13 +469,13 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>1878.0</v>
+        <v>1879.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -489,10 +495,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
         <v>527.0</v>
@@ -515,10 +521,10 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
         <v>737.0</v>
@@ -541,10 +547,10 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
         <v>1.0</v>
@@ -567,10 +573,10 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>456.0</v>
@@ -593,10 +599,10 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
         <v>99.0</v>
@@ -619,10 +625,10 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
         <v>336.0</v>
@@ -645,10 +651,10 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
         <v>3805.0</v>
@@ -671,10 +677,10 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
         <v>1743.0</v>
@@ -697,10 +703,10 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -723,10 +729,10 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F20" t="n">
         <v>640.0</v>
@@ -749,13 +755,13 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10862.0</v>
+        <v>10886.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -775,13 +781,13 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3418.0</v>
+        <v>3419.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -801,10 +807,10 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
         <v>6674.0</v>
@@ -827,13 +833,13 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>3638.0</v>
+        <v>3641.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -853,10 +859,10 @@
         <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F25" t="n">
         <v>6236.0</v>
@@ -879,10 +885,10 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F26" t="n">
         <v>1753.0</v>
@@ -905,10 +911,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F27" t="n">
         <v>4636.0</v>
@@ -931,10 +937,10 @@
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
         <v>1005.0</v>
@@ -957,10 +963,10 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -983,10 +989,10 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F30" t="n">
         <v>2076.0</v>
@@ -1009,10 +1015,10 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F31" t="n">
         <v>122.0</v>
@@ -1035,10 +1041,10 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F32" t="n">
         <v>55.0</v>
@@ -1061,10 +1067,10 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F33" t="n">
         <v>15.0</v>
@@ -1087,10 +1093,10 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F34" t="n">
         <v>2.0</v>
@@ -1113,10 +1119,10 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F35" t="n">
         <v>16.0</v>
@@ -1139,10 +1145,10 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F36" t="n">
         <v>2352.0</v>
@@ -1165,10 +1171,10 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F37" t="n">
         <v>1734.0</v>
@@ -1191,10 +1197,10 @@
         <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F38" t="n">
         <v>625.0</v>
@@ -1217,10 +1223,10 @@
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F39" t="n">
         <v>101.0</v>
@@ -1243,10 +1249,10 @@
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -1269,10 +1275,10 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F41" t="n">
         <v>1376.0</v>
@@ -1295,10 +1301,10 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F42" t="n">
         <v>1108.0</v>
@@ -1321,10 +1327,10 @@
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F43" t="n">
         <v>621.0</v>
@@ -1347,10 +1353,10 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F44" t="n">
         <v>386.0</v>
@@ -1373,10 +1379,10 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F45" t="n">
         <v>39.0</v>
@@ -1399,10 +1405,10 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F46" t="n">
         <v>114.0</v>
@@ -1425,10 +1431,10 @@
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F47" t="n">
         <v>569.0</v>
@@ -1451,10 +1457,10 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F48" t="n">
         <v>1.0</v>
@@ -1477,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F49" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1503,10 +1509,10 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F50" t="n">
         <v>81.0</v>
@@ -1529,13 +1535,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F51" t="n">
-        <v>695.0</v>
+        <v>699.0</v>
       </c>
       <c r="G51" t="n">
         <v>3.0</v>
@@ -1555,13 +1561,13 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F52" t="n">
-        <v>1596.0</v>
+        <v>1598.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1581,13 +1587,13 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F53" t="n">
-        <v>752.0</v>
+        <v>753.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1607,10 +1613,10 @@
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F54" t="n">
         <v>1738.0</v>
@@ -1633,10 +1639,10 @@
         <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F55" t="n">
         <v>1615.0</v>
@@ -1659,10 +1665,10 @@
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>1.0</v>
@@ -1685,13 +1691,13 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1180.0</v>
+        <v>1181.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1711,10 +1717,10 @@
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F58" t="n">
         <v>2824.0</v>
@@ -1737,10 +1743,10 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F59" t="n">
         <v>2.0</v>
@@ -1763,10 +1769,10 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F60" t="n">
         <v>1565.0</v>
@@ -1789,10 +1795,10 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F61" t="n">
         <v>1.0</v>
@@ -1815,10 +1821,10 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F62" t="n">
         <v>83.0</v>
@@ -1841,10 +1847,10 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F63" t="n">
         <v>13.0</v>
@@ -1867,10 +1873,10 @@
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F64" t="n">
         <v>24.0</v>
@@ -1893,10 +1899,10 @@
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F65" t="n">
         <v>253.0</v>
@@ -1919,10 +1925,10 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F66" t="n">
         <v>2222.0</v>
@@ -1945,10 +1951,10 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F67" t="n">
         <v>610.0</v>
@@ -1971,10 +1977,10 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F68" t="n">
         <v>144.0</v>
@@ -1997,10 +2003,10 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F69" t="n">
         <v>9.0</v>
@@ -2023,10 +2029,10 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E70" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F70" t="n">
         <v>1.0</v>
@@ -2049,13 +2055,13 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F71" t="n">
-        <v>2217.0</v>
+        <v>2232.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2075,10 +2081,10 @@
         <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F72" t="n">
         <v>846.0</v>
@@ -2101,10 +2107,10 @@
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F73" t="n">
         <v>130.0</v>
@@ -2127,13 +2133,13 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1030.0</v>
+        <v>1036.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2153,10 +2159,10 @@
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E75" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F75" t="n">
         <v>28.0</v>
@@ -2179,10 +2185,10 @@
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E76" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F76" t="n">
         <v>24.0</v>
@@ -2205,10 +2211,10 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E77" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F77" t="n">
         <v>17.0</v>
@@ -2231,10 +2237,10 @@
         <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E78" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F78" t="n">
         <v>2.0</v>
@@ -2257,10 +2263,10 @@
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E79" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F79" t="n">
         <v>76.0</v>
@@ -2283,10 +2289,10 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F80" t="n">
         <v>2818.0</v>
@@ -2309,10 +2315,10 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F81" t="n">
         <v>4386.0</v>
@@ -2335,10 +2341,10 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F82" t="n">
         <v>50.0</v>
@@ -2361,10 +2367,10 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F83" t="n">
         <v>32.0</v>
@@ -2387,10 +2393,10 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E84" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F84" t="n">
         <v>24.0</v>
@@ -2413,10 +2419,10 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F85" t="n">
         <v>29.0</v>
@@ -2439,10 +2445,10 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E86" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F86" t="n">
         <v>7.0</v>
@@ -2465,10 +2471,10 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E87" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F87" t="n">
         <v>74.0</v>
@@ -2491,10 +2497,10 @@
         <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E88" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F88" t="n">
         <v>136.0</v>
@@ -2517,10 +2523,10 @@
         <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F89" t="n">
         <v>1.0</v>
@@ -2543,13 +2549,13 @@
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>344.0</v>
+        <v>345.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2569,10 +2575,10 @@
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F91" t="n">
         <v>10.0</v>
@@ -2595,10 +2601,10 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E92" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F92" t="n">
         <v>10.0</v>
@@ -2621,10 +2627,10 @@
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E93" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F93" t="n">
         <v>1.0</v>
@@ -2647,10 +2653,10 @@
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E94" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F94" t="n">
         <v>15.0</v>
@@ -2673,10 +2679,10 @@
         <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E95" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F95" t="n">
         <v>113.0</v>
@@ -2699,10 +2705,10 @@
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F96" t="n">
         <v>4.0</v>
@@ -2725,10 +2731,10 @@
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F97" t="n">
         <v>7.0</v>
@@ -2751,10 +2757,10 @@
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E98" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2777,10 +2783,10 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E99" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F99" t="n">
         <v>9.0</v>
@@ -2803,10 +2809,10 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E100" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F100" t="n">
         <v>40.0</v>
@@ -2829,10 +2835,10 @@
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E101" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F101" t="n">
         <v>3.0</v>
@@ -2855,10 +2861,10 @@
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F102" t="n">
         <v>234.0</v>
@@ -2881,10 +2887,10 @@
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F103" t="n">
         <v>523.0</v>
@@ -2907,10 +2913,10 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F104" t="n">
         <v>279.0</v>
@@ -2933,10 +2939,10 @@
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F105" t="n">
         <v>1.0</v>
@@ -2959,10 +2965,10 @@
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E106" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F106" t="n">
         <v>289.0</v>
@@ -2985,10 +2991,10 @@
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E107" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F107" t="n">
         <v>13.0</v>
@@ -3011,13 +3017,13 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E108" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F108" t="n">
-        <v>3996.0</v>
+        <v>3998.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3037,13 +3043,13 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E109" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F109" t="n">
-        <v>7949.0</v>
+        <v>7951.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>
@@ -3063,10 +3069,10 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E110" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F110" t="n">
         <v>1224.0</v>
@@ -3089,13 +3095,13 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E111" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F111" t="n">
-        <v>3878.0</v>
+        <v>3879.0</v>
       </c>
       <c r="G111" t="n">
         <v>1.0</v>
@@ -3115,10 +3121,10 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E112" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F112" t="n">
         <v>75.0</v>
@@ -3141,10 +3147,10 @@
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E113" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F113" t="n">
         <v>325.0</v>
@@ -3167,10 +3173,10 @@
         <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E114" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F114" t="n">
         <v>150.0</v>
@@ -3193,13 +3199,13 @@
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E115" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12709.0</v>
+        <v>12717.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3219,10 +3225,10 @@
         <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E116" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F116" t="n">
         <v>597.0</v>
@@ -3245,10 +3251,10 @@
         <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E117" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F117" t="n">
         <v>4.0</v>
@@ -3271,10 +3277,10 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E118" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F118" t="n">
         <v>1149.0</v>
@@ -3297,10 +3303,10 @@
         <v>19</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E119" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F119" t="n">
         <v>1.0</v>
@@ -3323,10 +3329,10 @@
         <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E120" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F120" t="n">
         <v>4.0</v>
@@ -3335,6 +3341,32 @@
         <v>0.0</v>
       </c>
       <c r="H120" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121" t="s">
+        <v>52</v>
+      </c>
+      <c r="E121" t="s">
+        <v>54</v>
+      </c>
+      <c r="F121" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H121" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -527,7 +527,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>737.0</v>
+        <v>741.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1005.0</v>
+        <v>1006.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -975,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>202.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="30">
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2076.0</v>
+        <v>2080.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1376.0</v>
+        <v>1378.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,13 +1307,13 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1108.0</v>
+        <v>1110.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
       </c>
       <c r="H42" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="43">
@@ -1827,7 +1827,7 @@
         <v>53</v>
       </c>
       <c r="F62" t="n">
-        <v>83.0</v>
+        <v>86.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2217,7 +2217,7 @@
         <v>54</v>
       </c>
       <c r="F77" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1432.0</v>
+        <v>1436.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -475,7 +475,7 @@
         <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>1879.0</v>
+        <v>1882.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>527.0</v>
+        <v>531.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -527,7 +527,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>741.0</v>
+        <v>742.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -579,7 +579,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>456.0</v>
+        <v>457.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10886.0</v>
+        <v>10893.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3419.0</v>
+        <v>3435.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,10 +813,10 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6674.0</v>
+        <v>6676.0</v>
       </c>
       <c r="G23" t="n">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="H23" t="n">
         <v>255.0</v>
@@ -891,7 +891,7 @@
         <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>1753.0</v>
+        <v>1754.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -949,7 +949,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
     </row>
     <row r="29">
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2080.0</v>
+        <v>2081.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1261,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="41">
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1110.0</v>
+        <v>1112.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1738.0</v>
+        <v>1739.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1615.0</v>
+        <v>1619.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1181.0</v>
+        <v>1191.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1565.0</v>
+        <v>1569.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1036.0</v>
+        <v>1041.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12717.0</v>
+        <v>12752.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>597.0</v>
+        <v>600.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1149.0</v>
+        <v>1159.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1436.0</v>
+        <v>1437.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -527,7 +527,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>742.0</v>
+        <v>743.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -767,7 +767,7 @@
         <v>147.0</v>
       </c>
       <c r="H21" t="n">
-        <v>1022.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="22">
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6236.0</v>
+        <v>6241.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4636.0</v>
+        <v>4642.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1006.0</v>
+        <v>1008.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1739.0</v>
+        <v>1742.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1191.0</v>
+        <v>1192.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1041.0</v>
+        <v>1043.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3153,7 +3153,7 @@
         <v>54</v>
       </c>
       <c r="F113" t="n">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12752.0</v>
+        <v>12756.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>600.0</v>
+        <v>601.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1159.0</v>
+        <v>1160.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1378.0</v>
+        <v>1380.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1112.0</v>
+        <v>1114.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -2191,7 +2191,7 @@
         <v>54</v>
       </c>
       <c r="F76" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -267,7 +267,7 @@
         <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>149.0</v>
+        <v>156.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -293,7 +293,7 @@
         <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>470.0</v>
+        <v>475.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -345,7 +345,7 @@
         <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -371,7 +371,7 @@
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>730.0</v>
+        <v>738.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -397,7 +397,7 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1239.0</v>
+        <v>1242.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>531.0</v>
+        <v>536.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -631,7 +631,7 @@
         <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>336.0</v>
+        <v>341.0</v>
       </c>
       <c r="G16" t="n">
         <v>15.0</v>
@@ -657,10 +657,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>3805.0</v>
+        <v>3844.0</v>
       </c>
       <c r="G17" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="H17" t="n">
         <v>420.0</v>
@@ -683,7 +683,7 @@
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>1743.0</v>
+        <v>1745.0</v>
       </c>
       <c r="G18" t="n">
         <v>55.0</v>
@@ -735,10 +735,10 @@
         <v>53</v>
       </c>
       <c r="F20" t="n">
-        <v>640.0</v>
+        <v>645.0</v>
       </c>
       <c r="G20" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3435.0</v>
+        <v>3444.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6676.0</v>
+        <v>6693.0</v>
       </c>
       <c r="G23" t="n">
         <v>42.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4642.0</v>
+        <v>4643.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
@@ -1047,7 +1047,7 @@
         <v>53</v>
       </c>
       <c r="F32" t="n">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1333,7 +1333,7 @@
         <v>53</v>
       </c>
       <c r="F43" t="n">
-        <v>621.0</v>
+        <v>626.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1359,7 +1359,7 @@
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>386.0</v>
+        <v>389.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1385,7 +1385,7 @@
         <v>53</v>
       </c>
       <c r="F45" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1192.0</v>
+        <v>1195.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1879,7 +1879,7 @@
         <v>54</v>
       </c>
       <c r="F64" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1905,7 +1905,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="n">
-        <v>253.0</v>
+        <v>267.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1931,7 +1931,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>2222.0</v>
+        <v>2254.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>610.0</v>
+        <v>616.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1983,7 +1983,7 @@
         <v>54</v>
       </c>
       <c r="F68" t="n">
-        <v>144.0</v>
+        <v>150.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1043.0</v>
+        <v>1050.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2295,7 +2295,7 @@
         <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>2818.0</v>
+        <v>2844.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2321,7 +2321,7 @@
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>4386.0</v>
+        <v>4420.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2867,7 +2867,7 @@
         <v>54</v>
       </c>
       <c r="F102" t="n">
-        <v>234.0</v>
+        <v>237.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -2893,7 +2893,7 @@
         <v>54</v>
       </c>
       <c r="F103" t="n">
-        <v>523.0</v>
+        <v>527.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2919,7 +2919,7 @@
         <v>54</v>
       </c>
       <c r="F104" t="n">
-        <v>279.0</v>
+        <v>283.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2971,7 +2971,7 @@
         <v>54</v>
       </c>
       <c r="F106" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12756.0</v>
+        <v>12770.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -293,7 +293,7 @@
         <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>475.0</v>
+        <v>477.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -371,7 +371,7 @@
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>738.0</v>
+        <v>741.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -423,7 +423,7 @@
         <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>762.0</v>
+        <v>764.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -631,7 +631,7 @@
         <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>341.0</v>
+        <v>343.0</v>
       </c>
       <c r="G16" t="n">
         <v>15.0</v>
@@ -657,7 +657,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>3844.0</v>
+        <v>3850.0</v>
       </c>
       <c r="G17" t="n">
         <v>104.0</v>
@@ -683,7 +683,7 @@
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>1745.0</v>
+        <v>1746.0</v>
       </c>
       <c r="G18" t="n">
         <v>55.0</v>
@@ -735,7 +735,7 @@
         <v>53</v>
       </c>
       <c r="F20" t="n">
-        <v>645.0</v>
+        <v>646.0</v>
       </c>
       <c r="G20" t="n">
         <v>21.0</v>
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10893.0</v>
+        <v>10914.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3444.0</v>
+        <v>3446.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -839,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>3641.0</v>
+        <v>3646.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6241.0</v>
+        <v>6244.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -949,7 +949,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
     </row>
     <row r="29">
@@ -1047,7 +1047,7 @@
         <v>53</v>
       </c>
       <c r="F32" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1333,7 +1333,7 @@
         <v>53</v>
       </c>
       <c r="F43" t="n">
-        <v>626.0</v>
+        <v>630.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1359,7 +1359,7 @@
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>389.0</v>
+        <v>392.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1489,7 +1489,7 @@
         <v>53</v>
       </c>
       <c r="F49" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1541,7 +1541,7 @@
         <v>53</v>
       </c>
       <c r="F51" t="n">
-        <v>699.0</v>
+        <v>702.0</v>
       </c>
       <c r="G51" t="n">
         <v>3.0</v>
@@ -1593,7 +1593,7 @@
         <v>53</v>
       </c>
       <c r="F53" t="n">
-        <v>753.0</v>
+        <v>754.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1742.0</v>
+        <v>1743.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1619.0</v>
+        <v>1620.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1195.0</v>
+        <v>1198.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1905,7 +1905,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="n">
-        <v>267.0</v>
+        <v>269.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1931,7 +1931,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>2254.0</v>
+        <v>2258.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>616.0</v>
+        <v>617.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2061,7 +2061,7 @@
         <v>54</v>
       </c>
       <c r="F71" t="n">
-        <v>2232.0</v>
+        <v>2250.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1050.0</v>
+        <v>1052.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2295,7 +2295,7 @@
         <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>2844.0</v>
+        <v>2849.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2321,7 +2321,7 @@
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>4420.0</v>
+        <v>4425.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2685,7 +2685,7 @@
         <v>54</v>
       </c>
       <c r="F95" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -3023,7 +3023,7 @@
         <v>54</v>
       </c>
       <c r="F108" t="n">
-        <v>3998.0</v>
+        <v>4001.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3049,7 +3049,7 @@
         <v>54</v>
       </c>
       <c r="F109" t="n">
-        <v>7951.0</v>
+        <v>7953.0</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>
@@ -3075,7 +3075,7 @@
         <v>54</v>
       </c>
       <c r="F110" t="n">
-        <v>1224.0</v>
+        <v>1225.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12770.0</v>
+        <v>12787.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>601.0</v>
+        <v>603.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>536.0</v>
+        <v>538.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -663,7 +663,7 @@
         <v>104.0</v>
       </c>
       <c r="H17" t="n">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
     </row>
     <row r="18">
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3446.0</v>
+        <v>3455.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6693.0</v>
+        <v>6700.0</v>
       </c>
       <c r="G23" t="n">
         <v>42.0</v>
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6244.0</v>
+        <v>6246.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4643.0</v>
+        <v>4648.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1008.0</v>
+        <v>1013.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -975,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>206.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="30">
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2081.0</v>
+        <v>2082.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1203,7 +1203,7 @@
         <v>53</v>
       </c>
       <c r="F38" t="n">
-        <v>625.0</v>
+        <v>626.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1261,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="41">
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1380.0</v>
+        <v>1385.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1114.0</v>
+        <v>1123.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1743.0</v>
+        <v>1745.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1827,7 +1827,7 @@
         <v>53</v>
       </c>
       <c r="F62" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2087,7 +2087,7 @@
         <v>54</v>
       </c>
       <c r="F72" t="n">
-        <v>846.0</v>
+        <v>847.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1052.0</v>
+        <v>1059.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>348.0</v>
+        <v>350.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12787.0</v>
+        <v>12809.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>538.0</v>
+        <v>545.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -579,7 +579,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>457.0</v>
+        <v>459.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -819,7 +819,7 @@
         <v>42.0</v>
       </c>
       <c r="H23" t="n">
-        <v>255.0</v>
+        <v>261.0</v>
       </c>
     </row>
     <row r="24">
@@ -917,13 +917,13 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4648.0</v>
+        <v>4649.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
       </c>
       <c r="H27" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="28">
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2082.0</v>
+        <v>2083.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1385.0</v>
+        <v>1386.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1123.0</v>
+        <v>1126.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1198.0</v>
+        <v>1201.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1723,7 +1723,7 @@
         <v>53</v>
       </c>
       <c r="F58" t="n">
-        <v>2824.0</v>
+        <v>2825.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1059.0</v>
+        <v>1065.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3179,7 +3179,7 @@
         <v>54</v>
       </c>
       <c r="F114" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12809.0</v>
+        <v>12825.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>603.0</v>
+        <v>606.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -397,7 +397,7 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1242.0</v>
+        <v>1249.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1437.0</v>
+        <v>1439.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -527,7 +527,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>743.0</v>
+        <v>744.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10914.0</v>
+        <v>10930.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3455.0</v>
+        <v>3461.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,10 +813,10 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6700.0</v>
+        <v>6701.0</v>
       </c>
       <c r="G23" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="H23" t="n">
         <v>261.0</v>
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6246.0</v>
+        <v>6247.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -891,7 +891,7 @@
         <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>1754.0</v>
+        <v>1755.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1013.0</v>
+        <v>1014.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1126.0</v>
+        <v>1127.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1745.0</v>
+        <v>1746.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1201.0</v>
+        <v>1203.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1569.0</v>
+        <v>1571.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1065.0</v>
+        <v>1069.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12825.0</v>
+        <v>12832.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2083.0</v>
+        <v>2087.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1386.0</v>
+        <v>1388.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1127.0</v>
+        <v>1133.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -267,7 +267,7 @@
         <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -293,7 +293,7 @@
         <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>477.0</v>
+        <v>480.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -371,7 +371,7 @@
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>741.0</v>
+        <v>753.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -657,10 +657,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>3850.0</v>
+        <v>3852.0</v>
       </c>
       <c r="G17" t="n">
-        <v>104.0</v>
+        <v>109.0</v>
       </c>
       <c r="H17" t="n">
         <v>422.0</v>
@@ -735,7 +735,7 @@
         <v>53</v>
       </c>
       <c r="F20" t="n">
-        <v>646.0</v>
+        <v>656.0</v>
       </c>
       <c r="G20" t="n">
         <v>21.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3461.0</v>
+        <v>3470.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4649.0</v>
+        <v>4650.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
@@ -1047,7 +1047,7 @@
         <v>53</v>
       </c>
       <c r="F32" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1333,7 +1333,7 @@
         <v>53</v>
       </c>
       <c r="F43" t="n">
-        <v>630.0</v>
+        <v>635.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1385,7 +1385,7 @@
         <v>53</v>
       </c>
       <c r="F45" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1411,7 +1411,7 @@
         <v>53</v>
       </c>
       <c r="F46" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1905,7 +1905,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="n">
-        <v>269.0</v>
+        <v>275.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1931,7 +1931,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>2258.0</v>
+        <v>2268.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>617.0</v>
+        <v>621.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1983,7 +1983,7 @@
         <v>54</v>
       </c>
       <c r="F68" t="n">
-        <v>150.0</v>
+        <v>154.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1069.0</v>
+        <v>1071.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2269,7 +2269,7 @@
         <v>54</v>
       </c>
       <c r="F79" t="n">
-        <v>76.0</v>
+        <v>81.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2295,7 +2295,7 @@
         <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>2849.0</v>
+        <v>2870.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2321,7 +2321,7 @@
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>4425.0</v>
+        <v>4447.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2867,7 +2867,7 @@
         <v>54</v>
       </c>
       <c r="F102" t="n">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -2919,7 +2919,7 @@
         <v>54</v>
       </c>
       <c r="F104" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2971,7 +2971,7 @@
         <v>54</v>
       </c>
       <c r="F106" t="n">
-        <v>290.0</v>
+        <v>293.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3179,7 +3179,7 @@
         <v>54</v>
       </c>
       <c r="F114" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12832.0</v>
+        <v>12846.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>606.0</v>
+        <v>609.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -475,7 +475,7 @@
         <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>1882.0</v>
+        <v>1884.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10930.0</v>
+        <v>10931.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3470.0</v>
+        <v>3474.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -839,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>3646.0</v>
+        <v>3648.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4650.0</v>
+        <v>4657.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1014.0</v>
+        <v>1015.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -1515,7 +1515,7 @@
         <v>53</v>
       </c>
       <c r="F50" t="n">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
       <c r="G50" t="n">
         <v>1.0</v>
@@ -1593,7 +1593,7 @@
         <v>53</v>
       </c>
       <c r="F53" t="n">
-        <v>754.0</v>
+        <v>756.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1746.0</v>
+        <v>1747.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1620.0</v>
+        <v>1621.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -2061,7 +2061,7 @@
         <v>54</v>
       </c>
       <c r="F71" t="n">
-        <v>2250.0</v>
+        <v>2259.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1071.0</v>
+        <v>1073.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2451,7 +2451,7 @@
         <v>54</v>
       </c>
       <c r="F86" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3023,7 +3023,7 @@
         <v>54</v>
       </c>
       <c r="F108" t="n">
-        <v>4001.0</v>
+        <v>4002.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3075,7 +3075,7 @@
         <v>54</v>
       </c>
       <c r="F110" t="n">
-        <v>1225.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3101,7 +3101,7 @@
         <v>54</v>
       </c>
       <c r="F111" t="n">
-        <v>3879.0</v>
+        <v>3880.0</v>
       </c>
       <c r="G111" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12846.0</v>
+        <v>12867.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -397,7 +397,7 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1249.0</v>
+        <v>1251.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1439.0</v>
+        <v>1442.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3474.0</v>
+        <v>3485.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6701.0</v>
+        <v>6719.0</v>
       </c>
       <c r="G23" t="n">
         <v>43.0</v>
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6247.0</v>
+        <v>6255.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2087.0</v>
+        <v>2089.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1177,7 +1177,7 @@
         <v>53</v>
       </c>
       <c r="F37" t="n">
-        <v>1734.0</v>
+        <v>1735.0</v>
       </c>
       <c r="G37" t="n">
         <v>7.0</v>
@@ -1261,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="41">
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1388.0</v>
+        <v>1398.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1133.0</v>
+        <v>1140.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1747.0</v>
+        <v>1751.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1621.0</v>
+        <v>1624.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1203.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1571.0</v>
+        <v>1575.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1827,7 +1827,7 @@
         <v>53</v>
       </c>
       <c r="F62" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1073.0</v>
+        <v>1081.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2425,7 +2425,7 @@
         <v>54</v>
       </c>
       <c r="F85" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12867.0</v>
+        <v>12879.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>609.0</v>
+        <v>610.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1160.0</v>
+        <v>1161.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3485.0</v>
+        <v>3489.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,10 +813,10 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6719.0</v>
+        <v>6721.0</v>
       </c>
       <c r="G23" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="H23" t="n">
         <v>261.0</v>
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2089.0</v>
+        <v>2090.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1398.0</v>
+        <v>1399.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1751.0</v>
+        <v>1752.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1624.0</v>
+        <v>1625.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1208.0</v>
+        <v>1210.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12879.0</v>
+        <v>12892.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -579,7 +579,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>459.0</v>
+        <v>470.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10931.0</v>
+        <v>10944.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3489.0</v>
+        <v>3491.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6721.0</v>
+        <v>6733.0</v>
       </c>
       <c r="G23" t="n">
         <v>44.0</v>
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2090.0</v>
+        <v>2091.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1140.0</v>
+        <v>1141.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1081.0</v>
+        <v>1083.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12892.0</v>
+        <v>12894.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>610.0</v>
+        <v>614.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -527,7 +527,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>744.0</v>
+        <v>747.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -579,7 +579,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1015.0</v>
+        <v>1017.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2091.0</v>
+        <v>2092.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1141.0</v>
+        <v>1143.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1442.0</v>
+        <v>1443.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10944.0</v>
+        <v>10951.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3491.0</v>
+        <v>3506.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6733.0</v>
+        <v>6735.0</v>
       </c>
       <c r="G23" t="n">
         <v>44.0</v>
@@ -1203,7 +1203,7 @@
         <v>53</v>
       </c>
       <c r="F38" t="n">
-        <v>626.0</v>
+        <v>627.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1752.0</v>
+        <v>1753.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1625.0</v>
+        <v>1627.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1210.0</v>
+        <v>1213.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1723,7 +1723,7 @@
         <v>53</v>
       </c>
       <c r="F58" t="n">
-        <v>2825.0</v>
+        <v>2826.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1575.0</v>
+        <v>1576.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1083.0</v>
+        <v>1087.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3153,7 +3153,7 @@
         <v>54</v>
       </c>
       <c r="F113" t="n">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12894.0</v>
+        <v>12910.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>614.0</v>
+        <v>616.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1161.0</v>
+        <v>1163.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -397,7 +397,7 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1251.0</v>
+        <v>1253.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -715,7 +715,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="20">
@@ -761,7 +761,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10951.0</v>
+        <v>10963.0</v>
       </c>
       <c r="G21" t="n">
         <v>147.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3506.0</v>
+        <v>3510.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6735.0</v>
+        <v>6742.0</v>
       </c>
       <c r="G23" t="n">
         <v>44.0</v>
@@ -839,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>3648.0</v>
+        <v>3649.0</v>
       </c>
       <c r="G24" t="n">
         <v>7.0</v>
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6255.0</v>
+        <v>6258.0</v>
       </c>
       <c r="G25" t="n">
         <v>8.0</v>
@@ -949,7 +949,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
     </row>
     <row r="29">
@@ -1489,7 +1489,7 @@
         <v>53</v>
       </c>
       <c r="F49" t="n">
-        <v>142.0</v>
+        <v>144.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1541,7 +1541,7 @@
         <v>53</v>
       </c>
       <c r="F51" t="n">
-        <v>702.0</v>
+        <v>703.0</v>
       </c>
       <c r="G51" t="n">
         <v>3.0</v>
@@ -1567,7 +1567,7 @@
         <v>53</v>
       </c>
       <c r="F52" t="n">
-        <v>1598.0</v>
+        <v>1599.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1753.0</v>
+        <v>1757.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1576.0</v>
+        <v>1578.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -2061,7 +2061,7 @@
         <v>54</v>
       </c>
       <c r="F71" t="n">
-        <v>2259.0</v>
+        <v>2271.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1087.0</v>
+        <v>1096.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>353.0</v>
+        <v>355.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -3127,7 +3127,7 @@
         <v>54</v>
       </c>
       <c r="F112" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G112" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12910.0</v>
+        <v>12927.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1163.0</v>
+        <v>1165.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1443.0</v>
+        <v>1444.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3510.0</v>
+        <v>3524.0</v>
       </c>
       <c r="G22" t="n">
         <v>20.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6742.0</v>
+        <v>6746.0</v>
       </c>
       <c r="G23" t="n">
         <v>44.0</v>
@@ -917,13 +917,13 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4657.0</v>
+        <v>4666.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
       </c>
       <c r="H27" t="n">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="28">
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1017.0</v>
+        <v>1024.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2092.0</v>
+        <v>2094.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1399.0</v>
+        <v>1406.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1143.0</v>
+        <v>1162.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1627.0</v>
+        <v>1631.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1213.0</v>
+        <v>1215.0</v>
       </c>
       <c r="G57" t="n">
         <v>5.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1578.0</v>
+        <v>1579.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1853,7 +1853,7 @@
         <v>53</v>
       </c>
       <c r="F63" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1096.0</v>
+        <v>1101.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2503,7 +2503,7 @@
         <v>54</v>
       </c>
       <c r="F88" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -3153,7 +3153,7 @@
         <v>54</v>
       </c>
       <c r="F113" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12927.0</v>
+        <v>12945.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3231,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>616.0</v>
+        <v>617.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4666.0</v>
+        <v>4672.0</v>
       </c>
       <c r="G27" t="n">
         <v>36.0</v>
@@ -995,7 +995,7 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2094.0</v>
+        <v>2099.0</v>
       </c>
       <c r="G30" t="n">
         <v>1.0</v>
@@ -1281,7 +1281,7 @@
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1406.0</v>
+        <v>1407.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1162.0</v>
+        <v>1165.0</v>
       </c>
       <c r="G42" t="n">
         <v>1.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1631.0</v>
+        <v>1633.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1723,7 +1723,7 @@
         <v>53</v>
       </c>
       <c r="F58" t="n">
-        <v>2826.0</v>
+        <v>2827.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1579.0</v>
+        <v>1580.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1879,7 +1879,7 @@
         <v>54</v>
       </c>
       <c r="F64" t="n">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1905,7 +1905,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="n">
-        <v>275.0</v>
+        <v>291.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1931,7 +1931,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>2268.0</v>
+        <v>2294.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>621.0</v>
+        <v>629.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1983,7 +1983,7 @@
         <v>54</v>
       </c>
       <c r="F68" t="n">
-        <v>154.0</v>
+        <v>158.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2269,7 +2269,7 @@
         <v>54</v>
       </c>
       <c r="F79" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2295,7 +2295,7 @@
         <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>2870.0</v>
+        <v>2910.0</v>
       </c>
       <c r="G80" t="n">
         <v>2.0</v>
@@ -2321,7 +2321,7 @@
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>4447.0</v>
+        <v>4494.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2347,7 +2347,7 @@
         <v>54</v>
       </c>
       <c r="F82" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>355.0</v>
+        <v>356.0</v>
       </c>
       <c r="G90" t="n">
         <v>1.0</v>
@@ -2919,7 +2919,7 @@
         <v>54</v>
       </c>
       <c r="F104" t="n">
-        <v>284.0</v>
+        <v>291.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2971,7 +2971,7 @@
         <v>54</v>
       </c>
       <c r="F106" t="n">
-        <v>293.0</v>
+        <v>295.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12945.0</v>
+        <v>12949.0</v>
       </c>
       <c r="G115" t="n">
         <v>13.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1165.0</v>
+        <v>1166.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/tested_positives_ZR.xlsx
+++ b/Download/tested_positives_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="55">
   <si>
     <t>Area</t>
   </si>
@@ -107,6 +107,9 @@
     <t>Cuneo</t>
   </si>
   <si>
+    <t>Firenze</t>
+  </si>
+  <si>
     <t>Lucca</t>
   </si>
   <si>
@@ -159,9 +162,6 @@
   </si>
   <si>
     <t>Vercelli</t>
-  </si>
-  <si>
-    <t>Firenze</t>
   </si>
   <si>
     <t>Salerno</t>
@@ -293,7 +293,7 @@
         <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>480.0</v>
+        <v>356.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -397,7 +397,7 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1253.0</v>
+        <v>1259.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1444.0</v>
+        <v>1445.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>545.0</v>
+        <v>551.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -527,7 +527,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>747.0</v>
+        <v>8.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -553,7 +553,7 @@
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0</v>
+        <v>175.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -579,10 +579,10 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>471.0</v>
+        <v>227.0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>102.0</v>
+        <v>465.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -619,25 +619,25 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>343.0</v>
+        <v>103.0</v>
       </c>
       <c r="G16" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -651,19 +651,19 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>3852.0</v>
+        <v>467.0</v>
       </c>
       <c r="G17" t="n">
-        <v>109.0</v>
+        <v>15.0</v>
       </c>
       <c r="H17" t="n">
-        <v>422.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
@@ -677,19 +677,19 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>1746.0</v>
+        <v>3852.0</v>
       </c>
       <c r="G18" t="n">
-        <v>55.0</v>
+        <v>109.0</v>
       </c>
       <c r="H18" t="n">
-        <v>233.0</v>
+        <v>422.0</v>
       </c>
     </row>
     <row r="19">
@@ -703,19 +703,19 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
         <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0</v>
+        <v>1746.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>55.0</v>
       </c>
       <c r="H19" t="n">
-        <v>59.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="20">
@@ -729,19 +729,19 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
         <v>53</v>
       </c>
       <c r="F20" t="n">
-        <v>656.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="21">
@@ -752,22 +752,22 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>10963.0</v>
+        <v>656.0</v>
       </c>
       <c r="G21" t="n">
-        <v>147.0</v>
+        <v>21.0</v>
       </c>
       <c r="H21" t="n">
-        <v>1023.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -787,13 +787,13 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>3524.0</v>
+        <v>10975.0</v>
       </c>
       <c r="G22" t="n">
-        <v>20.0</v>
+        <v>147.0</v>
       </c>
       <c r="H22" t="n">
-        <v>76.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="23">
@@ -807,19 +807,19 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>6746.0</v>
+        <v>3525.0</v>
       </c>
       <c r="G23" t="n">
-        <v>44.0</v>
+        <v>20.0</v>
       </c>
       <c r="H23" t="n">
-        <v>261.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="24">
@@ -830,22 +830,22 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>3649.0</v>
+        <v>6777.0</v>
       </c>
       <c r="G24" t="n">
-        <v>7.0</v>
+        <v>45.0</v>
       </c>
       <c r="H24" t="n">
-        <v>209.0</v>
+        <v>261.0</v>
       </c>
     </row>
     <row r="25">
@@ -856,22 +856,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>6258.0</v>
+        <v>3649.0</v>
       </c>
       <c r="G25" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H25" t="n">
-        <v>572.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="26">
@@ -885,19 +885,19 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
         <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>1755.0</v>
+        <v>6260.0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H26" t="n">
-        <v>19.0</v>
+        <v>572.0</v>
       </c>
     </row>
     <row r="27">
@@ -911,19 +911,19 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>4672.0</v>
+        <v>1755.0</v>
       </c>
       <c r="G27" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" t="n">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="28">
@@ -934,22 +934,22 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>1024.0</v>
+        <v>4675.0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0</v>
+        <v>37.0</v>
       </c>
       <c r="H28" t="n">
-        <v>434.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="29">
@@ -963,19 +963,19 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
         <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0</v>
+        <v>1685.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" t="n">
-        <v>207.0</v>
+        <v>434.0</v>
       </c>
     </row>
     <row r="30">
@@ -995,13 +995,13 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>2099.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="31">
@@ -1009,25 +1009,25 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
         <v>53</v>
       </c>
       <c r="F31" t="n">
-        <v>122.0</v>
+        <v>2099.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -1035,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
         <v>53</v>
       </c>
       <c r="F32" t="n">
-        <v>60.0</v>
+        <v>6.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -1067,19 +1067,19 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
         <v>53</v>
       </c>
       <c r="F33" t="n">
-        <v>15.0</v>
+        <v>122.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="34">
@@ -1093,19 +1093,19 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
         <v>53</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0</v>
+        <v>60.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="35">
@@ -1116,22 +1116,22 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
       </c>
       <c r="F35" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
       </c>
       <c r="H35" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -1142,22 +1142,22 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
       </c>
       <c r="F36" t="n">
-        <v>2352.0</v>
+        <v>2.0</v>
       </c>
       <c r="G36" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H36" t="n">
-        <v>143.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -1168,22 +1168,22 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
         <v>53</v>
       </c>
       <c r="F37" t="n">
-        <v>1735.0</v>
+        <v>16.0</v>
       </c>
       <c r="G37" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="38">
@@ -1197,19 +1197,19 @@
         <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
         <v>53</v>
       </c>
       <c r="F38" t="n">
-        <v>627.0</v>
+        <v>2352.0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="39">
@@ -1220,22 +1220,22 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
         <v>53</v>
       </c>
       <c r="F39" t="n">
-        <v>101.0</v>
+        <v>1735.0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="40">
@@ -1246,22 +1246,22 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
         <v>53</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0</v>
+        <v>627.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H40" t="n">
-        <v>161.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -1275,16 +1275,16 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E41" t="s">
         <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>1407.0</v>
+        <v>101.0</v>
       </c>
       <c r="G41" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1301,19 +1301,19 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E42" t="s">
         <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>1165.0</v>
+        <v>0.0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>29.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="43">
@@ -1321,22 +1321,22 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s">
         <v>53</v>
       </c>
       <c r="F43" t="n">
-        <v>635.0</v>
+        <v>1407.0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1347,25 +1347,25 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>392.0</v>
+        <v>1165.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="45">
@@ -1379,13 +1379,13 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E45" t="s">
         <v>53</v>
       </c>
       <c r="F45" t="n">
-        <v>41.0</v>
+        <v>635.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1405,13 +1405,13 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>53</v>
       </c>
       <c r="F46" t="n">
-        <v>115.0</v>
+        <v>392.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1428,19 +1428,19 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E47" t="s">
         <v>53</v>
       </c>
       <c r="F47" t="n">
-        <v>569.0</v>
+        <v>41.0</v>
       </c>
       <c r="G47" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1454,16 +1454,16 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E48" t="s">
         <v>53</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>115.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1480,19 +1480,19 @@
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
         <v>53</v>
       </c>
       <c r="F49" t="n">
-        <v>144.0</v>
+        <v>569.0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1509,16 +1509,16 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
       </c>
       <c r="F50" t="n">
-        <v>84.0</v>
+        <v>1.0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1535,19 +1535,19 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E51" t="s">
         <v>53</v>
       </c>
       <c r="F51" t="n">
-        <v>703.0</v>
+        <v>144.0</v>
       </c>
       <c r="G51" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H51" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1561,19 +1561,19 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E52" t="s">
         <v>53</v>
       </c>
       <c r="F52" t="n">
-        <v>1599.0</v>
+        <v>84.0</v>
       </c>
       <c r="G52" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H52" t="n">
-        <v>86.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -1593,13 +1593,13 @@
         <v>53</v>
       </c>
       <c r="F53" t="n">
-        <v>756.0</v>
+        <v>703.0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="54">
@@ -1610,22 +1610,22 @@
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1757.0</v>
+        <v>1599.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="55">
@@ -1636,19 +1636,19 @@
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>1633.0</v>
+        <v>756.0</v>
       </c>
       <c r="G55" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1665,19 +1665,19 @@
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E56" t="s">
         <v>53</v>
       </c>
       <c r="F56" t="n">
+        <v>1759.0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H56" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -1691,16 +1691,16 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E57" t="s">
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1215.0</v>
+        <v>1635.0</v>
       </c>
       <c r="G57" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1723,13 +1723,13 @@
         <v>53</v>
       </c>
       <c r="F58" t="n">
-        <v>2827.0</v>
+        <v>1.0</v>
       </c>
       <c r="G58" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1743,16 +1743,16 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E59" t="s">
         <v>53</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0</v>
+        <v>1221.0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1769,19 +1769,19 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E60" t="s">
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>1580.0</v>
+        <v>2827.0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="61">
@@ -1792,16 +1792,16 @@
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E61" t="s">
         <v>53</v>
       </c>
       <c r="F61" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1818,19 +1818,19 @@
         <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E62" t="s">
         <v>53</v>
       </c>
       <c r="F62" t="n">
-        <v>88.0</v>
+        <v>1580.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1847,13 +1847,13 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E63" t="s">
         <v>53</v>
       </c>
       <c r="F63" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1867,19 +1867,19 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F64" t="n">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1899,13 +1899,13 @@
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E65" t="s">
         <v>54</v>
       </c>
       <c r="F65" t="n">
-        <v>291.0</v>
+        <v>29.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,13 +1925,13 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>2294.0</v>
+        <v>280.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,13 +1951,13 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>629.0</v>
+        <v>2294.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1977,13 +1977,13 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
         <v>54</v>
       </c>
       <c r="F68" t="n">
-        <v>158.0</v>
+        <v>629.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2000,16 +2000,16 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
         <v>54</v>
       </c>
       <c r="F69" t="n">
-        <v>9.0</v>
+        <v>158.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2026,16 +2026,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
         <v>54</v>
       </c>
       <c r="F70" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2055,19 +2055,19 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E71" t="s">
         <v>54</v>
       </c>
       <c r="F71" t="n">
-        <v>2271.0</v>
+        <v>1.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2078,22 +2078,22 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
         <v>54</v>
       </c>
       <c r="F72" t="n">
-        <v>847.0</v>
+        <v>2271.0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="73">
@@ -2107,16 +2107,16 @@
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
         <v>54</v>
       </c>
       <c r="F73" t="n">
-        <v>130.0</v>
+        <v>848.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2133,16 +2133,16 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E74" t="s">
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>1101.0</v>
+        <v>130.0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2156,19 +2156,19 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E75" t="s">
         <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>28.0</v>
+        <v>1109.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2185,13 +2185,13 @@
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E76" t="s">
         <v>54</v>
       </c>
       <c r="F76" t="n">
-        <v>25.0</v>
+        <v>13.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2211,13 +2211,13 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E77" t="s">
         <v>54</v>
       </c>
       <c r="F77" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E78" t="s">
         <v>54</v>
       </c>
       <c r="F78" t="n">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2257,19 +2257,19 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s">
         <v>54</v>
       </c>
       <c r="F79" t="n">
-        <v>82.0</v>
+        <v>18.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2286,19 +2286,19 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E80" t="s">
         <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>2910.0</v>
+        <v>2.0</v>
       </c>
       <c r="G80" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2315,19 +2315,19 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E81" t="s">
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>4494.0</v>
+        <v>93.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
       </c>
       <c r="H81" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -2341,16 +2341,16 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
         <v>54</v>
       </c>
       <c r="F82" t="n">
-        <v>53.0</v>
+        <v>2910.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2364,22 +2364,22 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
         <v>54</v>
       </c>
       <c r="F83" t="n">
-        <v>32.0</v>
+        <v>4494.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="84">
@@ -2390,19 +2390,19 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E84" t="s">
         <v>54</v>
       </c>
       <c r="F84" t="n">
-        <v>24.0</v>
+        <v>53.0</v>
       </c>
       <c r="G84" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2419,13 +2419,13 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E85" t="s">
         <v>54</v>
       </c>
       <c r="F85" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2442,19 +2442,19 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
         <v>54</v>
       </c>
       <c r="F86" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2468,22 +2468,22 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E87" t="s">
         <v>54</v>
       </c>
       <c r="F87" t="n">
-        <v>74.0</v>
+        <v>30.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -2494,16 +2494,16 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E88" t="s">
         <v>54</v>
       </c>
       <c r="F88" t="n">
-        <v>137.0</v>
+        <v>8.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2520,22 +2520,22 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E89" t="s">
         <v>54</v>
       </c>
       <c r="F89" t="n">
-        <v>1.0</v>
+        <v>74.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="90">
@@ -2549,16 +2549,16 @@
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E90" t="s">
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>356.0</v>
+        <v>137.0</v>
       </c>
       <c r="G90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2572,16 +2572,16 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
         <v>54</v>
       </c>
       <c r="F91" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2598,19 +2598,19 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
         <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>10.0</v>
+        <v>356.0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H92" t="n">
         <v>0.0</v>
@@ -2621,19 +2621,19 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E93" t="s">
         <v>54</v>
       </c>
       <c r="F93" t="n">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2647,19 +2647,19 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E94" t="s">
         <v>54</v>
       </c>
       <c r="F94" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2676,16 +2676,16 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E95" t="s">
         <v>54</v>
       </c>
       <c r="F95" t="n">
-        <v>114.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2702,16 +2702,16 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E96" t="s">
         <v>54</v>
       </c>
       <c r="F96" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2728,16 +2728,16 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E97" t="s">
         <v>54</v>
       </c>
       <c r="F97" t="n">
-        <v>7.0</v>
+        <v>114.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2754,22 +2754,22 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E98" t="s">
         <v>54</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
       </c>
       <c r="H98" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -2783,13 +2783,13 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E99" t="s">
         <v>54</v>
       </c>
       <c r="F99" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2809,19 +2809,19 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E100" t="s">
         <v>54</v>
       </c>
       <c r="F100" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="101">
@@ -2829,19 +2829,19 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E101" t="s">
         <v>54</v>
       </c>
       <c r="F101" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -2855,25 +2855,25 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E102" t="s">
         <v>54</v>
       </c>
       <c r="F102" t="n">
-        <v>239.0</v>
+        <v>40.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="103">
@@ -2884,16 +2884,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E103" t="s">
         <v>54</v>
       </c>
       <c r="F103" t="n">
-        <v>527.0</v>
+        <v>3.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2913,13 +2913,13 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E104" t="s">
         <v>54</v>
       </c>
       <c r="F104" t="n">
-        <v>291.0</v>
+        <v>239.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2939,13 +2939,13 @@
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E105" t="s">
         <v>54</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>527.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2965,13 +2965,13 @@
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E106" t="s">
         <v>54</v>
       </c>
       <c r="F106" t="n">
-        <v>295.0</v>
+        <v>291.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -2988,16 +2988,16 @@
         <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E107" t="s">
         <v>54</v>
       </c>
       <c r="F107" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3014,16 +3014,16 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E108" t="s">
         <v>54</v>
       </c>
       <c r="F108" t="n">
-        <v>4002.0</v>
+        <v>295.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3040,22 +3040,22 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E109" t="s">
         <v>54</v>
       </c>
       <c r="F109" t="n">
-        <v>7953.0</v>
+        <v>13.0</v>
       </c>
       <c r="G109" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H109" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="110">
@@ -3069,19 +3069,19 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E110" t="s">
         <v>54</v>
       </c>
       <c r="F110" t="n">
-        <v>1228.0</v>
+        <v>4002.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
       </c>
       <c r="H110" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -3095,19 +3095,19 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E111" t="s">
         <v>54</v>
       </c>
       <c r="F111" t="n">
-        <v>3880.0</v>
+        <v>7953.0</v>
       </c>
       <c r="G111" t="n">
         <v>1.0</v>
       </c>
       <c r="H111" t="n">
-        <v>23.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="112">
@@ -3127,13 +3127,13 @@
         <v>54</v>
       </c>
       <c r="F112" t="n">
-        <v>76.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G112" t="n">
         <v>0.0</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="113">
@@ -3144,22 +3144,22 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E113" t="s">
         <v>54</v>
       </c>
       <c r="F113" t="n">
-        <v>330.0</v>
+        <v>3880.0</v>
       </c>
       <c r="G113" t="n">
         <v>1.0</v>
       </c>
       <c r="H113" t="n">
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="114">
@@ -3170,16 +3170,16 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E114" t="s">
         <v>54</v>
       </c>
       <c r="F114" t="n">
-        <v>153.0</v>
+        <v>76.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -3199,19 +3199,19 @@
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E115" t="s">
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>12949.0</v>
+        <v>333.0</v>
       </c>
       <c r="G115" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="116">
@@ -3225,19 +3225,19 @@
         <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E116" t="s">
         <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>617.0</v>
+        <v>153.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -3251,16 +3251,16 @@
         <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E117" t="s">
         <v>54</v>
       </c>
       <c r="F117" t="n">
-        <v>4.0</v>
+        <v>12970.0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3277,19 +3277,19 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E118" t="s">
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>1166.0</v>
+        <v>617.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>6.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="119">
@@ -3300,16 +3300,16 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E119" t="s">
         <v>54</v>
       </c>
       <c r="F119" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G119" t="n">
         <v>0.0</v>
@@ -3326,22 +3326,22 @@
         <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E120" t="s">
         <v>54</v>
       </c>
       <c r="F120" t="n">
-        <v>4.0</v>
+        <v>1166.0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="121">
@@ -3352,21 +3352,47 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" t="s">
+        <v>51</v>
+      </c>
+      <c r="E121" t="s">
+        <v>54</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" t="s">
         <v>20</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D122" t="s">
         <v>52</v>
       </c>
-      <c r="E121" t="s">
-        <v>54</v>
-      </c>
-      <c r="F121" t="n">
+      <c r="E122" t="s">
+        <v>54</v>
+      </c>
+      <c r="F122" t="n">
         <v>5.0</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H121" t="n">
+      <c r="G122" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H122" t="n">
         <v>0.0</v>
       </c>
     </row>
